--- a/V2 BETA/RRF/Valkyrie Connection Table.xlsx
+++ b/V2 BETA/RRF/Valkyrie Connection Table.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29912"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29917"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3837cd5b4a1a02ac/Document Library/GitHub/Project-Valkyrie/Firmware/RRF/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1158" documentId="8_{C788BE8B-89FF-47EE-BC54-747C3D562542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39160140-E775-4DB6-BE42-C7BD3CC79B01}"/>
+  <xr:revisionPtr revIDLastSave="1605" documentId="8_{C788BE8B-89FF-47EE-BC54-747C3D562542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A38CC013-3949-459A-A6E3-DEAD98A85760}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="16440" firstSheet="1" activeTab="1" xr2:uid="{344B6B93-88E2-4E8A-A19A-9E2625195A37}"/>
   </bookViews>
   <sheets>
     <sheet name="DUET 3 6HC" sheetId="1" r:id="rId1"/>
-    <sheet name="OCTOPUS PRO" sheetId="3" r:id="rId2"/>
-    <sheet name="SKR Super8" sheetId="4" r:id="rId3"/>
-    <sheet name="GX 20" sheetId="2" r:id="rId4"/>
+    <sheet name="V2 Duet beta " sheetId="5" r:id="rId2"/>
+    <sheet name="OCTOPUS PRO" sheetId="3" r:id="rId3"/>
+    <sheet name="SKR Super8" sheetId="4" r:id="rId4"/>
+    <sheet name="GX 20" sheetId="2" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1832" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2327" uniqueCount="517">
   <si>
     <t>Type</t>
   </si>
@@ -434,6 +435,297 @@
     <t>temp3</t>
   </si>
   <si>
+    <t>mm^2</t>
+  </si>
+  <si>
+    <t>current 12v</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSU 12V </t>
+  </si>
+  <si>
+    <t>PSU24V</t>
+  </si>
+  <si>
+    <t>PSU 24V</t>
+  </si>
+  <si>
+    <t>IO_1_3V3</t>
+  </si>
+  <si>
+    <t>sensor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filament buffer ROS ( maybe used for auto feed ) </t>
+  </si>
+  <si>
+    <t>IO_1_in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IO_1_gnd </t>
+  </si>
+  <si>
+    <t>IO_1_out</t>
+  </si>
+  <si>
+    <t>IO_1_5V</t>
+  </si>
+  <si>
+    <t>IO_2_3V3</t>
+  </si>
+  <si>
+    <t>IO_2_in</t>
+  </si>
+  <si>
+    <t>IO_2_gnd</t>
+  </si>
+  <si>
+    <t>IO_2_out</t>
+  </si>
+  <si>
+    <t>IO_2_5V</t>
+  </si>
+  <si>
+    <t>IO_3_3V3</t>
+  </si>
+  <si>
+    <t>Filament buffer ROS</t>
+  </si>
+  <si>
+    <t>IO_3_in</t>
+  </si>
+  <si>
+    <t>IO_3_gnd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sensor </t>
+  </si>
+  <si>
+    <t>IO_3_out</t>
+  </si>
+  <si>
+    <t>IO_3_5V</t>
+  </si>
+  <si>
+    <t>IO_4_3V3</t>
+  </si>
+  <si>
+    <t>IO_4_in</t>
+  </si>
+  <si>
+    <t>IO_4_gnd</t>
+  </si>
+  <si>
+    <t>IO_4_out</t>
+  </si>
+  <si>
+    <t>IO_4_5V</t>
+  </si>
+  <si>
+    <t>IO_5_3V3</t>
+  </si>
+  <si>
+    <t>Anvil Nozzle Probe</t>
+  </si>
+  <si>
+    <t>IO_5_in</t>
+  </si>
+  <si>
+    <t>io5.in</t>
+  </si>
+  <si>
+    <t>IO_5_gnd</t>
+  </si>
+  <si>
+    <t>IO_5_out</t>
+  </si>
+  <si>
+    <t>IO_5_5V</t>
+  </si>
+  <si>
+    <t>IO_6_3V3</t>
+  </si>
+  <si>
+    <t>IO_6_in</t>
+  </si>
+  <si>
+    <t>IO_6_gnd</t>
+  </si>
+  <si>
+    <t>IO_6_out</t>
+  </si>
+  <si>
+    <t>IO_6_5V</t>
+  </si>
+  <si>
+    <t>IO_7_3V3</t>
+  </si>
+  <si>
+    <t>IO_7_in</t>
+  </si>
+  <si>
+    <t>IO_7_gnd</t>
+  </si>
+  <si>
+    <t>IO_7_out</t>
+  </si>
+  <si>
+    <t>IO_7_5V</t>
+  </si>
+  <si>
+    <t>IO_8_3V3</t>
+  </si>
+  <si>
+    <t>IO_8_in</t>
+  </si>
+  <si>
+    <t>IO_8_gnd</t>
+  </si>
+  <si>
+    <t>IO_8_out</t>
+  </si>
+  <si>
+    <t>IO_8_5V</t>
+  </si>
+  <si>
+    <t>power</t>
+  </si>
+  <si>
+    <t>12v power , Cpap, water pump+fan+Flow meter</t>
+  </si>
+  <si>
+    <t>2.2A + 800ma+ 500ma</t>
+  </si>
+  <si>
+    <t>SSR dry box heater</t>
+  </si>
+  <si>
+    <t>SSR Bed heater</t>
+  </si>
+  <si>
+    <t>OUT 4_gnd</t>
+  </si>
+  <si>
+    <t>SSR Chamber heater</t>
+  </si>
+  <si>
+    <t>OUT 4_vout</t>
+  </si>
+  <si>
+    <t>OUT 4_tach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSR Chamber heater </t>
+  </si>
+  <si>
+    <t>OUT 4_out</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fan wiring TBC dot star or RGB </t>
+  </si>
+  <si>
+    <t>OUT 5_gnd</t>
+  </si>
+  <si>
+    <t>VIN 24v</t>
+  </si>
+  <si>
+    <t>OUT 5_vout</t>
+  </si>
+  <si>
+    <t>OUT 5_tach</t>
+  </si>
+  <si>
+    <t>OUT 5_out</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fan </t>
+  </si>
+  <si>
+    <t>CPAP PWM</t>
+  </si>
+  <si>
+    <t>OUT 6_gnd</t>
+  </si>
+  <si>
+    <t>OUT 6_vout</t>
+  </si>
+  <si>
+    <t>OUT 6_tach</t>
+  </si>
+  <si>
+    <t>OUT 6_out</t>
+  </si>
+  <si>
+    <t>Cooling fan fro robo fan</t>
+  </si>
+  <si>
+    <t>5V</t>
+  </si>
+  <si>
+    <t>Radiator Fan RGB</t>
+  </si>
+  <si>
+    <t>Clk</t>
+  </si>
+  <si>
+    <t>ESP32 DEV board</t>
+  </si>
+  <si>
+    <t>Power</t>
+  </si>
+  <si>
+    <t>12v</t>
+  </si>
+  <si>
+    <t>0v</t>
+  </si>
+  <si>
+    <t>12v dc</t>
+  </si>
+  <si>
+    <t>100ma</t>
+  </si>
+  <si>
+    <t>Fan Duet 6HC</t>
+  </si>
+  <si>
+    <t>VFUSED</t>
+  </si>
+  <si>
+    <t>V_Fused</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BME senor </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tc, Humidity </t>
+  </si>
+  <si>
+    <t>connection details BME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dauaghter board </t>
+  </si>
+  <si>
+    <t>LED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chamber Lighting </t>
+  </si>
+  <si>
+    <t>POWER IN_Vin</t>
+  </si>
+  <si>
+    <t>POWER IN_gnd</t>
+  </si>
+  <si>
+    <t>https://github.com/Fly3DTeam/Buffer</t>
+  </si>
+  <si>
     <t>OCTOPUS-Pro</t>
   </si>
   <si>
@@ -1137,9 +1429,6 @@
   </si>
   <si>
     <t>Accelerometer</t>
-  </si>
-  <si>
-    <t>5V</t>
   </si>
   <si>
     <t>PD0</t>
@@ -1311,7 +1600,7 @@
   <numFmts count="1">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1365,8 +1654,15 @@
       <name val="Aptos Narrow"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1382,6 +1678,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1637,7 +1951,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1700,12 +2014,61 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="6">
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1741,10 +2104,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1767,8 +2130,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7658100" y="762000"/>
-          <a:ext cx="4572000" cy="3686175"/>
+          <a:off x="7239000" y="933450"/>
+          <a:ext cx="5867400" cy="4724400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1781,6 +2144,293 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>1733550</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E25D0EDA-DADA-AE78-33DE-F93364EC54BA}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{96CFE3AB-D2FE-0A32-99A5-FBD60319F6B1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7924800" y="11249025"/>
+          <a:ext cx="1733550" cy="2819400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>1781175</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B3F5A3E-27CE-9063-1C73-D2CC42157C61}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{E25D0EDA-DADA-AE78-33DE-F93364EC54BA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10182225" y="11468100"/>
+          <a:ext cx="2505075" cy="1371600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>118</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>152</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{66554B50-5150-19EC-233E-116B33368475}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{5B3F5A3E-27CE-9063-1C73-D2CC42157C61}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5715000" y="22945725"/>
+          <a:ext cx="8172450" cy="6496050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>156</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>179</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C9CF096-B745-F827-7F11-C19D9BBE6093}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{283DCDFA-BBFA-2AE8-EB21-95E5D88E15DA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7610475" y="29756100"/>
+          <a:ext cx="4572000" cy="4552950"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>182</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>202</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51D9285C-5302-E85E-8809-12DA5B7E7DA5}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{8C9CF096-B745-F827-7F11-C19D9BBE6093}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7610475" y="34709100"/>
+          <a:ext cx="4572000" cy="3829050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>428625</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CCBFFAFC-F218-03C8-DA65-BA4FC746863F}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{51D9285C-5302-E85E-8809-12DA5B7E7DA5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13192125" y="723900"/>
+          <a:ext cx="6057900" cy="7667625"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1836,8 +2486,8 @@
     <tableColumn id="1" xr3:uid="{397AA321-F1EB-4099-B211-CCE80436FE01}" name="Type"/>
     <tableColumn id="2" xr3:uid="{D9F0DF65-BA4D-4AB2-8B59-B8984C117205}" name="Component"/>
     <tableColumn id="3" xr3:uid="{197E12AC-7214-42A2-8983-84FDA291C15C}" name="Column1"/>
-    <tableColumn id="4" xr3:uid="{A0B25C55-AFFC-44F2-AB5F-261DD1FD5797}" name="Duet IO" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{94120994-05CB-4215-8B7C-BB8702AA86AF}" name="Duet Pin" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{A0B25C55-AFFC-44F2-AB5F-261DD1FD5797}" name="Duet IO" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{94120994-05CB-4215-8B7C-BB8702AA86AF}" name="Duet Pin" dataDxfId="4"/>
     <tableColumn id="6" xr3:uid="{DFBD57EE-063E-450B-9A2C-9A9FEC5FCA4F}" name="AWG"/>
     <tableColumn id="7" xr3:uid="{E30CCDEC-2D31-4686-A595-AC2AFA10DBF2}" name="Wire Length cm"/>
   </tableColumns>
@@ -1846,6 +2496,27 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{0E2427EA-C3E0-423B-81F0-ACED48493E04}" name="Table14" displayName="Table14" ref="A1:I117" totalsRowShown="0">
+  <autoFilter ref="A1:I117" xr:uid="{0E2427EA-C3E0-423B-81F0-ACED48493E04}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H112">
+    <sortCondition ref="D1:D112"/>
+  </sortState>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{E54694D7-637F-4525-940B-9947A6C33E21}" name="Type"/>
+    <tableColumn id="2" xr3:uid="{F2058106-0E68-49C5-96F2-1A9472521EDA}" name="Component"/>
+    <tableColumn id="3" xr3:uid="{6811FB59-B6AB-4B8D-8F0D-F2399B1B4EC9}" name="Column1"/>
+    <tableColumn id="4" xr3:uid="{5A047AAE-8274-42A9-8BA9-2AF076A745B3}" name="Duet IO" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{DAE2F889-2E8B-457B-BE34-A8329C7B28A8}" name="Duet Pin" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{4A956E16-F0C2-4635-89FE-DE225315A99C}" name="AWG"/>
+    <tableColumn id="8" xr3:uid="{D103DE46-86C0-4894-82B5-F95614516B65}" name="mm^2"/>
+    <tableColumn id="7" xr3:uid="{5881A112-4688-453B-BE70-2A489B3C6AAD}" name="Wire Length cm"/>
+    <tableColumn id="9" xr3:uid="{A52C04CC-B13F-43AE-BFCF-54C9498EC421}" name="current 12v"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C51C1D48-58CB-48CF-8FAD-F9796682627A}" name="Table13" displayName="Table13" ref="A1:G211" totalsRowShown="0">
   <autoFilter ref="A1:G211" xr:uid="{C51C1D48-58CB-48CF-8FAD-F9796682627A}"/>
   <tableColumns count="7">
@@ -3940,6 +4611,2517 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19DDB254-C43A-4170-A201-38D01BEC06EB}">
+  <dimension ref="A1:N181"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="44.85546875" customWidth="1"/>
+    <col min="4" max="4" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="28" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="45.75">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2">
+        <v>14</v>
+      </c>
+      <c r="G2">
+        <v>2.5</v>
+      </c>
+      <c r="H2" s="46" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3">
+        <v>14</v>
+      </c>
+      <c r="G3">
+        <v>2.5</v>
+      </c>
+      <c r="H3" s="46" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4">
+        <v>14</v>
+      </c>
+      <c r="G4">
+        <v>2.5</v>
+      </c>
+      <c r="H4" s="46" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5">
+        <v>14</v>
+      </c>
+      <c r="G5">
+        <v>2.5</v>
+      </c>
+      <c r="H5" s="46" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="54" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="54" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="53">
+        <v>24</v>
+      </c>
+      <c r="G6" s="53">
+        <v>0.25</v>
+      </c>
+      <c r="H6" s="55"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="54" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="54" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" s="53">
+        <v>24</v>
+      </c>
+      <c r="G7" s="53">
+        <v>0.25</v>
+      </c>
+      <c r="H7" s="55"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="54" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="54" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" s="53">
+        <v>24</v>
+      </c>
+      <c r="G8" s="53">
+        <v>0.25</v>
+      </c>
+      <c r="H8" s="55"/>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="54" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="54" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="53">
+        <v>24</v>
+      </c>
+      <c r="G9" s="53">
+        <v>0.25</v>
+      </c>
+      <c r="H9" s="55"/>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="56" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="56" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="57" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="56">
+        <v>24</v>
+      </c>
+      <c r="G10" s="56">
+        <v>0.25</v>
+      </c>
+      <c r="H10" s="58"/>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="56" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="56" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="57" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="57" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="56">
+        <v>24</v>
+      </c>
+      <c r="G11" s="56">
+        <v>0.25</v>
+      </c>
+      <c r="H11" s="58"/>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="56" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="56" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="57" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="57" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="56">
+        <v>24</v>
+      </c>
+      <c r="G12" s="56">
+        <v>0.25</v>
+      </c>
+      <c r="H12" s="58"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="56" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="56" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="57" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="57" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" s="56">
+        <v>24</v>
+      </c>
+      <c r="G13" s="56">
+        <v>0.25</v>
+      </c>
+      <c r="H13" s="58"/>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="54" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="53">
+        <v>24</v>
+      </c>
+      <c r="G14" s="53">
+        <v>0.25</v>
+      </c>
+      <c r="H14" s="55"/>
+      <c r="I14" s="47"/>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="54" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" s="53">
+        <v>24</v>
+      </c>
+      <c r="G15" s="53">
+        <v>0.25</v>
+      </c>
+      <c r="H15" s="55"/>
+      <c r="I15" s="47"/>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="54" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" s="53">
+        <v>24</v>
+      </c>
+      <c r="G16" s="53">
+        <v>0.25</v>
+      </c>
+      <c r="H16" s="55"/>
+      <c r="I16" s="47"/>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" s="54" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" s="53">
+        <v>24</v>
+      </c>
+      <c r="G17" s="53">
+        <v>0.25</v>
+      </c>
+      <c r="H17" s="55"/>
+      <c r="I17" s="47"/>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="56" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="56" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="57" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" s="56">
+        <v>24</v>
+      </c>
+      <c r="G18" s="56">
+        <v>0.25</v>
+      </c>
+      <c r="H18" s="58"/>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="56" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="56" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="57" t="s">
+        <v>39</v>
+      </c>
+      <c r="E19" s="57" t="s">
+        <v>29</v>
+      </c>
+      <c r="F19" s="56">
+        <v>24</v>
+      </c>
+      <c r="G19" s="56">
+        <v>0.25</v>
+      </c>
+      <c r="H19" s="58"/>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="56" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="56" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" s="57" t="s">
+        <v>39</v>
+      </c>
+      <c r="E20" s="57" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20" s="56">
+        <v>24</v>
+      </c>
+      <c r="G20" s="56">
+        <v>0.25</v>
+      </c>
+      <c r="H20" s="58"/>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="56" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="56" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="57" t="s">
+        <v>39</v>
+      </c>
+      <c r="E21" s="57" t="s">
+        <v>33</v>
+      </c>
+      <c r="F21" s="56">
+        <v>24</v>
+      </c>
+      <c r="G21" s="56">
+        <v>0.25</v>
+      </c>
+      <c r="H21" s="58"/>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="D22" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="E22" s="54" t="s">
+        <v>27</v>
+      </c>
+      <c r="F22" s="53">
+        <v>24</v>
+      </c>
+      <c r="G22" s="53">
+        <v>0.25</v>
+      </c>
+      <c r="H22" s="55"/>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="E23" s="54" t="s">
+        <v>29</v>
+      </c>
+      <c r="F23" s="53">
+        <v>24</v>
+      </c>
+      <c r="G23" s="53">
+        <v>0.25</v>
+      </c>
+      <c r="H23" s="55"/>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="D24" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="E24" s="54" t="s">
+        <v>31</v>
+      </c>
+      <c r="F24" s="53">
+        <v>24</v>
+      </c>
+      <c r="G24" s="53">
+        <v>0.25</v>
+      </c>
+      <c r="H24" s="55"/>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="E25" s="54" t="s">
+        <v>33</v>
+      </c>
+      <c r="F25" s="53">
+        <v>24</v>
+      </c>
+      <c r="G25" s="53">
+        <v>0.25</v>
+      </c>
+      <c r="H25" s="55"/>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" s="56" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" s="56" t="s">
+        <v>25</v>
+      </c>
+      <c r="D26" s="57" t="s">
+        <v>43</v>
+      </c>
+      <c r="E26" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="F26" s="56">
+        <v>24</v>
+      </c>
+      <c r="G26" s="56">
+        <v>0.25</v>
+      </c>
+      <c r="H26" s="58"/>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" s="56" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" s="56" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" s="57" t="s">
+        <v>43</v>
+      </c>
+      <c r="E27" s="57" t="s">
+        <v>29</v>
+      </c>
+      <c r="F27" s="56">
+        <v>24</v>
+      </c>
+      <c r="G27" s="56">
+        <v>0.25</v>
+      </c>
+      <c r="H27" s="58"/>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" s="56" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" s="56" t="s">
+        <v>30</v>
+      </c>
+      <c r="D28" s="57" t="s">
+        <v>43</v>
+      </c>
+      <c r="E28" s="57" t="s">
+        <v>31</v>
+      </c>
+      <c r="F28" s="56">
+        <v>24</v>
+      </c>
+      <c r="G28" s="56">
+        <v>0.25</v>
+      </c>
+      <c r="H28" s="58"/>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" s="56" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" s="56" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29" s="57" t="s">
+        <v>43</v>
+      </c>
+      <c r="E29" s="57" t="s">
+        <v>33</v>
+      </c>
+      <c r="F29" s="56">
+        <v>24</v>
+      </c>
+      <c r="G29" s="56">
+        <v>0.25</v>
+      </c>
+      <c r="H29" s="58"/>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="53"/>
+      <c r="B30" s="53"/>
+      <c r="C30" s="53"/>
+      <c r="D30" s="54" t="s">
+        <v>137</v>
+      </c>
+      <c r="E30" s="54"/>
+      <c r="F30" s="53"/>
+      <c r="G30" s="53"/>
+      <c r="H30" s="55"/>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="B31" s="53" t="s">
+        <v>139</v>
+      </c>
+      <c r="C31" s="53"/>
+      <c r="D31" s="54" t="s">
+        <v>140</v>
+      </c>
+      <c r="E31" s="54"/>
+      <c r="F31" s="53"/>
+      <c r="G31" s="53"/>
+      <c r="H31" s="55"/>
+      <c r="I31" s="1"/>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="53"/>
+      <c r="B32" s="53"/>
+      <c r="C32" s="53"/>
+      <c r="D32" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="E32" s="54"/>
+      <c r="F32" s="53"/>
+      <c r="G32" s="53"/>
+      <c r="H32" s="55"/>
+      <c r="I32" s="1"/>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="B33" s="53" t="s">
+        <v>139</v>
+      </c>
+      <c r="C33" s="53"/>
+      <c r="D33" s="54" t="s">
+        <v>142</v>
+      </c>
+      <c r="E33" s="54"/>
+      <c r="F33" s="53"/>
+      <c r="G33" s="53"/>
+      <c r="H33" s="55"/>
+      <c r="I33" s="1"/>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="53"/>
+      <c r="B34" s="53"/>
+      <c r="C34" s="53"/>
+      <c r="D34" s="54" t="s">
+        <v>143</v>
+      </c>
+      <c r="E34" s="54"/>
+      <c r="F34" s="53"/>
+      <c r="G34" s="53"/>
+      <c r="H34" s="55"/>
+      <c r="I34" s="1"/>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="56"/>
+      <c r="B35" s="56"/>
+      <c r="C35" s="56"/>
+      <c r="D35" s="57" t="s">
+        <v>144</v>
+      </c>
+      <c r="E35" s="57"/>
+      <c r="F35" s="56"/>
+      <c r="G35" s="56"/>
+      <c r="H35" s="58"/>
+      <c r="I35" s="1"/>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="B36" s="56" t="s">
+        <v>51</v>
+      </c>
+      <c r="C36" s="56"/>
+      <c r="D36" s="57" t="s">
+        <v>145</v>
+      </c>
+      <c r="E36" s="57"/>
+      <c r="F36" s="56">
+        <v>24</v>
+      </c>
+      <c r="G36" s="56">
+        <v>0.25</v>
+      </c>
+      <c r="H36" s="58" t="s">
+        <v>133</v>
+      </c>
+      <c r="I36" s="48"/>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="56" t="s">
+        <v>51</v>
+      </c>
+      <c r="C37" s="56"/>
+      <c r="D37" s="57" t="s">
+        <v>146</v>
+      </c>
+      <c r="E37" s="57"/>
+      <c r="F37" s="56">
+        <v>24</v>
+      </c>
+      <c r="G37" s="56">
+        <v>0.25</v>
+      </c>
+      <c r="H37" s="58" t="s">
+        <v>133</v>
+      </c>
+      <c r="I37" s="48"/>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="56"/>
+      <c r="B38" s="56"/>
+      <c r="C38" s="56"/>
+      <c r="D38" s="57" t="s">
+        <v>147</v>
+      </c>
+      <c r="E38" s="57"/>
+      <c r="F38" s="56"/>
+      <c r="G38" s="56"/>
+      <c r="H38" s="58"/>
+      <c r="I38" s="1"/>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="56"/>
+      <c r="B39" s="56"/>
+      <c r="C39" s="56"/>
+      <c r="D39" s="57" t="s">
+        <v>148</v>
+      </c>
+      <c r="E39" s="57"/>
+      <c r="F39" s="56"/>
+      <c r="G39" s="56"/>
+      <c r="H39" s="58"/>
+      <c r="I39" s="1"/>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="53"/>
+      <c r="B40" s="53"/>
+      <c r="C40" s="53"/>
+      <c r="D40" s="54" t="s">
+        <v>149</v>
+      </c>
+      <c r="E40" s="54"/>
+      <c r="F40" s="53"/>
+      <c r="G40" s="53"/>
+      <c r="H40" s="55"/>
+      <c r="I40" s="1"/>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="53" t="s">
+        <v>150</v>
+      </c>
+      <c r="C41" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="D41" s="54" t="s">
+        <v>151</v>
+      </c>
+      <c r="E41" s="54" t="s">
+        <v>55</v>
+      </c>
+      <c r="F41" s="53">
+        <v>24</v>
+      </c>
+      <c r="G41" s="53">
+        <v>0.25</v>
+      </c>
+      <c r="H41" s="55" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42" s="53" t="s">
+        <v>150</v>
+      </c>
+      <c r="C42" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="54" t="s">
+        <v>152</v>
+      </c>
+      <c r="E42" s="54" t="s">
+        <v>11</v>
+      </c>
+      <c r="F42" s="53">
+        <v>24</v>
+      </c>
+      <c r="G42" s="53">
+        <v>0.25</v>
+      </c>
+      <c r="H42" s="55" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" s="53" t="s">
+        <v>153</v>
+      </c>
+      <c r="B43" s="53" t="s">
+        <v>139</v>
+      </c>
+      <c r="C43" s="53"/>
+      <c r="D43" s="54" t="s">
+        <v>154</v>
+      </c>
+      <c r="E43" s="54"/>
+      <c r="F43" s="53"/>
+      <c r="G43" s="53"/>
+      <c r="H43" s="55"/>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" s="53"/>
+      <c r="B44" s="53"/>
+      <c r="C44" s="53"/>
+      <c r="D44" s="54" t="s">
+        <v>155</v>
+      </c>
+      <c r="E44" s="54"/>
+      <c r="F44" s="53"/>
+      <c r="G44" s="53"/>
+      <c r="H44" s="55"/>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" s="56"/>
+      <c r="B45" s="56"/>
+      <c r="C45" s="56"/>
+      <c r="D45" s="57" t="s">
+        <v>156</v>
+      </c>
+      <c r="E45" s="57"/>
+      <c r="F45" s="56"/>
+      <c r="G45" s="56"/>
+      <c r="H45" s="58"/>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46" s="56" t="s">
+        <v>56</v>
+      </c>
+      <c r="C46" s="56" t="s">
+        <v>46</v>
+      </c>
+      <c r="D46" s="57" t="s">
+        <v>157</v>
+      </c>
+      <c r="E46" s="57" t="s">
+        <v>48</v>
+      </c>
+      <c r="F46" s="56">
+        <v>24</v>
+      </c>
+      <c r="G46" s="56">
+        <v>0.25</v>
+      </c>
+      <c r="H46" s="58" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="B47" s="56" t="s">
+        <v>56</v>
+      </c>
+      <c r="C47" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="57" t="s">
+        <v>158</v>
+      </c>
+      <c r="E47" s="57" t="s">
+        <v>11</v>
+      </c>
+      <c r="F47" s="56">
+        <v>24</v>
+      </c>
+      <c r="G47" s="56">
+        <v>0.25</v>
+      </c>
+      <c r="H47" s="58" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" s="56"/>
+      <c r="B48" s="56"/>
+      <c r="C48" s="56"/>
+      <c r="D48" s="57" t="s">
+        <v>159</v>
+      </c>
+      <c r="E48" s="57"/>
+      <c r="F48" s="56"/>
+      <c r="G48" s="56"/>
+      <c r="H48" s="58"/>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" s="56"/>
+      <c r="B49" s="56"/>
+      <c r="C49" s="56"/>
+      <c r="D49" s="57" t="s">
+        <v>160</v>
+      </c>
+      <c r="E49" s="57"/>
+      <c r="F49" s="56"/>
+      <c r="G49" s="56"/>
+      <c r="H49" s="58"/>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" s="53"/>
+      <c r="B50" s="53"/>
+      <c r="C50" s="53"/>
+      <c r="D50" s="54" t="s">
+        <v>161</v>
+      </c>
+      <c r="E50" s="54"/>
+      <c r="F50" s="53"/>
+      <c r="G50" s="53"/>
+      <c r="H50" s="55"/>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="B51" s="53" t="s">
+        <v>162</v>
+      </c>
+      <c r="C51" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="D51" s="54" t="s">
+        <v>163</v>
+      </c>
+      <c r="E51" s="54" t="s">
+        <v>164</v>
+      </c>
+      <c r="F51" s="53">
+        <v>24</v>
+      </c>
+      <c r="G51" s="53">
+        <v>0.25</v>
+      </c>
+      <c r="H51" s="55" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="B52" s="53" t="s">
+        <v>162</v>
+      </c>
+      <c r="C52" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" s="54" t="s">
+        <v>165</v>
+      </c>
+      <c r="E52" s="54" t="s">
+        <v>11</v>
+      </c>
+      <c r="F52" s="53">
+        <v>24</v>
+      </c>
+      <c r="G52" s="53">
+        <v>0.25</v>
+      </c>
+      <c r="H52" s="55" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" s="53"/>
+      <c r="B53" s="53"/>
+      <c r="C53" s="53"/>
+      <c r="D53" s="54" t="s">
+        <v>166</v>
+      </c>
+      <c r="E53" s="54"/>
+      <c r="F53" s="53"/>
+      <c r="G53" s="53"/>
+      <c r="H53" s="55"/>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" s="53"/>
+      <c r="B54" s="53"/>
+      <c r="C54" s="53"/>
+      <c r="D54" s="54" t="s">
+        <v>167</v>
+      </c>
+      <c r="E54" s="54"/>
+      <c r="F54" s="53"/>
+      <c r="G54" s="53"/>
+      <c r="H54" s="55"/>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="B55" s="56" t="s">
+        <v>60</v>
+      </c>
+      <c r="C55" s="56" t="s">
+        <v>61</v>
+      </c>
+      <c r="D55" s="57" t="s">
+        <v>168</v>
+      </c>
+      <c r="E55" s="57" t="s">
+        <v>61</v>
+      </c>
+      <c r="F55" s="56">
+        <v>24</v>
+      </c>
+      <c r="G55" s="56">
+        <v>0.25</v>
+      </c>
+      <c r="H55" s="58" t="s">
+        <v>133</v>
+      </c>
+      <c r="I55" s="49"/>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="A56" s="56"/>
+      <c r="B56" s="56"/>
+      <c r="C56" s="56"/>
+      <c r="D56" s="57" t="s">
+        <v>169</v>
+      </c>
+      <c r="E56" s="57"/>
+      <c r="F56" s="56"/>
+      <c r="G56" s="56"/>
+      <c r="H56" s="58"/>
+      <c r="I56" s="49"/>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="A57" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="B57" s="56" t="s">
+        <v>60</v>
+      </c>
+      <c r="C57" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="D57" s="57" t="s">
+        <v>170</v>
+      </c>
+      <c r="E57" s="57" t="s">
+        <v>11</v>
+      </c>
+      <c r="F57" s="56">
+        <v>24</v>
+      </c>
+      <c r="G57" s="56">
+        <v>0.25</v>
+      </c>
+      <c r="H57" s="58" t="s">
+        <v>133</v>
+      </c>
+      <c r="I57" s="49"/>
+    </row>
+    <row r="58" spans="1:9">
+      <c r="A58" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="B58" s="56" t="s">
+        <v>60</v>
+      </c>
+      <c r="C58" s="56" t="s">
+        <v>63</v>
+      </c>
+      <c r="D58" s="57" t="s">
+        <v>171</v>
+      </c>
+      <c r="E58" s="57" t="s">
+        <v>64</v>
+      </c>
+      <c r="F58" s="56">
+        <v>24</v>
+      </c>
+      <c r="G58" s="56">
+        <v>0.25</v>
+      </c>
+      <c r="H58" s="58" t="s">
+        <v>133</v>
+      </c>
+      <c r="I58" s="49"/>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="A59" s="56"/>
+      <c r="B59" s="56"/>
+      <c r="C59" s="56"/>
+      <c r="D59" s="57" t="s">
+        <v>172</v>
+      </c>
+      <c r="E59" s="57"/>
+      <c r="F59" s="56"/>
+      <c r="G59" s="56"/>
+      <c r="H59" s="58"/>
+      <c r="I59" s="49"/>
+    </row>
+    <row r="60" spans="1:9">
+      <c r="A60" s="53"/>
+      <c r="B60" s="53"/>
+      <c r="C60" s="53"/>
+      <c r="D60" s="54" t="s">
+        <v>173</v>
+      </c>
+      <c r="E60" s="54"/>
+      <c r="F60" s="53"/>
+      <c r="G60" s="53"/>
+      <c r="H60" s="55"/>
+      <c r="I60" s="49"/>
+    </row>
+    <row r="61" spans="1:9">
+      <c r="A61" s="53"/>
+      <c r="B61" s="53"/>
+      <c r="C61" s="53"/>
+      <c r="D61" s="54" t="s">
+        <v>174</v>
+      </c>
+      <c r="E61" s="54"/>
+      <c r="F61" s="53"/>
+      <c r="G61" s="53"/>
+      <c r="H61" s="55"/>
+    </row>
+    <row r="62" spans="1:9">
+      <c r="A62" s="53"/>
+      <c r="B62" s="53"/>
+      <c r="C62" s="53"/>
+      <c r="D62" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="E62" s="54"/>
+      <c r="F62" s="53"/>
+      <c r="G62" s="53"/>
+      <c r="H62" s="55"/>
+    </row>
+    <row r="63" spans="1:9">
+      <c r="A63" s="53"/>
+      <c r="B63" s="53"/>
+      <c r="C63" s="53"/>
+      <c r="D63" s="54" t="s">
+        <v>176</v>
+      </c>
+      <c r="E63" s="54"/>
+      <c r="F63" s="53"/>
+      <c r="G63" s="53"/>
+      <c r="H63" s="55"/>
+    </row>
+    <row r="64" spans="1:9">
+      <c r="A64" s="53"/>
+      <c r="B64" s="53"/>
+      <c r="C64" s="53"/>
+      <c r="D64" s="54" t="s">
+        <v>177</v>
+      </c>
+      <c r="E64" s="54"/>
+      <c r="F64" s="53"/>
+      <c r="G64" s="53"/>
+      <c r="H64" s="55"/>
+    </row>
+    <row r="65" spans="1:9">
+      <c r="A65" s="56"/>
+      <c r="B65" s="56"/>
+      <c r="C65" s="56"/>
+      <c r="D65" s="57" t="s">
+        <v>178</v>
+      </c>
+      <c r="E65" s="57"/>
+      <c r="F65" s="56"/>
+      <c r="G65" s="56"/>
+      <c r="H65" s="58"/>
+    </row>
+    <row r="66" spans="1:9">
+      <c r="A66" s="56"/>
+      <c r="B66" s="56"/>
+      <c r="C66" s="56"/>
+      <c r="D66" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="E66" s="57"/>
+      <c r="F66" s="56"/>
+      <c r="G66" s="56"/>
+      <c r="H66" s="58"/>
+    </row>
+    <row r="67" spans="1:9">
+      <c r="A67" s="56"/>
+      <c r="B67" s="56"/>
+      <c r="C67" s="56"/>
+      <c r="D67" s="57" t="s">
+        <v>180</v>
+      </c>
+      <c r="E67" s="57"/>
+      <c r="F67" s="56"/>
+      <c r="G67" s="56"/>
+      <c r="H67" s="58"/>
+    </row>
+    <row r="68" spans="1:9">
+      <c r="A68" s="56"/>
+      <c r="B68" s="56"/>
+      <c r="C68" s="56"/>
+      <c r="D68" s="57" t="s">
+        <v>181</v>
+      </c>
+      <c r="E68" s="57"/>
+      <c r="F68" s="56"/>
+      <c r="G68" s="56"/>
+      <c r="H68" s="58"/>
+    </row>
+    <row r="69" spans="1:9">
+      <c r="A69" s="56"/>
+      <c r="B69" s="56"/>
+      <c r="C69" s="56"/>
+      <c r="D69" s="57" t="s">
+        <v>182</v>
+      </c>
+      <c r="E69" s="57"/>
+      <c r="F69" s="56"/>
+      <c r="G69" s="56"/>
+      <c r="H69" s="58"/>
+    </row>
+    <row r="70" spans="1:9" ht="18" customHeight="1">
+      <c r="A70" s="53" t="s">
+        <v>183</v>
+      </c>
+      <c r="B70" s="66" t="s">
+        <v>184</v>
+      </c>
+      <c r="C70" s="53" t="s">
+        <v>69</v>
+      </c>
+      <c r="D70" s="54" t="s">
+        <v>70</v>
+      </c>
+      <c r="E70" s="54" t="s">
+        <v>13</v>
+      </c>
+      <c r="F70" s="53">
+        <v>16</v>
+      </c>
+      <c r="G70" s="53">
+        <v>1.5</v>
+      </c>
+      <c r="H70" s="55" t="s">
+        <v>133</v>
+      </c>
+      <c r="I70" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A71" s="53" t="s">
+        <v>183</v>
+      </c>
+      <c r="B71" s="66" t="s">
+        <v>184</v>
+      </c>
+      <c r="C71" s="53" t="s">
+        <v>72</v>
+      </c>
+      <c r="D71" s="54" t="s">
+        <v>70</v>
+      </c>
+      <c r="E71" s="54" t="s">
+        <v>73</v>
+      </c>
+      <c r="F71" s="53">
+        <v>16</v>
+      </c>
+      <c r="G71" s="53">
+        <v>1.5</v>
+      </c>
+      <c r="H71" s="55" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
+      <c r="A72" s="56" t="s">
+        <v>74</v>
+      </c>
+      <c r="B72" s="56" t="s">
+        <v>75</v>
+      </c>
+      <c r="C72" s="56" t="s">
+        <v>69</v>
+      </c>
+      <c r="D72" s="57" t="s">
+        <v>76</v>
+      </c>
+      <c r="E72" s="57" t="s">
+        <v>77</v>
+      </c>
+      <c r="F72" s="56">
+        <v>16</v>
+      </c>
+      <c r="G72" s="56">
+        <v>1.5</v>
+      </c>
+      <c r="H72" s="58" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9">
+      <c r="A73" s="56" t="s">
+        <v>74</v>
+      </c>
+      <c r="B73" s="56" t="s">
+        <v>75</v>
+      </c>
+      <c r="C73" s="56" t="s">
+        <v>72</v>
+      </c>
+      <c r="D73" s="57" t="s">
+        <v>76</v>
+      </c>
+      <c r="E73" s="57" t="s">
+        <v>78</v>
+      </c>
+      <c r="F73" s="56">
+        <v>16</v>
+      </c>
+      <c r="G73" s="56">
+        <v>1.5</v>
+      </c>
+      <c r="H73" s="58" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
+      <c r="A74" s="53" t="s">
+        <v>67</v>
+      </c>
+      <c r="B74" s="53" t="s">
+        <v>186</v>
+      </c>
+      <c r="C74" s="53" t="s">
+        <v>69</v>
+      </c>
+      <c r="D74" s="54" t="s">
+        <v>80</v>
+      </c>
+      <c r="E74" s="54" t="s">
+        <v>77</v>
+      </c>
+      <c r="F74" s="53">
+        <v>24</v>
+      </c>
+      <c r="G74" s="53">
+        <v>0.25</v>
+      </c>
+      <c r="H74" s="55" t="s">
+        <v>133</v>
+      </c>
+      <c r="I74" s="47"/>
+    </row>
+    <row r="75" spans="1:9">
+      <c r="A75" s="53" t="s">
+        <v>67</v>
+      </c>
+      <c r="B75" s="53" t="s">
+        <v>186</v>
+      </c>
+      <c r="C75" s="53" t="s">
+        <v>72</v>
+      </c>
+      <c r="D75" s="54" t="s">
+        <v>80</v>
+      </c>
+      <c r="E75" s="54" t="s">
+        <v>81</v>
+      </c>
+      <c r="F75" s="53">
+        <v>24</v>
+      </c>
+      <c r="G75" s="53">
+        <v>0.25</v>
+      </c>
+      <c r="H75" s="55" t="s">
+        <v>133</v>
+      </c>
+      <c r="I75" s="47"/>
+    </row>
+    <row r="76" spans="1:9">
+      <c r="A76" s="56" t="s">
+        <v>67</v>
+      </c>
+      <c r="B76" s="56" t="s">
+        <v>187</v>
+      </c>
+      <c r="C76" s="56" t="s">
+        <v>69</v>
+      </c>
+      <c r="D76" s="57" t="s">
+        <v>83</v>
+      </c>
+      <c r="E76" s="57" t="s">
+        <v>77</v>
+      </c>
+      <c r="F76" s="56">
+        <v>24</v>
+      </c>
+      <c r="G76" s="56">
+        <v>0.25</v>
+      </c>
+      <c r="H76" s="58" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9">
+      <c r="A77" s="56" t="s">
+        <v>67</v>
+      </c>
+      <c r="B77" s="56" t="s">
+        <v>187</v>
+      </c>
+      <c r="C77" s="56" t="s">
+        <v>72</v>
+      </c>
+      <c r="D77" s="57" t="s">
+        <v>83</v>
+      </c>
+      <c r="E77" s="57" t="s">
+        <v>84</v>
+      </c>
+      <c r="F77" s="56">
+        <v>24</v>
+      </c>
+      <c r="G77" s="56">
+        <v>0.25</v>
+      </c>
+      <c r="H77" s="58" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9">
+      <c r="A78" s="53"/>
+      <c r="B78" s="53"/>
+      <c r="C78" s="53"/>
+      <c r="D78" s="54" t="s">
+        <v>188</v>
+      </c>
+      <c r="E78" s="54"/>
+      <c r="F78" s="53"/>
+      <c r="G78" s="53"/>
+      <c r="H78" s="55"/>
+    </row>
+    <row r="79" spans="1:9">
+      <c r="A79" s="53" t="s">
+        <v>67</v>
+      </c>
+      <c r="B79" s="53" t="s">
+        <v>189</v>
+      </c>
+      <c r="C79" s="53" t="s">
+        <v>69</v>
+      </c>
+      <c r="D79" s="54" t="s">
+        <v>190</v>
+      </c>
+      <c r="E79" s="54" t="s">
+        <v>88</v>
+      </c>
+      <c r="F79" s="53"/>
+      <c r="G79" s="53"/>
+      <c r="H79" s="55" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
+      <c r="A80" s="53"/>
+      <c r="B80" s="53"/>
+      <c r="C80" s="53"/>
+      <c r="D80" s="54" t="s">
+        <v>191</v>
+      </c>
+      <c r="E80" s="54"/>
+      <c r="F80" s="53"/>
+      <c r="G80" s="53"/>
+      <c r="H80" s="53"/>
+    </row>
+    <row r="81" spans="1:14">
+      <c r="A81" s="53" t="s">
+        <v>67</v>
+      </c>
+      <c r="B81" s="53" t="s">
+        <v>192</v>
+      </c>
+      <c r="C81" s="53" t="s">
+        <v>72</v>
+      </c>
+      <c r="D81" s="54" t="s">
+        <v>193</v>
+      </c>
+      <c r="E81" s="54" t="s">
+        <v>89</v>
+      </c>
+      <c r="F81" s="53"/>
+      <c r="G81" s="53"/>
+      <c r="H81" s="55" t="s">
+        <v>133</v>
+      </c>
+      <c r="N81" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14">
+      <c r="A82" s="56" t="s">
+        <v>90</v>
+      </c>
+      <c r="B82" s="56" t="s">
+        <v>91</v>
+      </c>
+      <c r="C82" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="D82" s="57" t="s">
+        <v>195</v>
+      </c>
+      <c r="E82" s="57" t="s">
+        <v>11</v>
+      </c>
+      <c r="F82" s="56"/>
+      <c r="G82" s="56"/>
+      <c r="H82" s="58"/>
+    </row>
+    <row r="83" spans="1:14">
+      <c r="A83" s="56" t="s">
+        <v>90</v>
+      </c>
+      <c r="B83" s="56" t="s">
+        <v>91</v>
+      </c>
+      <c r="C83" s="56" t="s">
+        <v>196</v>
+      </c>
+      <c r="D83" s="57" t="s">
+        <v>197</v>
+      </c>
+      <c r="E83" s="57" t="s">
+        <v>88</v>
+      </c>
+      <c r="F83" s="56"/>
+      <c r="G83" s="56"/>
+      <c r="H83" s="58"/>
+    </row>
+    <row r="84" spans="1:14">
+      <c r="A84" s="59" t="s">
+        <v>93</v>
+      </c>
+      <c r="B84" s="59" t="s">
+        <v>94</v>
+      </c>
+      <c r="C84" s="59" t="s">
+        <v>95</v>
+      </c>
+      <c r="D84" s="57" t="s">
+        <v>198</v>
+      </c>
+      <c r="E84" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="F84" s="56"/>
+      <c r="G84" s="56"/>
+      <c r="H84" s="58" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14">
+      <c r="A85" s="59"/>
+      <c r="B85" s="56"/>
+      <c r="C85" s="56"/>
+      <c r="D85" s="57" t="s">
+        <v>199</v>
+      </c>
+      <c r="E85" s="57" t="s">
+        <v>98</v>
+      </c>
+      <c r="F85" s="56"/>
+      <c r="G85" s="56"/>
+      <c r="H85" s="58" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14">
+      <c r="A86" s="53" t="s">
+        <v>200</v>
+      </c>
+      <c r="B86" s="61" t="s">
+        <v>201</v>
+      </c>
+      <c r="C86" s="53" t="s">
+        <v>72</v>
+      </c>
+      <c r="D86" s="54" t="s">
+        <v>202</v>
+      </c>
+      <c r="E86" s="54" t="s">
+        <v>11</v>
+      </c>
+      <c r="F86" s="53">
+        <v>24</v>
+      </c>
+      <c r="G86" s="53">
+        <v>0.25</v>
+      </c>
+      <c r="H86" s="55" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14">
+      <c r="A87" s="53"/>
+      <c r="B87" s="53"/>
+      <c r="C87" s="61"/>
+      <c r="D87" s="63" t="s">
+        <v>203</v>
+      </c>
+      <c r="E87" s="63" t="s">
+        <v>88</v>
+      </c>
+      <c r="F87" s="61">
+        <v>24</v>
+      </c>
+      <c r="G87" s="53">
+        <v>0.25</v>
+      </c>
+      <c r="H87" s="55" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14">
+      <c r="A88" s="62" t="s">
+        <v>200</v>
+      </c>
+      <c r="B88" s="61" t="s">
+        <v>101</v>
+      </c>
+      <c r="C88" s="61" t="s">
+        <v>95</v>
+      </c>
+      <c r="D88" s="54" t="s">
+        <v>204</v>
+      </c>
+      <c r="E88" s="63" t="s">
+        <v>102</v>
+      </c>
+      <c r="F88" s="61"/>
+      <c r="G88" s="53"/>
+      <c r="H88" s="55" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14">
+      <c r="A89" s="53" t="s">
+        <v>200</v>
+      </c>
+      <c r="B89" s="61" t="s">
+        <v>201</v>
+      </c>
+      <c r="C89" s="61"/>
+      <c r="D89" s="54" t="s">
+        <v>205</v>
+      </c>
+      <c r="E89" s="63" t="s">
+        <v>103</v>
+      </c>
+      <c r="F89" s="61"/>
+      <c r="G89" s="53"/>
+      <c r="H89" s="55" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14">
+      <c r="A90" s="64" t="s">
+        <v>85</v>
+      </c>
+      <c r="B90" s="56" t="s">
+        <v>104</v>
+      </c>
+      <c r="C90" s="56" t="s">
+        <v>69</v>
+      </c>
+      <c r="D90" s="57" t="s">
+        <v>105</v>
+      </c>
+      <c r="E90" s="57" t="s">
+        <v>106</v>
+      </c>
+      <c r="F90" s="56">
+        <v>24</v>
+      </c>
+      <c r="G90" s="56">
+        <v>0.25</v>
+      </c>
+      <c r="H90" s="58" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14">
+      <c r="A91" s="64" t="s">
+        <v>85</v>
+      </c>
+      <c r="B91" s="56" t="s">
+        <v>104</v>
+      </c>
+      <c r="C91" s="56" t="s">
+        <v>72</v>
+      </c>
+      <c r="D91" s="57" t="s">
+        <v>105</v>
+      </c>
+      <c r="E91" s="57" t="s">
+        <v>107</v>
+      </c>
+      <c r="F91" s="56">
+        <v>24</v>
+      </c>
+      <c r="G91" s="56">
+        <v>0.25</v>
+      </c>
+      <c r="H91" s="58" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14">
+      <c r="A92" s="62" t="s">
+        <v>85</v>
+      </c>
+      <c r="B92" s="53" t="s">
+        <v>108</v>
+      </c>
+      <c r="C92" s="53" t="s">
+        <v>69</v>
+      </c>
+      <c r="D92" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="E92" s="54" t="s">
+        <v>106</v>
+      </c>
+      <c r="F92" s="53">
+        <v>24</v>
+      </c>
+      <c r="G92" s="53">
+        <v>0.25</v>
+      </c>
+      <c r="H92" s="55" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14">
+      <c r="A93" s="61" t="s">
+        <v>85</v>
+      </c>
+      <c r="B93" s="61" t="s">
+        <v>108</v>
+      </c>
+      <c r="C93" s="61" t="s">
+        <v>72</v>
+      </c>
+      <c r="D93" s="63" t="s">
+        <v>109</v>
+      </c>
+      <c r="E93" s="63" t="s">
+        <v>110</v>
+      </c>
+      <c r="F93" s="61">
+        <v>24</v>
+      </c>
+      <c r="G93" s="61">
+        <v>0.25</v>
+      </c>
+      <c r="H93" s="65" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14">
+      <c r="A94" s="59" t="s">
+        <v>85</v>
+      </c>
+      <c r="B94" s="56" t="s">
+        <v>206</v>
+      </c>
+      <c r="C94" s="56"/>
+      <c r="D94" s="57" t="s">
+        <v>112</v>
+      </c>
+      <c r="E94" s="57" t="s">
+        <v>106</v>
+      </c>
+      <c r="F94" s="56">
+        <v>24</v>
+      </c>
+      <c r="G94" s="56">
+        <v>0.25</v>
+      </c>
+      <c r="H94" s="58" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14">
+      <c r="A95" s="59" t="s">
+        <v>85</v>
+      </c>
+      <c r="B95" s="56" t="s">
+        <v>206</v>
+      </c>
+      <c r="C95" s="56"/>
+      <c r="D95" s="57" t="s">
+        <v>112</v>
+      </c>
+      <c r="E95" s="57" t="s">
+        <v>113</v>
+      </c>
+      <c r="F95" s="56">
+        <v>24</v>
+      </c>
+      <c r="G95" s="56">
+        <v>0.25</v>
+      </c>
+      <c r="H95" s="58" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14">
+      <c r="A96" s="53"/>
+      <c r="B96" s="53"/>
+      <c r="C96" s="53"/>
+      <c r="D96" s="54" t="s">
+        <v>19</v>
+      </c>
+      <c r="E96" s="54" t="s">
+        <v>207</v>
+      </c>
+      <c r="F96" s="53"/>
+      <c r="G96" s="53"/>
+      <c r="H96" s="53"/>
+      <c r="I96" s="53"/>
+    </row>
+    <row r="97" spans="1:9">
+      <c r="A97" s="53" t="s">
+        <v>200</v>
+      </c>
+      <c r="B97" s="53" t="s">
+        <v>208</v>
+      </c>
+      <c r="C97" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="D97" s="54" t="s">
+        <v>19</v>
+      </c>
+      <c r="E97" s="54" t="s">
+        <v>22</v>
+      </c>
+      <c r="F97" s="53">
+        <v>24</v>
+      </c>
+      <c r="G97" s="53">
+        <v>0.25</v>
+      </c>
+      <c r="H97" s="55" t="s">
+        <v>133</v>
+      </c>
+      <c r="I97" s="53"/>
+    </row>
+    <row r="98" spans="1:9">
+      <c r="A98" s="53"/>
+      <c r="B98" s="53"/>
+      <c r="C98" s="53"/>
+      <c r="D98" s="54" t="s">
+        <v>19</v>
+      </c>
+      <c r="E98" s="54" t="s">
+        <v>209</v>
+      </c>
+      <c r="F98" s="53"/>
+      <c r="G98" s="53"/>
+      <c r="H98" s="53"/>
+      <c r="I98" s="53"/>
+    </row>
+    <row r="99" spans="1:9">
+      <c r="A99" s="53" t="s">
+        <v>200</v>
+      </c>
+      <c r="B99" s="53" t="s">
+        <v>208</v>
+      </c>
+      <c r="C99" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D99" s="54" t="s">
+        <v>19</v>
+      </c>
+      <c r="E99" s="54" t="s">
+        <v>11</v>
+      </c>
+      <c r="F99" s="53">
+        <v>24</v>
+      </c>
+      <c r="G99" s="53">
+        <v>0.25</v>
+      </c>
+      <c r="H99" s="55" t="s">
+        <v>133</v>
+      </c>
+      <c r="I99" s="53"/>
+    </row>
+    <row r="100" spans="1:9">
+      <c r="A100" s="56" t="s">
+        <v>59</v>
+      </c>
+      <c r="B100" s="56" t="s">
+        <v>210</v>
+      </c>
+      <c r="C100" s="56" t="s">
+        <v>12</v>
+      </c>
+      <c r="D100" s="57" t="s">
+        <v>211</v>
+      </c>
+      <c r="E100" s="57" t="s">
+        <v>212</v>
+      </c>
+      <c r="F100" s="56"/>
+      <c r="G100" s="56"/>
+      <c r="H100" s="58"/>
+      <c r="I100" s="56"/>
+    </row>
+    <row r="101" spans="1:9">
+      <c r="A101" s="56" t="s">
+        <v>59</v>
+      </c>
+      <c r="B101" s="56" t="s">
+        <v>210</v>
+      </c>
+      <c r="C101" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="D101" s="57" t="s">
+        <v>211</v>
+      </c>
+      <c r="E101" s="57" t="s">
+        <v>213</v>
+      </c>
+      <c r="F101" s="56"/>
+      <c r="G101" s="56"/>
+      <c r="H101" s="58"/>
+      <c r="I101" s="56"/>
+    </row>
+    <row r="102" spans="1:9">
+      <c r="A102" s="53"/>
+      <c r="B102" s="53"/>
+      <c r="C102" s="53"/>
+      <c r="D102" s="54"/>
+      <c r="E102" s="54"/>
+      <c r="F102" s="53"/>
+      <c r="G102" s="53"/>
+      <c r="H102" s="55"/>
+      <c r="I102" s="53"/>
+    </row>
+    <row r="103" spans="1:9">
+      <c r="A103" s="56" t="s">
+        <v>114</v>
+      </c>
+      <c r="B103" s="56" t="s">
+        <v>115</v>
+      </c>
+      <c r="C103" s="56" t="s">
+        <v>116</v>
+      </c>
+      <c r="D103" s="57" t="s">
+        <v>117</v>
+      </c>
+      <c r="E103" s="57" t="s">
+        <v>118</v>
+      </c>
+      <c r="F103" s="56">
+        <v>24</v>
+      </c>
+      <c r="G103" s="56">
+        <v>0.25</v>
+      </c>
+      <c r="H103" s="58" t="s">
+        <v>133</v>
+      </c>
+      <c r="I103" s="56"/>
+    </row>
+    <row r="104" spans="1:9">
+      <c r="A104" s="56" t="s">
+        <v>114</v>
+      </c>
+      <c r="B104" s="56" t="s">
+        <v>115</v>
+      </c>
+      <c r="C104" s="56" t="s">
+        <v>119</v>
+      </c>
+      <c r="D104" s="57" t="s">
+        <v>117</v>
+      </c>
+      <c r="E104" s="57" t="s">
+        <v>120</v>
+      </c>
+      <c r="F104" s="56">
+        <v>24</v>
+      </c>
+      <c r="G104" s="56">
+        <v>0.25</v>
+      </c>
+      <c r="H104" s="58" t="s">
+        <v>133</v>
+      </c>
+      <c r="I104" s="56"/>
+    </row>
+    <row r="105" spans="1:9">
+      <c r="A105" s="53" t="s">
+        <v>121</v>
+      </c>
+      <c r="B105" s="53" t="s">
+        <v>122</v>
+      </c>
+      <c r="C105" s="53" t="s">
+        <v>116</v>
+      </c>
+      <c r="D105" s="54" t="s">
+        <v>123</v>
+      </c>
+      <c r="E105" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="F105" s="53">
+        <v>24</v>
+      </c>
+      <c r="G105" s="53">
+        <v>0.25</v>
+      </c>
+      <c r="H105" s="55" t="s">
+        <v>133</v>
+      </c>
+      <c r="I105" s="53"/>
+    </row>
+    <row r="106" spans="1:9">
+      <c r="A106" s="53" t="s">
+        <v>121</v>
+      </c>
+      <c r="B106" s="53" t="s">
+        <v>122</v>
+      </c>
+      <c r="C106" s="53" t="s">
+        <v>119</v>
+      </c>
+      <c r="D106" s="54" t="s">
+        <v>123</v>
+      </c>
+      <c r="E106" s="54" t="s">
+        <v>124</v>
+      </c>
+      <c r="F106" s="53">
+        <v>24</v>
+      </c>
+      <c r="G106" s="53">
+        <v>0.25</v>
+      </c>
+      <c r="H106" s="55" t="s">
+        <v>133</v>
+      </c>
+      <c r="I106" s="53"/>
+    </row>
+    <row r="107" spans="1:9">
+      <c r="A107" s="56" t="s">
+        <v>114</v>
+      </c>
+      <c r="B107" s="56" t="s">
+        <v>125</v>
+      </c>
+      <c r="C107" s="56" t="s">
+        <v>116</v>
+      </c>
+      <c r="D107" s="57" t="s">
+        <v>126</v>
+      </c>
+      <c r="E107" s="57" t="s">
+        <v>118</v>
+      </c>
+      <c r="F107" s="56">
+        <v>24</v>
+      </c>
+      <c r="G107" s="56">
+        <v>0.25</v>
+      </c>
+      <c r="H107" s="58" t="s">
+        <v>133</v>
+      </c>
+      <c r="I107" s="56"/>
+    </row>
+    <row r="108" spans="1:9">
+      <c r="A108" s="56" t="s">
+        <v>114</v>
+      </c>
+      <c r="B108" s="56" t="s">
+        <v>125</v>
+      </c>
+      <c r="C108" s="56" t="s">
+        <v>119</v>
+      </c>
+      <c r="D108" s="57" t="s">
+        <v>126</v>
+      </c>
+      <c r="E108" s="57" t="s">
+        <v>127</v>
+      </c>
+      <c r="F108" s="56">
+        <v>24</v>
+      </c>
+      <c r="G108" s="56">
+        <v>0.25</v>
+      </c>
+      <c r="H108" s="58" t="s">
+        <v>133</v>
+      </c>
+      <c r="I108" s="56"/>
+    </row>
+    <row r="109" spans="1:9">
+      <c r="A109" s="53" t="s">
+        <v>114</v>
+      </c>
+      <c r="B109" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="C109" s="53" t="s">
+        <v>116</v>
+      </c>
+      <c r="D109" s="54" t="s">
+        <v>129</v>
+      </c>
+      <c r="E109" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="F109" s="53">
+        <v>24</v>
+      </c>
+      <c r="G109" s="53">
+        <v>0.25</v>
+      </c>
+      <c r="H109" s="55" t="s">
+        <v>133</v>
+      </c>
+      <c r="I109" s="53"/>
+    </row>
+    <row r="110" spans="1:9">
+      <c r="A110" s="53" t="s">
+        <v>114</v>
+      </c>
+      <c r="B110" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="C110" s="53" t="s">
+        <v>119</v>
+      </c>
+      <c r="D110" s="54" t="s">
+        <v>129</v>
+      </c>
+      <c r="E110" s="54" t="s">
+        <v>130</v>
+      </c>
+      <c r="F110" s="53">
+        <v>24</v>
+      </c>
+      <c r="G110" s="53">
+        <v>0.25</v>
+      </c>
+      <c r="H110" s="55" t="s">
+        <v>133</v>
+      </c>
+      <c r="I110" s="53"/>
+    </row>
+    <row r="111" spans="1:9">
+      <c r="A111" s="56" t="s">
+        <v>58</v>
+      </c>
+      <c r="B111" s="56" t="s">
+        <v>59</v>
+      </c>
+      <c r="C111" s="56" t="s">
+        <v>214</v>
+      </c>
+      <c r="D111" s="57"/>
+      <c r="E111" s="57"/>
+      <c r="F111" s="56">
+        <v>24</v>
+      </c>
+      <c r="G111" s="56">
+        <v>0.25</v>
+      </c>
+      <c r="H111" s="58" t="s">
+        <v>133</v>
+      </c>
+      <c r="I111" s="56" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9">
+      <c r="A112" s="56" t="s">
+        <v>58</v>
+      </c>
+      <c r="B112" s="56" t="s">
+        <v>59</v>
+      </c>
+      <c r="C112" s="56" t="s">
+        <v>213</v>
+      </c>
+      <c r="D112" s="57"/>
+      <c r="E112" s="57"/>
+      <c r="F112" s="56">
+        <v>24</v>
+      </c>
+      <c r="G112" s="56">
+        <v>0.25</v>
+      </c>
+      <c r="H112" s="58" t="s">
+        <v>133</v>
+      </c>
+      <c r="I112" s="56"/>
+    </row>
+    <row r="113" spans="1:9">
+      <c r="A113" s="56" t="s">
+        <v>200</v>
+      </c>
+      <c r="B113" s="56" t="s">
+        <v>216</v>
+      </c>
+      <c r="C113" s="56" t="s">
+        <v>15</v>
+      </c>
+      <c r="D113" s="57" t="s">
+        <v>217</v>
+      </c>
+      <c r="E113" s="57" t="s">
+        <v>218</v>
+      </c>
+      <c r="F113" s="56"/>
+      <c r="G113" s="56"/>
+      <c r="H113" s="58"/>
+      <c r="I113" s="56"/>
+    </row>
+    <row r="114" spans="1:9">
+      <c r="A114" s="56" t="s">
+        <v>85</v>
+      </c>
+      <c r="B114" s="56" t="s">
+        <v>216</v>
+      </c>
+      <c r="C114" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="D114" s="57" t="s">
+        <v>217</v>
+      </c>
+      <c r="E114" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="F114" s="56"/>
+      <c r="G114" s="56"/>
+      <c r="H114" s="58"/>
+      <c r="I114" s="56"/>
+    </row>
+    <row r="115" spans="1:9">
+      <c r="A115" s="50" t="s">
+        <v>219</v>
+      </c>
+      <c r="B115" s="50" t="s">
+        <v>220</v>
+      </c>
+      <c r="C115" s="50"/>
+      <c r="D115" s="52" t="s">
+        <v>221</v>
+      </c>
+      <c r="E115" s="51" t="s">
+        <v>222</v>
+      </c>
+      <c r="F115" s="50"/>
+      <c r="G115" s="50"/>
+      <c r="H115" s="50"/>
+    </row>
+    <row r="116" spans="1:9">
+      <c r="A116" s="56" t="s">
+        <v>223</v>
+      </c>
+      <c r="B116" s="56" t="s">
+        <v>224</v>
+      </c>
+      <c r="C116" s="56" t="s">
+        <v>15</v>
+      </c>
+      <c r="D116" s="57" t="s">
+        <v>225</v>
+      </c>
+      <c r="E116" s="57"/>
+      <c r="F116" s="56">
+        <v>24</v>
+      </c>
+      <c r="G116" s="56">
+        <v>0.25</v>
+      </c>
+      <c r="H116" s="56" t="s">
+        <v>133</v>
+      </c>
+      <c r="I116" s="56"/>
+    </row>
+    <row r="117" spans="1:9">
+      <c r="A117" s="56" t="s">
+        <v>223</v>
+      </c>
+      <c r="B117" s="56" t="s">
+        <v>224</v>
+      </c>
+      <c r="C117" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="D117" s="57" t="s">
+        <v>226</v>
+      </c>
+      <c r="E117" s="57"/>
+      <c r="F117" s="56">
+        <v>24</v>
+      </c>
+      <c r="G117" s="56">
+        <v>0.25</v>
+      </c>
+      <c r="H117" s="56" t="s">
+        <v>133</v>
+      </c>
+      <c r="I117" s="56"/>
+    </row>
+    <row r="181" spans="9:9">
+      <c r="I181" s="33" t="s">
+        <v>227</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D115" r:id="rId1" xr:uid="{A91C6ABB-1DF9-46D4-A994-DF9507DB5F67}"/>
+    <hyperlink ref="I181" r:id="rId2" xr:uid="{F3A6CAA0-52C1-48EB-88E4-0BB49B2E8A18}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId4"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F10D3F89-6631-4EDE-8E63-7F58B672DC4B}">
   <dimension ref="A1:O80"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3961,7 +7143,7 @@
     <row r="1" spans="1:15">
       <c r="A1" s="8"/>
       <c r="B1" s="18" t="s">
-        <v>131</v>
+        <v>228</v>
       </c>
       <c r="C1" s="8"/>
       <c r="D1" s="8"/>
@@ -3977,7 +7159,7 @@
     <row r="2" spans="1:15">
       <c r="A2" s="8"/>
       <c r="B2" s="19" t="s">
-        <v>132</v>
+        <v>229</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
@@ -3990,649 +7172,649 @@
       <c r="K2" s="8"/>
       <c r="L2" s="28"/>
       <c r="M2" t="s">
-        <v>133</v>
+        <v>230</v>
       </c>
       <c r="N2" t="s">
-        <v>134</v>
+        <v>231</v>
       </c>
       <c r="O2" t="s">
-        <v>135</v>
+        <v>232</v>
       </c>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="8"/>
       <c r="B3" s="20" t="s">
-        <v>136</v>
+        <v>233</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>137</v>
+        <v>234</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>138</v>
+        <v>235</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>139</v>
+        <v>236</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>140</v>
+        <v>237</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>141</v>
+        <v>238</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>142</v>
+        <v>239</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>143</v>
+        <v>240</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>144</v>
+        <v>241</v>
       </c>
       <c r="K3" s="26" t="s">
-        <v>145</v>
+        <v>242</v>
       </c>
       <c r="L3" s="29" t="s">
-        <v>146</v>
+        <v>243</v>
       </c>
       <c r="M3" t="s">
-        <v>147</v>
+        <v>244</v>
       </c>
       <c r="N3" t="s">
-        <v>148</v>
+        <v>245</v>
       </c>
       <c r="O3" t="s">
-        <v>149</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="8"/>
       <c r="B4" s="20" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="E4" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="G4" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H4" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="I4" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J4" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K4" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L4" s="29"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="8"/>
       <c r="B5" s="20" t="s">
-        <v>151</v>
+        <v>248</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>152</v>
+        <v>249</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>153</v>
+        <v>250</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>154</v>
+        <v>251</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>153</v>
+        <v>250</v>
       </c>
       <c r="G5" s="22" t="s">
-        <v>155</v>
+        <v>252</v>
       </c>
       <c r="H5" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="I5" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J5" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K5" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L5" s="29"/>
       <c r="M5" t="s">
-        <v>156</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="8"/>
       <c r="B6" s="20" t="s">
-        <v>157</v>
+        <v>254</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>158</v>
+        <v>255</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>159</v>
+        <v>256</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>160</v>
+        <v>257</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>159</v>
+        <v>256</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>155</v>
+        <v>252</v>
       </c>
       <c r="H6" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="I6" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J6" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K6" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L6" s="29" t="s">
-        <v>161</v>
+        <v>258</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="8"/>
       <c r="B7" s="20" t="s">
-        <v>162</v>
+        <v>259</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>163</v>
+        <v>260</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>164</v>
+        <v>261</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>165</v>
+        <v>262</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>164</v>
+        <v>261</v>
       </c>
       <c r="G7" s="22" t="s">
-        <v>155</v>
+        <v>252</v>
       </c>
       <c r="H7" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="I7" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J7" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K7" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L7" s="29" t="s">
-        <v>161</v>
+        <v>258</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="8"/>
       <c r="B8" s="20" t="s">
-        <v>166</v>
+        <v>263</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>167</v>
+        <v>264</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>168</v>
+        <v>265</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>169</v>
+        <v>266</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>168</v>
+        <v>265</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>155</v>
+        <v>252</v>
       </c>
       <c r="H8" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="I8" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J8" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K8" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L8" s="29"/>
       <c r="O8" t="s">
-        <v>170</v>
+        <v>267</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="8"/>
       <c r="B9" s="20" t="s">
-        <v>171</v>
+        <v>268</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>172</v>
+        <v>269</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>173</v>
+        <v>270</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>174</v>
+        <v>271</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>173</v>
+        <v>270</v>
       </c>
       <c r="G9" s="22" t="s">
-        <v>155</v>
+        <v>252</v>
       </c>
       <c r="H9" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="I9" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J9" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K9" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L9" s="29"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="8"/>
       <c r="B10" s="20" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H10" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="I10" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J10" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K10" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L10" s="29"/>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="8"/>
       <c r="B11" s="20" t="s">
-        <v>175</v>
+        <v>272</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>176</v>
+        <v>273</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>177</v>
+        <v>274</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H11" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="I11" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J11" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K11" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L11" s="29" t="s">
-        <v>178</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="8"/>
       <c r="B12" s="20" t="s">
-        <v>179</v>
+        <v>276</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>180</v>
+        <v>277</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>181</v>
+        <v>278</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H12" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="I12" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J12" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K12" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L12" s="29" t="s">
-        <v>182</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="8"/>
       <c r="B13" s="20" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="G13" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H13" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="I13" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J13" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K13" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L13" s="29"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="8"/>
       <c r="B14" s="20" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="G14" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H14" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="I14" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J14" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K14" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L14" s="29"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="8"/>
       <c r="B15" s="20" t="s">
-        <v>183</v>
+        <v>280</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="G15" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H15" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="I15" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J15" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K15" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L15" s="29"/>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="8"/>
       <c r="B16" s="20" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>184</v>
+        <v>281</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>185</v>
+        <v>282</v>
       </c>
       <c r="E16" s="22" t="s">
-        <v>186</v>
+        <v>283</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>187</v>
+        <v>284</v>
       </c>
       <c r="G16" s="22" t="s">
-        <v>155</v>
+        <v>252</v>
       </c>
       <c r="H16" s="23" t="s">
-        <v>185</v>
+        <v>282</v>
       </c>
       <c r="I16" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J16" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K16" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L16" s="29"/>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="8"/>
       <c r="B17" s="20" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>188</v>
+        <v>285</v>
       </c>
       <c r="D17" s="22" t="s">
-        <v>189</v>
+        <v>286</v>
       </c>
       <c r="E17" s="22" t="s">
-        <v>190</v>
+        <v>287</v>
       </c>
       <c r="F17" s="22" t="s">
-        <v>187</v>
+        <v>284</v>
       </c>
       <c r="G17" s="22" t="s">
-        <v>155</v>
+        <v>252</v>
       </c>
       <c r="H17" s="21" t="s">
-        <v>189</v>
+        <v>286</v>
       </c>
       <c r="I17" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J17" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K17" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L17" s="29"/>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="8"/>
       <c r="B18" s="20" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>191</v>
+        <v>288</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>192</v>
+        <v>289</v>
       </c>
       <c r="E18" s="22" t="s">
-        <v>193</v>
+        <v>290</v>
       </c>
       <c r="F18" s="22" t="s">
-        <v>187</v>
+        <v>284</v>
       </c>
       <c r="G18" s="22" t="s">
-        <v>155</v>
+        <v>252</v>
       </c>
       <c r="H18" s="22" t="s">
-        <v>192</v>
+        <v>289</v>
       </c>
       <c r="I18" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J18" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K18" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L18" s="29"/>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="8"/>
       <c r="B19" s="20" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>194</v>
+        <v>291</v>
       </c>
       <c r="D19" s="22" t="s">
-        <v>195</v>
+        <v>292</v>
       </c>
       <c r="E19" s="22" t="s">
-        <v>196</v>
+        <v>293</v>
       </c>
       <c r="F19" s="22" t="s">
-        <v>187</v>
+        <v>284</v>
       </c>
       <c r="G19" s="22" t="s">
-        <v>155</v>
+        <v>252</v>
       </c>
       <c r="H19" s="22" t="s">
-        <v>195</v>
+        <v>292</v>
       </c>
       <c r="I19" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J19" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K19" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L19" s="29"/>
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="8"/>
       <c r="B20" s="20" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>197</v>
+        <v>294</v>
       </c>
       <c r="D20" s="22" t="s">
-        <v>198</v>
+        <v>295</v>
       </c>
       <c r="E20" s="22" t="s">
-        <v>199</v>
+        <v>296</v>
       </c>
       <c r="F20" s="22" t="s">
-        <v>187</v>
+        <v>284</v>
       </c>
       <c r="G20" s="22" t="s">
-        <v>155</v>
+        <v>252</v>
       </c>
       <c r="H20" s="22" t="s">
-        <v>198</v>
+        <v>295</v>
       </c>
       <c r="I20" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J20" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K20" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L20" s="29"/>
     </row>
@@ -4642,65 +7824,65 @@
         <v>53</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>200</v>
+        <v>297</v>
       </c>
       <c r="D21" s="22" t="s">
-        <v>201</v>
+        <v>298</v>
       </c>
       <c r="E21" s="22" t="s">
-        <v>202</v>
+        <v>299</v>
       </c>
       <c r="F21" s="22" t="s">
-        <v>187</v>
+        <v>284</v>
       </c>
       <c r="G21" s="22" t="s">
-        <v>155</v>
+        <v>252</v>
       </c>
       <c r="H21" s="22" t="s">
-        <v>201</v>
+        <v>298</v>
       </c>
       <c r="I21" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J21" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K21" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L21" s="29"/>
     </row>
     <row r="22" spans="1:15">
       <c r="A22" s="8"/>
       <c r="B22" s="24" t="s">
-        <v>203</v>
+        <v>300</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>204</v>
+        <v>301</v>
       </c>
       <c r="D22" s="22" t="s">
-        <v>205</v>
+        <v>302</v>
       </c>
       <c r="E22" s="22" t="s">
-        <v>206</v>
+        <v>303</v>
       </c>
       <c r="F22" s="22" t="s">
-        <v>187</v>
+        <v>284</v>
       </c>
       <c r="G22" s="22" t="s">
-        <v>155</v>
+        <v>252</v>
       </c>
       <c r="H22" s="22" t="s">
-        <v>205</v>
+        <v>302</v>
       </c>
       <c r="I22" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J22" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K22" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L22" s="29"/>
     </row>
@@ -4708,1002 +7890,1002 @@
       <c r="A23" s="8"/>
       <c r="B23" s="25"/>
       <c r="C23" s="22" t="s">
-        <v>207</v>
+        <v>304</v>
       </c>
       <c r="D23" s="22" t="s">
-        <v>208</v>
+        <v>305</v>
       </c>
       <c r="E23" s="22" t="s">
-        <v>209</v>
+        <v>306</v>
       </c>
       <c r="F23" s="22" t="s">
-        <v>187</v>
+        <v>284</v>
       </c>
       <c r="G23" s="22" t="s">
-        <v>155</v>
+        <v>252</v>
       </c>
       <c r="H23" s="22" t="s">
-        <v>208</v>
+        <v>305</v>
       </c>
       <c r="I23" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J23" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K23" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="8"/>
       <c r="B24" s="20" t="s">
-        <v>210</v>
+        <v>307</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="D24" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="E24" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="F24" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="G24" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H24" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="I24" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J24" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K24" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L24" s="29"/>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="8"/>
       <c r="B25" s="20" t="s">
-        <v>211</v>
+        <v>308</v>
       </c>
       <c r="C25" s="22" t="s">
-        <v>212</v>
+        <v>309</v>
       </c>
       <c r="D25" s="22" t="s">
-        <v>213</v>
+        <v>310</v>
       </c>
       <c r="E25" s="22" t="s">
-        <v>214</v>
+        <v>311</v>
       </c>
       <c r="F25" s="22" t="s">
-        <v>215</v>
+        <v>312</v>
       </c>
       <c r="G25" s="22" t="s">
-        <v>155</v>
+        <v>252</v>
       </c>
       <c r="H25" s="22" t="s">
-        <v>213</v>
+        <v>310</v>
       </c>
       <c r="I25" s="22"/>
       <c r="J25" s="22"/>
       <c r="K25" s="27"/>
       <c r="L25" s="29" t="s">
-        <v>216</v>
+        <v>313</v>
       </c>
     </row>
     <row r="26" spans="1:15" ht="15" customHeight="1">
       <c r="A26" s="8"/>
       <c r="B26" s="20" t="s">
-        <v>217</v>
+        <v>314</v>
       </c>
       <c r="C26" s="22" t="s">
-        <v>218</v>
+        <v>315</v>
       </c>
       <c r="D26" s="22" t="s">
-        <v>219</v>
+        <v>316</v>
       </c>
       <c r="E26" s="22" t="s">
-        <v>220</v>
+        <v>317</v>
       </c>
       <c r="F26" s="22" t="s">
-        <v>155</v>
+        <v>252</v>
       </c>
       <c r="G26" s="22" t="s">
-        <v>218</v>
+        <v>315</v>
       </c>
       <c r="H26" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="I26" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J26" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K26" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L26" s="29" t="s">
-        <v>221</v>
+        <v>318</v>
       </c>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="8"/>
       <c r="B27" s="20" t="s">
-        <v>222</v>
+        <v>319</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>223</v>
+        <v>320</v>
       </c>
       <c r="D27" s="22" t="s">
-        <v>224</v>
+        <v>321</v>
       </c>
       <c r="E27" s="22" t="s">
-        <v>225</v>
+        <v>322</v>
       </c>
       <c r="F27" s="22" t="s">
-        <v>155</v>
+        <v>252</v>
       </c>
       <c r="G27" s="22" t="s">
-        <v>226</v>
+        <v>323</v>
       </c>
       <c r="H27" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="I27" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J27" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K27" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L27" s="29"/>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="8"/>
       <c r="B28" s="20" t="s">
-        <v>227</v>
+        <v>324</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>228</v>
+        <v>325</v>
       </c>
       <c r="D28" s="22" t="s">
-        <v>229</v>
+        <v>326</v>
       </c>
       <c r="E28" s="22" t="s">
-        <v>230</v>
+        <v>327</v>
       </c>
       <c r="F28" s="22" t="s">
-        <v>155</v>
+        <v>252</v>
       </c>
       <c r="G28" s="22" t="s">
-        <v>228</v>
+        <v>325</v>
       </c>
       <c r="H28" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="I28" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J28" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K28" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L28" s="29"/>
       <c r="O28" t="s">
-        <v>170</v>
+        <v>267</v>
       </c>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="8"/>
       <c r="B29" s="20" t="s">
-        <v>231</v>
+        <v>328</v>
       </c>
       <c r="C29" s="22" t="s">
-        <v>232</v>
+        <v>329</v>
       </c>
       <c r="D29" s="22" t="s">
-        <v>233</v>
+        <v>330</v>
       </c>
       <c r="E29" s="22" t="s">
-        <v>234</v>
+        <v>331</v>
       </c>
       <c r="F29" s="22" t="s">
-        <v>155</v>
+        <v>252</v>
       </c>
       <c r="G29" s="22" t="s">
-        <v>232</v>
+        <v>329</v>
       </c>
       <c r="H29" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="I29" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J29" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K29" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L29" s="29"/>
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="8"/>
       <c r="B30" s="20" t="s">
-        <v>235</v>
+        <v>332</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>236</v>
+        <v>333</v>
       </c>
       <c r="D30" s="22" t="s">
-        <v>237</v>
+        <v>334</v>
       </c>
       <c r="E30" s="22" t="s">
-        <v>238</v>
+        <v>335</v>
       </c>
       <c r="F30" s="22" t="s">
-        <v>155</v>
+        <v>252</v>
       </c>
       <c r="G30" s="22" t="s">
-        <v>236</v>
+        <v>333</v>
       </c>
       <c r="H30" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="I30" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J30" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K30" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L30" s="29"/>
       <c r="N30" t="s">
-        <v>239</v>
+        <v>336</v>
       </c>
     </row>
     <row r="31" spans="1:15">
       <c r="A31" s="8"/>
       <c r="B31" s="20" t="s">
-        <v>240</v>
+        <v>337</v>
       </c>
       <c r="C31" s="22" t="s">
-        <v>241</v>
+        <v>338</v>
       </c>
       <c r="D31" s="22" t="s">
-        <v>242</v>
+        <v>339</v>
       </c>
       <c r="E31" s="22" t="s">
-        <v>243</v>
+        <v>340</v>
       </c>
       <c r="F31" s="22" t="s">
-        <v>155</v>
+        <v>252</v>
       </c>
       <c r="G31" s="22" t="s">
-        <v>241</v>
+        <v>338</v>
       </c>
       <c r="H31" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="I31" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J31" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K31" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L31" s="29"/>
     </row>
     <row r="32" spans="1:15">
       <c r="A32" s="8"/>
       <c r="B32" s="20" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="C32" s="22" t="s">
-        <v>244</v>
+        <v>341</v>
       </c>
       <c r="D32" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="E32" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="F32" s="22" t="s">
-        <v>155</v>
+        <v>252</v>
       </c>
       <c r="G32" s="22" t="s">
-        <v>244</v>
+        <v>341</v>
       </c>
       <c r="H32" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="I32" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J32" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K32" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L32" s="29" t="s">
-        <v>245</v>
+        <v>342</v>
       </c>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="8"/>
       <c r="B33" s="20" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="C33" s="22" t="s">
-        <v>246</v>
+        <v>343</v>
       </c>
       <c r="D33" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="E33" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="F33" s="22" t="s">
-        <v>155</v>
+        <v>252</v>
       </c>
       <c r="G33" s="22" t="s">
-        <v>246</v>
+        <v>343</v>
       </c>
       <c r="H33" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="I33" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J33" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K33" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L33" s="29" t="s">
-        <v>245</v>
+        <v>342</v>
       </c>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" s="8"/>
       <c r="B34" s="20" t="s">
-        <v>247</v>
+        <v>344</v>
       </c>
       <c r="C34" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="D34" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="E34" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="F34" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="G34" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H34" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="I34" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J34" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K34" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L34" s="29"/>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" s="8"/>
       <c r="B35" s="20" t="s">
-        <v>248</v>
+        <v>345</v>
       </c>
       <c r="C35" s="22" t="s">
-        <v>249</v>
+        <v>346</v>
       </c>
       <c r="D35" s="22" t="s">
-        <v>250</v>
+        <v>347</v>
       </c>
       <c r="E35" s="22" t="s">
-        <v>251</v>
+        <v>348</v>
       </c>
       <c r="F35" s="22" t="s">
+        <v>349</v>
+      </c>
+      <c r="G35" s="22" t="s">
         <v>252</v>
       </c>
-      <c r="G35" s="22" t="s">
-        <v>155</v>
-      </c>
       <c r="H35" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="I35" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J35" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K35" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L35" s="29" t="s">
-        <v>253</v>
+        <v>350</v>
       </c>
       <c r="M35" t="s">
-        <v>254</v>
+        <v>351</v>
       </c>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="8"/>
       <c r="B36" s="20" t="s">
-        <v>255</v>
+        <v>352</v>
       </c>
       <c r="C36" s="22" t="s">
-        <v>256</v>
+        <v>353</v>
       </c>
       <c r="D36" s="22" t="s">
-        <v>257</v>
+        <v>354</v>
       </c>
       <c r="E36" s="22" t="s">
-        <v>258</v>
+        <v>355</v>
       </c>
       <c r="F36" s="22" t="s">
+        <v>349</v>
+      </c>
+      <c r="G36" s="22" t="s">
         <v>252</v>
       </c>
-      <c r="G36" s="22" t="s">
-        <v>155</v>
-      </c>
       <c r="H36" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="I36" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J36" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K36" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L36" s="29"/>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" s="8"/>
       <c r="B37" s="20" t="s">
-        <v>259</v>
+        <v>356</v>
       </c>
       <c r="C37" s="22" t="s">
-        <v>260</v>
+        <v>357</v>
       </c>
       <c r="D37" s="22" t="s">
-        <v>261</v>
+        <v>358</v>
       </c>
       <c r="E37" s="22" t="s">
-        <v>262</v>
+        <v>359</v>
       </c>
       <c r="F37" s="22" t="s">
+        <v>349</v>
+      </c>
+      <c r="G37" s="22" t="s">
         <v>252</v>
       </c>
-      <c r="G37" s="22" t="s">
-        <v>155</v>
-      </c>
       <c r="H37" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="I37" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J37" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K37" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L37" s="29"/>
       <c r="N37" s="45" t="s">
-        <v>254</v>
+        <v>351</v>
       </c>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" s="8"/>
       <c r="B38" s="20" t="s">
-        <v>231</v>
+        <v>328</v>
       </c>
       <c r="C38" s="22" t="s">
-        <v>263</v>
+        <v>360</v>
       </c>
       <c r="D38" s="22" t="s">
-        <v>261</v>
+        <v>358</v>
       </c>
       <c r="E38" s="22" t="s">
-        <v>264</v>
+        <v>361</v>
       </c>
       <c r="F38" s="22" t="s">
+        <v>349</v>
+      </c>
+      <c r="G38" s="22" t="s">
         <v>252</v>
       </c>
-      <c r="G38" s="22" t="s">
-        <v>155</v>
-      </c>
       <c r="H38" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="I38" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J38" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K38" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L38" s="29"/>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" s="8"/>
       <c r="B39" s="20" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="C39" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="D39" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="E39" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="F39" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="G39" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H39" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="I39" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J39" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K39" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L39" s="29"/>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="8"/>
       <c r="B40" s="20" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="C40" s="22" t="s">
-        <v>265</v>
+        <v>362</v>
       </c>
       <c r="D40" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="E40" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="F40" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="G40" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H40" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="I40" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J40" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K40" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L40" s="29" t="s">
-        <v>266</v>
+        <v>363</v>
       </c>
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="8"/>
       <c r="B41" s="20" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="C41" s="22" t="s">
-        <v>212</v>
+        <v>309</v>
       </c>
       <c r="D41" s="22" t="s">
-        <v>213</v>
+        <v>310</v>
       </c>
       <c r="E41" s="22" t="s">
-        <v>267</v>
+        <v>364</v>
       </c>
       <c r="F41" s="22" t="s">
-        <v>155</v>
+        <v>252</v>
       </c>
       <c r="G41" s="22" t="s">
-        <v>268</v>
+        <v>365</v>
       </c>
       <c r="H41" s="22" t="s">
-        <v>187</v>
+        <v>284</v>
       </c>
       <c r="I41" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J41" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K41" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L41" s="29" t="s">
-        <v>269</v>
+        <v>366</v>
       </c>
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="8"/>
       <c r="B42" s="20" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="C42" s="22" t="s">
-        <v>270</v>
+        <v>367</v>
       </c>
       <c r="D42" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="E42" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="F42" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="G42" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H42" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="I42" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J42" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K42" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L42" s="29"/>
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="8"/>
       <c r="B43" s="20" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="C43" s="22" t="s">
-        <v>271</v>
+        <v>368</v>
       </c>
       <c r="D43" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="E43" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="F43" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="G43" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H43" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="I43" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J43" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K43" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L43" s="29"/>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="8"/>
       <c r="B44" s="20" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="C44" s="22" t="s">
-        <v>272</v>
+        <v>369</v>
       </c>
       <c r="D44" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="E44" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="F44" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="G44" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H44" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="I44" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J44" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K44" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L44" s="29"/>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="8"/>
       <c r="B45" s="20" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="C45" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="D45" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="E45" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="F45" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="G45" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H45" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="I45" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J45" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K45" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L45" s="29"/>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="8"/>
       <c r="B46" s="20" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="C46" s="22" t="s">
-        <v>273</v>
+        <v>370</v>
       </c>
       <c r="D46" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="E46" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="F46" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="G46" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H46" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="I46" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J46" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K46" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L46" s="29"/>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="8"/>
       <c r="B47" s="20" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="C47" s="22" t="s">
-        <v>274</v>
+        <v>371</v>
       </c>
       <c r="D47" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="E47" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="F47" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="G47" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H47" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="I47" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J47" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K47" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L47" s="29"/>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="8"/>
       <c r="B48" s="20" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="C48" s="22" t="s">
-        <v>275</v>
+        <v>372</v>
       </c>
       <c r="D48" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="E48" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="F48" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="G48" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H48" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="I48" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J48" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K48" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L48" s="29"/>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" s="8"/>
       <c r="B49" s="20" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="C49" s="22" t="s">
-        <v>276</v>
+        <v>373</v>
       </c>
       <c r="D49" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="E49" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="F49" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="G49" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H49" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="I49" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J49" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K49" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L49" s="29"/>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" s="8"/>
       <c r="B50" s="20" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="C50" s="22" t="s">
-        <v>277</v>
+        <v>374</v>
       </c>
       <c r="D50" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="E50" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="F50" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="G50" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H50" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="I50" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J50" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K50" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L50" s="29"/>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" s="8"/>
       <c r="B51" s="20" t="s">
-        <v>278</v>
+        <v>375</v>
       </c>
       <c r="C51" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="D51" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="E51" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="F51" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="G51" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H51" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="I51" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J51" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K51" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L51" s="29"/>
     </row>
@@ -5713,31 +8895,31 @@
         <v>15</v>
       </c>
       <c r="C52" s="20" t="s">
-        <v>279</v>
+        <v>376</v>
       </c>
       <c r="D52" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="E52" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="F52" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="G52" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H52" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="I52" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J52" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K52" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L52" s="29"/>
     </row>
@@ -5747,446 +8929,446 @@
         <v>15</v>
       </c>
       <c r="C53" s="22" t="s">
-        <v>280</v>
+        <v>377</v>
       </c>
       <c r="D53" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="E53" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="F53" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="G53" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H53" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="I53" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J53" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K53" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L53" s="29"/>
     </row>
     <row r="54" spans="1:12">
       <c r="A54" s="8"/>
       <c r="B54" s="20" t="s">
-        <v>281</v>
+        <v>378</v>
       </c>
       <c r="C54" s="22" t="s">
-        <v>282</v>
+        <v>379</v>
       </c>
       <c r="D54" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="E54" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="F54" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="G54" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H54" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="I54" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J54" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K54" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L54" s="29"/>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" s="8"/>
       <c r="B55" s="20" t="s">
-        <v>283</v>
+        <v>380</v>
       </c>
       <c r="C55" s="22" t="s">
-        <v>284</v>
+        <v>381</v>
       </c>
       <c r="D55" s="22" t="s">
-        <v>285</v>
+        <v>382</v>
       </c>
       <c r="E55" s="22" t="s">
-        <v>286</v>
+        <v>383</v>
       </c>
       <c r="F55" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="G55" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H55" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="I55" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J55" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K55" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L55" s="29"/>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" s="8"/>
       <c r="B56" s="20" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="C56" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="D56" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="E56" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="F56" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="G56" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H56" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="I56" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J56" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K56" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L56" s="29"/>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" s="8"/>
       <c r="B57" s="20" t="s">
-        <v>287</v>
+        <v>384</v>
       </c>
       <c r="C57" s="22" t="s">
-        <v>288</v>
+        <v>385</v>
       </c>
       <c r="D57" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="E57" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="F57" s="22" t="s">
-        <v>289</v>
+        <v>386</v>
       </c>
       <c r="G57" s="22" t="s">
-        <v>290</v>
+        <v>387</v>
       </c>
       <c r="H57" s="22" t="s">
-        <v>291</v>
+        <v>388</v>
       </c>
       <c r="I57" s="22" t="s">
-        <v>292</v>
+        <v>389</v>
       </c>
       <c r="J57" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K57" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L57" s="29"/>
     </row>
     <row r="58" spans="1:12">
       <c r="A58" s="8"/>
       <c r="B58" s="20" t="s">
-        <v>293</v>
+        <v>390</v>
       </c>
       <c r="C58" s="22" t="s">
-        <v>294</v>
+        <v>391</v>
       </c>
       <c r="D58" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="E58" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="F58" s="22" t="s">
-        <v>289</v>
+        <v>386</v>
       </c>
       <c r="G58" s="22" t="s">
-        <v>290</v>
+        <v>387</v>
       </c>
       <c r="H58" s="22" t="s">
-        <v>291</v>
+        <v>388</v>
       </c>
       <c r="I58" s="22" t="s">
-        <v>292</v>
+        <v>389</v>
       </c>
       <c r="J58" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K58" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L58" s="29"/>
     </row>
     <row r="59" spans="1:12">
       <c r="A59" s="8"/>
       <c r="B59" s="20" t="s">
-        <v>295</v>
+        <v>392</v>
       </c>
       <c r="C59" s="22" t="s">
-        <v>296</v>
+        <v>393</v>
       </c>
       <c r="D59" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="E59" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="F59" s="22" t="s">
-        <v>289</v>
+        <v>386</v>
       </c>
       <c r="G59" s="22" t="s">
-        <v>290</v>
+        <v>387</v>
       </c>
       <c r="H59" s="22" t="s">
-        <v>291</v>
+        <v>388</v>
       </c>
       <c r="I59" s="22" t="s">
-        <v>292</v>
+        <v>389</v>
       </c>
       <c r="J59" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K59" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L59" s="29"/>
     </row>
     <row r="60" spans="1:12">
       <c r="A60" s="8"/>
       <c r="B60" s="20" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="C60" s="22" t="s">
-        <v>297</v>
+        <v>394</v>
       </c>
       <c r="D60" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="E60" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="F60" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="G60" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H60" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="I60" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J60" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K60" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L60" s="29"/>
     </row>
     <row r="61" spans="1:12">
       <c r="A61" s="8"/>
       <c r="B61" s="20" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="C61" s="22" t="s">
-        <v>298</v>
+        <v>395</v>
       </c>
       <c r="D61" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="E61" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="F61" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="G61" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H61" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="I61" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J61" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K61" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L61" s="29"/>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" s="8"/>
       <c r="B62" s="20" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="C62" s="22" t="s">
-        <v>299</v>
+        <v>396</v>
       </c>
       <c r="D62" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="E62" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="F62" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="G62" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H62" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="I62" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="J62" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K62" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L62" s="29"/>
     </row>
     <row r="63" spans="1:12">
       <c r="A63" s="8"/>
       <c r="B63" s="20" t="s">
-        <v>300</v>
+        <v>397</v>
       </c>
       <c r="C63" s="22" t="s">
-        <v>301</v>
+        <v>398</v>
       </c>
       <c r="D63" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="E63" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="F63" s="22" t="s">
-        <v>289</v>
+        <v>386</v>
       </c>
       <c r="G63" s="22" t="s">
-        <v>290</v>
+        <v>387</v>
       </c>
       <c r="H63" s="22" t="s">
-        <v>291</v>
+        <v>388</v>
       </c>
       <c r="I63" s="22" t="s">
-        <v>292</v>
+        <v>389</v>
       </c>
       <c r="J63" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K63" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L63" s="29"/>
     </row>
     <row r="64" spans="1:12">
       <c r="A64" s="8"/>
       <c r="B64" s="20" t="s">
-        <v>302</v>
+        <v>399</v>
       </c>
       <c r="C64" s="22" t="s">
-        <v>303</v>
+        <v>400</v>
       </c>
       <c r="D64" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="E64" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="F64" s="22" t="s">
-        <v>289</v>
+        <v>386</v>
       </c>
       <c r="G64" s="22" t="s">
-        <v>290</v>
+        <v>387</v>
       </c>
       <c r="H64" s="22" t="s">
-        <v>291</v>
+        <v>388</v>
       </c>
       <c r="I64" s="22" t="s">
-        <v>292</v>
+        <v>389</v>
       </c>
       <c r="J64" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K64" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L64" s="29"/>
     </row>
     <row r="65" spans="1:15">
       <c r="A65" s="8"/>
       <c r="B65" s="20" t="s">
-        <v>304</v>
+        <v>401</v>
       </c>
       <c r="C65" s="22" t="s">
-        <v>305</v>
+        <v>402</v>
       </c>
       <c r="D65" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="E65" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="F65" s="22" t="s">
-        <v>289</v>
+        <v>386</v>
       </c>
       <c r="G65" s="22" t="s">
-        <v>290</v>
+        <v>387</v>
       </c>
       <c r="H65" s="22" t="s">
-        <v>291</v>
+        <v>388</v>
       </c>
       <c r="I65" s="22" t="s">
-        <v>292</v>
+        <v>389</v>
       </c>
       <c r="J65" s="22" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="K65" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L65" s="29"/>
     </row>
     <row r="66" spans="1:15">
       <c r="A66" s="8"/>
       <c r="B66" s="24" t="s">
-        <v>306</v>
+        <v>403</v>
       </c>
       <c r="C66" s="8"/>
       <c r="D66" s="8"/>
@@ -6201,7 +9383,7 @@
     <row r="67" spans="1:15">
       <c r="A67" s="8"/>
       <c r="B67" s="8" t="s">
-        <v>307</v>
+        <v>404</v>
       </c>
       <c r="C67" s="8"/>
       <c r="D67" s="8"/>
@@ -6213,13 +9395,13 @@
       <c r="J67" s="8"/>
       <c r="K67" s="8"/>
       <c r="O67" t="s">
-        <v>156</v>
+        <v>253</v>
       </c>
     </row>
     <row r="68" spans="1:15">
       <c r="A68" s="8"/>
       <c r="B68" s="8" t="s">
-        <v>308</v>
+        <v>405</v>
       </c>
       <c r="C68" s="8"/>
       <c r="D68" s="8"/>
@@ -6231,7 +9413,7 @@
       <c r="J68" s="8"/>
       <c r="K68" s="8"/>
       <c r="O68" t="s">
-        <v>309</v>
+        <v>406</v>
       </c>
     </row>
     <row r="69" spans="1:15">
@@ -6398,7 +9580,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F143BB98-7F62-4535-B91D-3F2AE9AA58C5}">
   <dimension ref="A1:L214"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -6420,13 +9602,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>310</v>
+        <v>407</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>311</v>
+        <v>408</v>
       </c>
       <c r="E1" t="s">
-        <v>312</v>
+        <v>409</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
@@ -6435,12 +9617,12 @@
         <v>6</v>
       </c>
       <c r="K1" t="s">
-        <v>313</v>
+        <v>410</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>314</v>
+        <v>411</v>
       </c>
       <c r="C2" t="s">
         <v>69</v>
@@ -6451,12 +9633,12 @@
       <c r="E2" s="1"/>
       <c r="G2" s="4"/>
       <c r="K2" t="s">
-        <v>315</v>
+        <v>412</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>314</v>
+        <v>411</v>
       </c>
       <c r="C3" t="s">
         <v>72</v>
@@ -6467,12 +9649,12 @@
       <c r="E3" s="1"/>
       <c r="G3" s="4"/>
       <c r="K3" t="s">
-        <v>316</v>
+        <v>413</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>317</v>
+        <v>414</v>
       </c>
       <c r="C4" t="s">
         <v>69</v>
@@ -6486,15 +9668,15 @@
         <v>15</v>
       </c>
       <c r="K4" t="s">
-        <v>318</v>
+        <v>415</v>
       </c>
       <c r="L4" s="33" t="s">
-        <v>319</v>
+        <v>416</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>317</v>
+        <v>414</v>
       </c>
       <c r="C5" t="s">
         <v>72</v>
@@ -6505,12 +9687,12 @@
       <c r="E5" s="1"/>
       <c r="G5" s="4"/>
       <c r="K5" t="s">
-        <v>320</v>
+        <v>417</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>321</v>
+        <v>418</v>
       </c>
       <c r="C6" t="s">
         <v>69</v>
@@ -6523,7 +9705,7 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>321</v>
+        <v>418</v>
       </c>
       <c r="C7" t="s">
         <v>72</v>
@@ -6536,7 +9718,7 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>322</v>
+        <v>419</v>
       </c>
       <c r="C8" t="s">
         <v>69</v>
@@ -6549,7 +9731,7 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>322</v>
+        <v>419</v>
       </c>
       <c r="C9" t="s">
         <v>72</v>
@@ -6562,7 +9744,7 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>323</v>
+        <v>420</v>
       </c>
       <c r="C10" t="s">
         <v>69</v>
@@ -6574,7 +9756,7 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>323</v>
+        <v>420</v>
       </c>
       <c r="C11" t="s">
         <v>72</v>
@@ -7083,13 +10265,13 @@
         <v>23</v>
       </c>
       <c r="B39" t="s">
-        <v>324</v>
+        <v>421</v>
       </c>
       <c r="C39" t="s">
         <v>25</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>325</v>
+        <v>422</v>
       </c>
       <c r="E39" s="1"/>
     </row>
@@ -7098,13 +10280,13 @@
         <v>23</v>
       </c>
       <c r="B40" t="s">
-        <v>324</v>
+        <v>421</v>
       </c>
       <c r="C40" t="s">
         <v>28</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>325</v>
+        <v>422</v>
       </c>
       <c r="E40" s="1"/>
     </row>
@@ -7113,13 +10295,13 @@
         <v>23</v>
       </c>
       <c r="B41" t="s">
-        <v>324</v>
+        <v>421</v>
       </c>
       <c r="C41" t="s">
         <v>30</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>325</v>
+        <v>422</v>
       </c>
       <c r="E41" s="1"/>
     </row>
@@ -7128,13 +10310,13 @@
         <v>23</v>
       </c>
       <c r="B42" t="s">
-        <v>324</v>
+        <v>421</v>
       </c>
       <c r="C42" t="s">
         <v>32</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>325</v>
+        <v>422</v>
       </c>
       <c r="E42" s="1"/>
     </row>
@@ -7143,13 +10325,13 @@
         <v>23</v>
       </c>
       <c r="B43" t="s">
-        <v>324</v>
+        <v>421</v>
       </c>
       <c r="C43" t="s">
         <v>25</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>326</v>
+        <v>423</v>
       </c>
       <c r="E43" s="1"/>
     </row>
@@ -7158,13 +10340,13 @@
         <v>23</v>
       </c>
       <c r="B44" t="s">
-        <v>324</v>
+        <v>421</v>
       </c>
       <c r="C44" t="s">
         <v>28</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>326</v>
+        <v>423</v>
       </c>
       <c r="E44" s="1"/>
     </row>
@@ -7173,13 +10355,13 @@
         <v>23</v>
       </c>
       <c r="B45" t="s">
-        <v>324</v>
+        <v>421</v>
       </c>
       <c r="C45" t="s">
         <v>30</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>326</v>
+        <v>423</v>
       </c>
       <c r="E45" s="1"/>
     </row>
@@ -7188,25 +10370,25 @@
         <v>23</v>
       </c>
       <c r="B46" t="s">
-        <v>324</v>
+        <v>421</v>
       </c>
       <c r="C46" t="s">
         <v>32</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>326</v>
+        <v>423</v>
       </c>
       <c r="E46" s="1"/>
     </row>
     <row r="47" spans="1:8">
       <c r="D47" s="1" t="s">
-        <v>327</v>
+        <v>424</v>
       </c>
       <c r="E47" s="1"/>
     </row>
     <row r="48" spans="1:8">
       <c r="D48" s="1" t="s">
-        <v>327</v>
+        <v>424</v>
       </c>
       <c r="E48" s="1"/>
     </row>
@@ -7221,7 +10403,7 @@
         <v>69</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>328</v>
+        <v>425</v>
       </c>
       <c r="E49" s="1"/>
     </row>
@@ -7236,43 +10418,43 @@
         <v>72</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>328</v>
+        <v>425</v>
       </c>
       <c r="E50" s="1"/>
     </row>
     <row r="51" spans="1:5">
       <c r="D51" s="1" t="s">
-        <v>329</v>
+        <v>426</v>
       </c>
       <c r="E51" s="1"/>
     </row>
     <row r="52" spans="1:5">
       <c r="D52" s="1" t="s">
-        <v>329</v>
+        <v>426</v>
       </c>
       <c r="E52" s="1"/>
     </row>
     <row r="53" spans="1:5">
       <c r="D53" s="1" t="s">
-        <v>330</v>
+        <v>427</v>
       </c>
       <c r="E53" s="1"/>
     </row>
     <row r="54" spans="1:5">
       <c r="D54" s="1" t="s">
-        <v>330</v>
+        <v>427</v>
       </c>
       <c r="E54" s="1"/>
     </row>
     <row r="55" spans="1:5">
       <c r="D55" s="1" t="s">
-        <v>331</v>
+        <v>428</v>
       </c>
       <c r="E55" s="1"/>
     </row>
     <row r="56" spans="1:5">
       <c r="D56" s="1" t="s">
-        <v>331</v>
+        <v>428</v>
       </c>
       <c r="E56" s="1"/>
     </row>
@@ -7284,10 +10466,10 @@
         <v>69</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>332</v>
+        <v>429</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>333</v>
+        <v>430</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -7298,10 +10480,10 @@
         <v>72</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>332</v>
+        <v>429</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>333</v>
+        <v>430</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -7312,10 +10494,10 @@
         <v>69</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>226</v>
+        <v>323</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>333</v>
+        <v>430</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -7326,10 +10508,10 @@
         <v>72</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>226</v>
+        <v>323</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>333</v>
+        <v>430</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -7340,10 +10522,10 @@
         <v>69</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>334</v>
+        <v>431</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>333</v>
+        <v>430</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -7354,10 +10536,10 @@
         <v>72</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>334</v>
+        <v>431</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>333</v>
+        <v>430</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -7368,10 +10550,10 @@
         <v>69</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>335</v>
+        <v>432</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>333</v>
+        <v>430</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -7382,10 +10564,10 @@
         <v>72</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>335</v>
+        <v>432</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>333</v>
+        <v>430</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -7396,10 +10578,10 @@
         <v>69</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>336</v>
+        <v>433</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>333</v>
+        <v>430</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -7410,10 +10592,10 @@
         <v>72</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>336</v>
+        <v>433</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>333</v>
+        <v>430</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -7424,10 +10606,10 @@
         <v>69</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>337</v>
+        <v>434</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>333</v>
+        <v>430</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -7438,10 +10620,10 @@
         <v>72</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>337</v>
+        <v>434</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>333</v>
+        <v>430</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -7452,10 +10634,10 @@
         <v>69</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>338</v>
+        <v>435</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>333</v>
+        <v>430</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -7466,10 +10648,10 @@
         <v>72</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>338</v>
+        <v>435</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>333</v>
+        <v>430</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -7480,10 +10662,10 @@
         <v>69</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>339</v>
+        <v>436</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>333</v>
+        <v>430</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -7494,10 +10676,10 @@
         <v>72</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>339</v>
+        <v>436</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>333</v>
+        <v>430</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -7508,10 +10690,10 @@
         <v>69</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>340</v>
+        <v>437</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>333</v>
+        <v>430</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -7522,10 +10704,10 @@
         <v>72</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>340</v>
+        <v>437</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>333</v>
+        <v>430</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -7536,10 +10718,10 @@
         <v>69</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>341</v>
+        <v>438</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>333</v>
+        <v>430</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -7550,10 +10732,10 @@
         <v>72</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>341</v>
+        <v>438</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>333</v>
+        <v>430</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -7567,7 +10749,7 @@
         <v>85</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>342</v>
+        <v>439</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -7581,758 +10763,758 @@
         <v>85</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>342</v>
+        <v>439</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" t="s">
-        <v>343</v>
+        <v>440</v>
       </c>
       <c r="C79" t="s">
         <v>69</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>344</v>
+        <v>441</v>
       </c>
       <c r="E79" s="1"/>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" t="s">
-        <v>343</v>
+        <v>440</v>
       </c>
       <c r="C80" t="s">
         <v>72</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>344</v>
+        <v>441</v>
       </c>
       <c r="E80" s="1"/>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" t="s">
-        <v>343</v>
+        <v>440</v>
       </c>
       <c r="C81" t="s">
-        <v>343</v>
+        <v>440</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>344</v>
+        <v>441</v>
       </c>
       <c r="E81" s="1"/>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" t="s">
-        <v>343</v>
+        <v>440</v>
       </c>
       <c r="C82" t="s">
         <v>69</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>345</v>
+        <v>442</v>
       </c>
       <c r="E82" s="1"/>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" t="s">
-        <v>343</v>
+        <v>440</v>
       </c>
       <c r="C83" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>345</v>
+        <v>442</v>
       </c>
       <c r="E83" s="1"/>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" t="s">
-        <v>343</v>
+        <v>440</v>
       </c>
       <c r="C84" t="s">
-        <v>343</v>
+        <v>440</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>345</v>
+        <v>442</v>
       </c>
       <c r="E84" s="1"/>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" t="s">
-        <v>343</v>
+        <v>440</v>
       </c>
       <c r="C85" t="s">
         <v>69</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>346</v>
+        <v>443</v>
       </c>
       <c r="E85" s="1"/>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" t="s">
-        <v>343</v>
+        <v>440</v>
       </c>
       <c r="C86" t="s">
         <v>72</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>346</v>
+        <v>443</v>
       </c>
       <c r="E86" s="1"/>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" t="s">
-        <v>343</v>
+        <v>440</v>
       </c>
       <c r="C87" t="s">
-        <v>343</v>
+        <v>440</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>346</v>
+        <v>443</v>
       </c>
       <c r="E87" s="1"/>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" t="s">
-        <v>343</v>
+        <v>440</v>
       </c>
       <c r="C88" t="s">
         <v>69</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>347</v>
+        <v>444</v>
       </c>
       <c r="E88" s="1"/>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" t="s">
-        <v>343</v>
+        <v>440</v>
       </c>
       <c r="C89" t="s">
         <v>72</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>347</v>
+        <v>444</v>
       </c>
       <c r="E89" s="1"/>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" t="s">
-        <v>343</v>
+        <v>440</v>
       </c>
       <c r="C90" t="s">
-        <v>343</v>
+        <v>440</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>347</v>
+        <v>444</v>
       </c>
       <c r="E90" s="1"/>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" t="s">
-        <v>343</v>
+        <v>440</v>
       </c>
       <c r="C91" t="s">
         <v>69</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>348</v>
+        <v>445</v>
       </c>
       <c r="E91" s="1"/>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" t="s">
-        <v>343</v>
+        <v>440</v>
       </c>
       <c r="C92" t="s">
         <v>72</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>348</v>
+        <v>445</v>
       </c>
       <c r="E92" s="1"/>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" t="s">
-        <v>343</v>
+        <v>440</v>
       </c>
       <c r="C93" t="s">
-        <v>343</v>
+        <v>440</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>348</v>
+        <v>445</v>
       </c>
       <c r="E93" s="1"/>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" t="s">
-        <v>343</v>
+        <v>440</v>
       </c>
       <c r="C94" t="s">
         <v>69</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>349</v>
+        <v>446</v>
       </c>
       <c r="E94" s="1"/>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" t="s">
-        <v>343</v>
+        <v>440</v>
       </c>
       <c r="C95" t="s">
         <v>72</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>349</v>
+        <v>446</v>
       </c>
       <c r="E95" s="1"/>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" t="s">
-        <v>343</v>
+        <v>440</v>
       </c>
       <c r="C96" t="s">
-        <v>343</v>
+        <v>440</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>349</v>
+        <v>446</v>
       </c>
       <c r="E96" s="1"/>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" t="s">
-        <v>343</v>
+        <v>440</v>
       </c>
       <c r="C97" t="s">
         <v>69</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>350</v>
+        <v>447</v>
       </c>
       <c r="E97" s="1"/>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" t="s">
-        <v>343</v>
+        <v>440</v>
       </c>
       <c r="C98" t="s">
         <v>72</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>350</v>
+        <v>447</v>
       </c>
       <c r="E98" s="1"/>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" t="s">
-        <v>343</v>
+        <v>440</v>
       </c>
       <c r="C99" t="s">
-        <v>351</v>
+        <v>448</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>350</v>
+        <v>447</v>
       </c>
       <c r="E99" s="1"/>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" t="s">
-        <v>352</v>
+        <v>449</v>
       </c>
       <c r="C100" t="s">
         <v>69</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>353</v>
+        <v>450</v>
       </c>
       <c r="E100" s="32"/>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" t="s">
-        <v>352</v>
+        <v>449</v>
       </c>
       <c r="C101" t="s">
         <v>72</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>353</v>
+        <v>450</v>
       </c>
       <c r="E101" s="32" t="s">
-        <v>354</v>
+        <v>451</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" t="s">
-        <v>352</v>
+        <v>449</v>
       </c>
       <c r="C102" t="s">
-        <v>351</v>
+        <v>448</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>353</v>
+        <v>450</v>
       </c>
       <c r="E102" s="32" t="s">
-        <v>354</v>
+        <v>451</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" t="s">
-        <v>352</v>
+        <v>449</v>
       </c>
       <c r="C103" t="s">
         <v>69</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>355</v>
+        <v>452</v>
       </c>
       <c r="E103" s="32"/>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" t="s">
-        <v>352</v>
+        <v>449</v>
       </c>
       <c r="C104" t="s">
         <v>72</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>355</v>
+        <v>452</v>
       </c>
       <c r="E104" s="32" t="s">
-        <v>354</v>
+        <v>451</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" t="s">
-        <v>352</v>
+        <v>449</v>
       </c>
       <c r="C105" t="s">
-        <v>351</v>
+        <v>448</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>355</v>
+        <v>452</v>
       </c>
       <c r="E105" s="32" t="s">
-        <v>354</v>
+        <v>451</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" t="s">
-        <v>352</v>
+        <v>449</v>
       </c>
       <c r="C106" t="s">
         <v>69</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>356</v>
+        <v>453</v>
       </c>
       <c r="E106" s="32"/>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" t="s">
-        <v>352</v>
+        <v>449</v>
       </c>
       <c r="C107" t="s">
         <v>72</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>356</v>
+        <v>453</v>
       </c>
       <c r="E107" s="32" t="s">
-        <v>354</v>
+        <v>451</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" t="s">
-        <v>352</v>
+        <v>449</v>
       </c>
       <c r="C108" t="s">
-        <v>351</v>
+        <v>448</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>356</v>
+        <v>453</v>
       </c>
       <c r="E108" s="32" t="s">
-        <v>354</v>
+        <v>451</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" t="s">
-        <v>352</v>
+        <v>449</v>
       </c>
       <c r="C109" t="s">
         <v>69</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>357</v>
+        <v>454</v>
       </c>
       <c r="E109" s="32"/>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" t="s">
-        <v>352</v>
+        <v>449</v>
       </c>
       <c r="C110" t="s">
         <v>72</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>357</v>
+        <v>454</v>
       </c>
       <c r="E110" s="32" t="s">
-        <v>354</v>
+        <v>451</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" t="s">
-        <v>352</v>
+        <v>449</v>
       </c>
       <c r="C111" t="s">
-        <v>351</v>
+        <v>448</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>357</v>
+        <v>454</v>
       </c>
       <c r="E111" s="32" t="s">
-        <v>354</v>
+        <v>451</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" t="s">
-        <v>352</v>
+        <v>449</v>
       </c>
       <c r="C112" t="s">
         <v>69</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>358</v>
+        <v>455</v>
       </c>
       <c r="E112" s="1"/>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" t="s">
-        <v>352</v>
+        <v>449</v>
       </c>
       <c r="C113" t="s">
         <v>72</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>358</v>
+        <v>455</v>
       </c>
       <c r="E113" s="32" t="s">
-        <v>359</v>
+        <v>456</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" t="s">
-        <v>352</v>
+        <v>449</v>
       </c>
       <c r="C114" t="s">
-        <v>351</v>
+        <v>448</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>358</v>
+        <v>455</v>
       </c>
       <c r="E114" s="32" t="s">
-        <v>359</v>
+        <v>456</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" t="s">
-        <v>360</v>
+        <v>457</v>
       </c>
       <c r="C115" t="s">
         <v>69</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>360</v>
+        <v>457</v>
       </c>
       <c r="E115" s="1"/>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" t="s">
-        <v>360</v>
+        <v>457</v>
       </c>
       <c r="C116" t="s">
         <v>72</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>360</v>
+        <v>457</v>
       </c>
       <c r="E116" s="1"/>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" t="s">
-        <v>360</v>
+        <v>457</v>
       </c>
       <c r="C117" t="s">
-        <v>351</v>
+        <v>448</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>360</v>
+        <v>457</v>
       </c>
       <c r="E117" s="1"/>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" t="s">
-        <v>361</v>
+        <v>458</v>
       </c>
       <c r="C118" t="s">
         <v>11</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>362</v>
+        <v>459</v>
       </c>
       <c r="E118" s="1"/>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" t="s">
-        <v>361</v>
+        <v>458</v>
       </c>
       <c r="C119" t="s">
-        <v>187</v>
+        <v>284</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>362</v>
+        <v>459</v>
       </c>
       <c r="E119" s="1"/>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" t="s">
-        <v>361</v>
+        <v>458</v>
       </c>
       <c r="C120" t="s">
-        <v>363</v>
+        <v>460</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>362</v>
+        <v>459</v>
       </c>
       <c r="E120" s="1"/>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" t="s">
-        <v>361</v>
+        <v>458</v>
       </c>
       <c r="C121" t="s">
         <v>11</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>212</v>
+        <v>309</v>
       </c>
       <c r="E121" s="1"/>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" t="s">
-        <v>361</v>
+        <v>458</v>
       </c>
       <c r="C122" t="s">
-        <v>364</v>
+        <v>461</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>212</v>
+        <v>309</v>
       </c>
       <c r="E122" s="1"/>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" t="s">
-        <v>365</v>
+        <v>462</v>
       </c>
       <c r="C123" t="s">
-        <v>366</v>
+        <v>207</v>
       </c>
       <c r="D123" t="s">
-        <v>365</v>
+        <v>462</v>
       </c>
       <c r="E123" s="1"/>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" t="s">
-        <v>365</v>
+        <v>462</v>
       </c>
       <c r="C124" t="s">
         <v>11</v>
       </c>
       <c r="D124" t="s">
-        <v>365</v>
+        <v>462</v>
       </c>
       <c r="E124" s="1"/>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" t="s">
-        <v>365</v>
+        <v>462</v>
       </c>
       <c r="C125" t="s">
-        <v>367</v>
+        <v>463</v>
       </c>
       <c r="D125" t="s">
-        <v>365</v>
+        <v>462</v>
       </c>
       <c r="E125" s="1"/>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" t="s">
-        <v>365</v>
+        <v>462</v>
       </c>
       <c r="C126" t="s">
-        <v>368</v>
+        <v>464</v>
       </c>
       <c r="D126" t="s">
-        <v>365</v>
+        <v>462</v>
       </c>
       <c r="E126" s="1"/>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" t="s">
-        <v>365</v>
+        <v>462</v>
       </c>
       <c r="C127" t="s">
-        <v>369</v>
+        <v>465</v>
       </c>
       <c r="D127" t="s">
-        <v>365</v>
+        <v>462</v>
       </c>
       <c r="E127" s="1"/>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" t="s">
-        <v>365</v>
+        <v>462</v>
       </c>
       <c r="C128" t="s">
-        <v>370</v>
+        <v>466</v>
       </c>
       <c r="D128" t="s">
-        <v>365</v>
+        <v>462</v>
       </c>
       <c r="E128" s="1"/>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" t="s">
-        <v>365</v>
+        <v>462</v>
       </c>
       <c r="C129" t="s">
-        <v>371</v>
+        <v>467</v>
       </c>
       <c r="D129" t="s">
-        <v>365</v>
+        <v>462</v>
       </c>
       <c r="E129" s="1"/>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" t="s">
-        <v>372</v>
+        <v>468</v>
       </c>
       <c r="C130" t="s">
-        <v>373</v>
+        <v>469</v>
       </c>
       <c r="D130" t="s">
-        <v>372</v>
+        <v>468</v>
       </c>
       <c r="E130" s="1"/>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" t="s">
-        <v>372</v>
+        <v>468</v>
       </c>
       <c r="C131" t="s">
-        <v>374</v>
+        <v>470</v>
       </c>
       <c r="D131" t="s">
-        <v>372</v>
+        <v>468</v>
       </c>
       <c r="E131" s="1"/>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" t="s">
-        <v>372</v>
+        <v>468</v>
       </c>
       <c r="C132" t="s">
-        <v>375</v>
+        <v>471</v>
       </c>
       <c r="D132" t="s">
-        <v>372</v>
+        <v>468</v>
       </c>
       <c r="E132" s="1"/>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" t="s">
-        <v>372</v>
+        <v>468</v>
       </c>
       <c r="C133" t="s">
         <v>11</v>
       </c>
       <c r="D133" t="s">
-        <v>372</v>
+        <v>468</v>
       </c>
       <c r="E133" s="1"/>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" t="s">
-        <v>372</v>
+        <v>468</v>
       </c>
       <c r="C134" t="s">
-        <v>376</v>
+        <v>472</v>
       </c>
       <c r="D134" t="s">
-        <v>372</v>
+        <v>468</v>
       </c>
       <c r="E134" s="1"/>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" t="s">
-        <v>372</v>
+        <v>468</v>
       </c>
       <c r="C135" t="s">
-        <v>366</v>
+        <v>207</v>
       </c>
       <c r="D135" t="s">
-        <v>372</v>
+        <v>468</v>
       </c>
       <c r="E135" s="1"/>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" t="s">
-        <v>377</v>
+        <v>473</v>
       </c>
       <c r="C136" t="s">
-        <v>378</v>
+        <v>474</v>
       </c>
       <c r="D136" t="s">
-        <v>377</v>
+        <v>473</v>
       </c>
       <c r="E136" s="1"/>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" t="s">
-        <v>377</v>
+        <v>473</v>
       </c>
       <c r="C137" t="s">
-        <v>379</v>
+        <v>475</v>
       </c>
       <c r="D137" t="s">
-        <v>377</v>
+        <v>473</v>
       </c>
       <c r="E137" s="1"/>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" t="s">
-        <v>377</v>
+        <v>473</v>
       </c>
       <c r="C138" t="s">
         <v>11</v>
       </c>
       <c r="D138" t="s">
-        <v>377</v>
+        <v>473</v>
       </c>
       <c r="E138" s="1"/>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" t="s">
-        <v>377</v>
+        <v>473</v>
       </c>
       <c r="C139" t="s">
-        <v>380</v>
+        <v>476</v>
       </c>
       <c r="D139" t="s">
-        <v>377</v>
+        <v>473</v>
       </c>
       <c r="E139" s="1"/>
     </row>
@@ -8860,7 +12042,7 @@
         <v>85</v>
       </c>
       <c r="B186" t="s">
-        <v>381</v>
+        <v>477</v>
       </c>
       <c r="C186" t="s">
         <v>69</v>
@@ -8877,7 +12059,7 @@
         <v>85</v>
       </c>
       <c r="B187" t="s">
-        <v>381</v>
+        <v>477</v>
       </c>
       <c r="C187" t="s">
         <v>72</v>
@@ -8931,7 +12113,7 @@
         <v>94</v>
       </c>
       <c r="C190" t="s">
-        <v>382</v>
+        <v>478</v>
       </c>
       <c r="D190" s="1" t="s">
         <v>92</v>
@@ -9373,7 +12555,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0EAAD77-A3AF-4370-A469-C91C3D80AA60}">
   <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9387,71 +12569,71 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="5" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H1" s="8"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="9" t="s">
-        <v>383</v>
+        <v>479</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>384</v>
+        <v>480</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>385</v>
+        <v>481</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>386</v>
+        <v>482</v>
       </c>
       <c r="H2" s="8"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="11" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
       <c r="D3" s="12" t="s">
-        <v>387</v>
+        <v>483</v>
       </c>
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
       <c r="G3" s="13" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H3" s="8"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="11" t="s">
-        <v>388</v>
+        <v>484</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -9459,13 +12641,13 @@
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
       <c r="G4" s="13" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H4" s="8"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="11" t="s">
-        <v>389</v>
+        <v>485</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -9473,7 +12655,7 @@
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
       <c r="G5" s="13" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H5" s="8"/>
     </row>
@@ -9482,16 +12664,16 @@
         <v>1</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>390</v>
+        <v>486</v>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="8" t="s">
-        <v>391</v>
+        <v>487</v>
       </c>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="G6" s="13" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H6" s="8"/>
     </row>
@@ -9500,16 +12682,16 @@
         <v>2</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>392</v>
+        <v>488</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8" t="s">
-        <v>393</v>
+        <v>489</v>
       </c>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
       <c r="G7" s="13" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H7" s="8"/>
     </row>
@@ -9518,16 +12700,16 @@
         <v>3</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>394</v>
+        <v>490</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="8" t="s">
-        <v>395</v>
+        <v>491</v>
       </c>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
       <c r="G8" s="13" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H8" s="8"/>
     </row>
@@ -9536,16 +12718,16 @@
         <v>4</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>396</v>
+        <v>492</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8" t="s">
-        <v>395</v>
+        <v>491</v>
       </c>
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
       <c r="G9" s="13" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H9" s="8"/>
     </row>
@@ -9554,16 +12736,16 @@
         <v>5</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>397</v>
+        <v>493</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8" t="s">
-        <v>398</v>
+        <v>494</v>
       </c>
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
       <c r="G10" s="13" t="s">
-        <v>399</v>
+        <v>495</v>
       </c>
       <c r="H10" s="8"/>
     </row>
@@ -9572,16 +12754,16 @@
         <v>6</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>397</v>
+        <v>493</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8" t="s">
-        <v>400</v>
+        <v>496</v>
       </c>
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
       <c r="G11" s="13" t="s">
-        <v>399</v>
+        <v>495</v>
       </c>
       <c r="H11" s="8"/>
     </row>
@@ -9590,16 +12772,16 @@
         <v>7</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>401</v>
+        <v>497</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8" t="s">
-        <v>391</v>
+        <v>487</v>
       </c>
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
       <c r="G12" s="13" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H12" s="8"/>
     </row>
@@ -9608,16 +12790,16 @@
         <v>8</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>402</v>
+        <v>498</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8" t="s">
-        <v>393</v>
+        <v>489</v>
       </c>
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
       <c r="G13" s="13" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H13" s="8"/>
     </row>
@@ -9626,16 +12808,16 @@
         <v>9</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>403</v>
+        <v>499</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8" t="s">
-        <v>404</v>
+        <v>500</v>
       </c>
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
       <c r="G14" s="13" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H14" s="8"/>
     </row>
@@ -9644,22 +12826,22 @@
         <v>10</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>403</v>
+        <v>499</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="8" t="s">
-        <v>404</v>
+        <v>500</v>
       </c>
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
       <c r="G15" s="13" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H15" s="8"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="11" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
@@ -9667,23 +12849,23 @@
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
       <c r="G16" s="13" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H16" s="8"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="11" t="s">
-        <v>405</v>
+        <v>501</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8" t="s">
-        <v>406</v>
+        <v>502</v>
       </c>
       <c r="F17" s="8"/>
       <c r="G17" s="13" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H17" s="8"/>
     </row>
@@ -9692,18 +12874,18 @@
         <v>1</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>407</v>
+        <v>503</v>
       </c>
       <c r="C18" s="14" t="s">
         <v>69</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>408</v>
+        <v>504</v>
       </c>
       <c r="E18" s="8"/>
       <c r="F18" s="8"/>
       <c r="G18" s="13" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H18" s="8"/>
     </row>
@@ -9712,18 +12894,18 @@
         <v>2</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>407</v>
+        <v>503</v>
       </c>
       <c r="C19" s="14" t="s">
         <v>72</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>408</v>
+        <v>504</v>
       </c>
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
       <c r="G19" s="13" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H19" s="8"/>
     </row>
@@ -9732,20 +12914,20 @@
         <v>3</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>409</v>
+        <v>505</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>410</v>
+        <v>506</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>411</v>
+        <v>507</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>412</v>
+        <v>508</v>
       </c>
       <c r="F20" s="8"/>
       <c r="G20" s="13" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H20" s="8"/>
     </row>
@@ -9754,20 +12936,20 @@
         <v>4</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>413</v>
+        <v>509</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>414</v>
+        <v>510</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>415</v>
+        <v>511</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>416</v>
+        <v>512</v>
       </c>
       <c r="F21" s="8"/>
       <c r="G21" s="13" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H21" s="8"/>
     </row>
@@ -9776,20 +12958,20 @@
         <v>5</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>413</v>
+        <v>509</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>33</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>417</v>
+        <v>513</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>418</v>
+        <v>514</v>
       </c>
       <c r="F22" s="8"/>
       <c r="G22" s="13" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H22" s="8"/>
     </row>
@@ -9798,44 +12980,44 @@
         <v>6</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>413</v>
+        <v>509</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>31</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>419</v>
+        <v>515</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>420</v>
+        <v>516</v>
       </c>
       <c r="F23" s="8"/>
       <c r="G23" s="13" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H23" s="8"/>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="15" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="H24" s="8"/>
     </row>

--- a/V2 BETA/RRF/Valkyrie Connection Table.xlsx
+++ b/V2 BETA/RRF/Valkyrie Connection Table.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30105"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3837cd5b4a1a02ac/Document Library/GitHub/Project-Valkyrie/V2 BETA/RRF/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3266" documentId="8_{C788BE8B-89FF-47EE-BC54-747C3D562542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{012EAD07-AD91-44DD-8457-0E6574E57FA2}"/>
+  <xr:revisionPtr revIDLastSave="3267" documentId="8_{C788BE8B-89FF-47EE-BC54-747C3D562542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3699C84-9A73-4AE3-B60D-115B6B92C5A0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{344B6B93-88E2-4E8A-A19A-9E2625195A37}"/>
   </bookViews>
@@ -1247,12 +1247,18 @@
     <t>https://github.com/Fly3DTeam/Buffer</t>
   </si>
   <si>
+    <t>io7_</t>
+  </si>
+  <si>
     <t>Ident</t>
   </si>
   <si>
     <t>Duet Pins</t>
   </si>
   <si>
+    <t>From</t>
+  </si>
+  <si>
     <t>wire aize awg</t>
   </si>
   <si>
@@ -1268,6 +1274,9 @@
     <t>Orange</t>
   </si>
   <si>
+    <t>Flint Zone Probe</t>
+  </si>
+  <si>
     <t>GX20_10Pin_M/9</t>
   </si>
   <si>
@@ -1290,6 +1299,9 @@
   </si>
   <si>
     <t>?</t>
+  </si>
+  <si>
+    <t>CPAP Robo</t>
   </si>
   <si>
     <t>⚠️ DANGER: HIGH VOLTAGE SAFETY DISCLAIMER ⚠️</t>
@@ -2179,25 +2191,13 @@
   <si>
     <t>rpm</t>
   </si>
-  <si>
-    <t>Flint Zone Probe</t>
-  </si>
-  <si>
-    <t>From</t>
-  </si>
-  <si>
-    <t>CPAP Robo</t>
-  </si>
-  <si>
-    <t>Duet 3 6HC control board connections</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
   </numFmts>
   <fonts count="15">
     <font>
@@ -2748,7 +2748,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3391,10 +3391,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8044BAE1-D091-43AF-A54C-DAF3DA9144D0}" name="Table1" displayName="Table1" ref="A1:G83" totalsRowShown="0">
   <autoFilter ref="A1:G83" xr:uid="{8044BAE1-D091-43AF-A54C-DAF3DA9144D0}"/>
@@ -3466,9 +3462,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3506,7 +3502,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3612,7 +3608,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3754,7 +3750,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -9057,27 +9053,27 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18.75">
       <c r="A1" s="92" t="s">
-        <v>709</v>
+        <v>401</v>
       </c>
       <c r="B1" s="93"/>
       <c r="C1" s="93" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D1" s="93" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E1" s="99" t="s">
-        <v>707</v>
+        <v>404</v>
       </c>
       <c r="F1" s="97" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="G1" s="127"/>
       <c r="H1" s="128" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="I1" s="94" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -9289,7 +9285,7 @@
         <v>184</v>
       </c>
       <c r="G9" s="70" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="H9" s="95"/>
       <c r="I9" s="45" t="s">
@@ -9343,7 +9339,7 @@
         <v>184</v>
       </c>
       <c r="G11" s="70" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="H11" s="95"/>
       <c r="I11" s="45" t="s">
@@ -9397,7 +9393,7 @@
         <v>184</v>
       </c>
       <c r="G13" s="70" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="H13" s="90"/>
       <c r="I13" s="44" t="s">
@@ -9451,7 +9447,7 @@
         <v>184</v>
       </c>
       <c r="G15" s="70" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="H15" s="90"/>
       <c r="I15" s="44" t="s">
@@ -10103,7 +10099,7 @@
         <v>44</v>
       </c>
       <c r="B48" s="35" t="s">
-        <v>706</v>
+        <v>410</v>
       </c>
       <c r="C48" s="35" t="s">
         <v>46</v>
@@ -10122,7 +10118,7 @@
       </c>
       <c r="H48" s="90"/>
       <c r="I48" s="44" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -10130,7 +10126,7 @@
         <v>44</v>
       </c>
       <c r="B49" s="35" t="s">
-        <v>706</v>
+        <v>410</v>
       </c>
       <c r="C49" s="35" t="s">
         <v>9</v>
@@ -10149,7 +10145,7 @@
       </c>
       <c r="H49" s="90"/>
       <c r="I49" s="44" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -10234,7 +10230,7 @@
         <v>256</v>
       </c>
       <c r="E54" s="40" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="F54" s="36">
         <v>22</v>
@@ -10500,7 +10496,7 @@
         <v>303</v>
       </c>
       <c r="E70" s="39" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="F70" s="35">
         <v>22</v>
@@ -10553,7 +10549,7 @@
         <v>312</v>
       </c>
       <c r="E73" s="40" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="F73" s="36">
         <v>22</v>
@@ -10607,7 +10603,7 @@
         <v>318</v>
       </c>
       <c r="E75" s="40" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F75" s="36">
         <v>22</v>
@@ -10638,7 +10634,7 @@
         <v>323</v>
       </c>
       <c r="B77" s="78" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C77" s="35" t="s">
         <v>70</v>
@@ -10665,7 +10661,7 @@
         <v>323</v>
       </c>
       <c r="B78" s="78" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C78" s="35" t="s">
         <v>73</v>
@@ -10981,7 +10977,7 @@
         <v>184</v>
       </c>
       <c r="G91" s="70" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="H91" s="95"/>
       <c r="I91" s="45" t="s">
@@ -11008,7 +11004,7 @@
         <v>184</v>
       </c>
       <c r="G92" s="70" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="H92" s="95"/>
       <c r="I92" s="45" t="s">
@@ -11056,7 +11052,7 @@
     </row>
     <row r="96" spans="1:9">
       <c r="A96" s="75" t="s">
-        <v>708</v>
+        <v>419</v>
       </c>
       <c r="B96" s="35" t="s">
         <v>365</v>
@@ -11674,10 +11670,10 @@
   <sheetData>
     <row r="1" spans="1:11" ht="26.25" customHeight="1">
       <c r="A1" s="112" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="F1" s="129" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="18.75">
@@ -11727,7 +11723,7 @@
         <v>141</v>
       </c>
       <c r="B5" s="114" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="C5" s="114" t="s">
         <v>143</v>
@@ -11736,11 +11732,11 @@
         <v>18</v>
       </c>
       <c r="E5" s="116" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="F5" s="117"/>
       <c r="G5" s="44" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -11748,7 +11744,7 @@
         <v>141</v>
       </c>
       <c r="B6" s="35" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="C6" s="35" t="s">
         <v>146</v>
@@ -11757,19 +11753,19 @@
         <v>18</v>
       </c>
       <c r="E6" s="78" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="F6" s="105"/>
       <c r="G6" s="44" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="87" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="B7" s="35" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="C7" s="35" t="s">
         <v>149</v>
@@ -11778,11 +11774,11 @@
         <v>18</v>
       </c>
       <c r="E7" s="118" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F7" s="105"/>
       <c r="G7" s="106" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -11790,7 +11786,7 @@
         <v>141</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C8" s="36" t="s">
         <v>143</v>
@@ -11799,11 +11795,11 @@
         <v>18</v>
       </c>
       <c r="E8" s="119" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="F8" s="104"/>
       <c r="G8" s="45" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -11811,7 +11807,7 @@
         <v>141</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C9" s="36" t="s">
         <v>146</v>
@@ -11820,11 +11816,11 @@
         <v>18</v>
       </c>
       <c r="E9" s="119" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="F9" s="104"/>
       <c r="G9" s="45" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -11832,7 +11828,7 @@
         <v>141</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C10" s="36" t="s">
         <v>143</v>
@@ -11841,22 +11837,22 @@
         <v>18</v>
       </c>
       <c r="E10" s="119" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="F10" s="104"/>
       <c r="G10" s="45" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="K10" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="87" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C11" s="35" t="s">
         <v>149</v>
@@ -11865,19 +11861,19 @@
         <v>18</v>
       </c>
       <c r="E11" s="118" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F11" s="105"/>
       <c r="G11" s="106" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="87" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="B12" s="35" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="C12" s="35" t="s">
         <v>149</v>
@@ -11886,19 +11882,19 @@
         <v>18</v>
       </c>
       <c r="E12" s="118" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F12" s="105"/>
       <c r="G12" s="106" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="87" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="B13" s="71" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="C13" s="35" t="s">
         <v>149</v>
@@ -11907,11 +11903,11 @@
         <v>18</v>
       </c>
       <c r="E13" s="118" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F13" s="105"/>
       <c r="G13" s="106" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -11919,7 +11915,7 @@
         <v>141</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="C14" s="36" t="s">
         <v>143</v>
@@ -11928,13 +11924,13 @@
         <v>18</v>
       </c>
       <c r="E14" s="119" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="F14" s="104">
         <v>40</v>
       </c>
       <c r="G14" s="45" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -11942,7 +11938,7 @@
         <v>141</v>
       </c>
       <c r="B15" s="36" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="C15" s="36" t="s">
         <v>146</v>
@@ -11951,13 +11947,13 @@
         <v>18</v>
       </c>
       <c r="E15" s="119" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="F15" s="104">
         <v>40</v>
       </c>
       <c r="G15" s="45" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -11965,7 +11961,7 @@
         <v>141</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="C16" s="36" t="s">
         <v>149</v>
@@ -11974,13 +11970,13 @@
         <v>18</v>
       </c>
       <c r="E16" s="120" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F16" s="104">
         <v>40</v>
       </c>
       <c r="G16" s="45" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -11997,13 +11993,13 @@
         <v>18</v>
       </c>
       <c r="E17" s="78" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="F17" s="105">
         <v>40</v>
       </c>
       <c r="G17" s="44" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -12020,13 +12016,13 @@
         <v>18</v>
       </c>
       <c r="E18" s="78" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="F18" s="105">
         <v>40</v>
       </c>
       <c r="G18" s="44" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -12043,13 +12039,13 @@
         <v>18</v>
       </c>
       <c r="E19" s="118" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F19" s="105">
         <v>40</v>
       </c>
       <c r="G19" s="44" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -12057,7 +12053,7 @@
         <v>141</v>
       </c>
       <c r="B20" s="36" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="C20" s="36" t="s">
         <v>143</v>
@@ -12066,13 +12062,13 @@
         <v>18</v>
       </c>
       <c r="E20" s="119" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="F20" s="104">
         <v>40</v>
       </c>
       <c r="G20" s="45" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -12080,7 +12076,7 @@
         <v>141</v>
       </c>
       <c r="B21" s="36" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C21" s="36" t="s">
         <v>143</v>
@@ -12089,11 +12085,11 @@
         <v>18</v>
       </c>
       <c r="E21" s="119" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="F21" s="104"/>
       <c r="G21" s="45" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -12101,7 +12097,7 @@
         <v>141</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C22" s="36" t="s">
         <v>146</v>
@@ -12110,11 +12106,11 @@
         <v>18</v>
       </c>
       <c r="E22" s="119" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="F22" s="104"/>
       <c r="G22" s="45" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -12122,7 +12118,7 @@
         <v>141</v>
       </c>
       <c r="B23" s="36" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="C23" s="36" t="s">
         <v>149</v>
@@ -12131,11 +12127,11 @@
         <v>18</v>
       </c>
       <c r="E23" s="119" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="F23" s="104"/>
       <c r="G23" s="45" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -12143,7 +12139,7 @@
         <v>141</v>
       </c>
       <c r="B24" s="35" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="C24" s="35" t="s">
         <v>143</v>
@@ -12152,11 +12148,11 @@
         <v>18</v>
       </c>
       <c r="E24" s="78" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="F24" s="105"/>
       <c r="G24" s="44" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -12164,7 +12160,7 @@
         <v>141</v>
       </c>
       <c r="B25" s="35" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="C25" s="35" t="s">
         <v>143</v>
@@ -12173,11 +12169,11 @@
         <v>18</v>
       </c>
       <c r="E25" s="78" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="F25" s="105"/>
       <c r="G25" s="44" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -12185,7 +12181,7 @@
         <v>141</v>
       </c>
       <c r="B26" s="35" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C26" s="35" t="s">
         <v>146</v>
@@ -12194,11 +12190,11 @@
         <v>18</v>
       </c>
       <c r="E26" s="78" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="F26" s="105"/>
       <c r="G26" s="44" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -12206,7 +12202,7 @@
         <v>141</v>
       </c>
       <c r="B27" s="35" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="C27" s="35" t="s">
         <v>149</v>
@@ -12215,11 +12211,11 @@
         <v>18</v>
       </c>
       <c r="E27" s="118" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F27" s="105"/>
       <c r="G27" s="44" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -12227,7 +12223,7 @@
         <v>141</v>
       </c>
       <c r="B28" s="36" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="C28" s="36" t="s">
         <v>143</v>
@@ -12236,11 +12232,11 @@
         <v>18</v>
       </c>
       <c r="E28" s="119" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="F28" s="104"/>
       <c r="G28" s="45" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -12248,7 +12244,7 @@
         <v>141</v>
       </c>
       <c r="B29" s="36" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="C29" s="36" t="s">
         <v>143</v>
@@ -12257,11 +12253,11 @@
         <v>18</v>
       </c>
       <c r="E29" s="119" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="F29" s="104"/>
       <c r="G29" s="45" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -12269,7 +12265,7 @@
         <v>141</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C30" s="36" t="s">
         <v>146</v>
@@ -12278,11 +12274,11 @@
         <v>18</v>
       </c>
       <c r="E30" s="119" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="F30" s="104"/>
       <c r="G30" s="45" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -12290,7 +12286,7 @@
         <v>141</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="C31" s="36" t="s">
         <v>149</v>
@@ -12299,11 +12295,11 @@
         <v>18</v>
       </c>
       <c r="E31" s="120" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F31" s="104"/>
       <c r="G31" s="45" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -12391,7 +12387,7 @@
     <row r="1" spans="1:15">
       <c r="A1" s="5"/>
       <c r="B1" s="6" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
@@ -12407,7 +12403,7 @@
     <row r="2" spans="1:15">
       <c r="A2" s="5"/>
       <c r="B2" s="7" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -12420,649 +12416,649 @@
       <c r="K2" s="5"/>
       <c r="L2" s="16"/>
       <c r="M2" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="N2" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="O2" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="5"/>
       <c r="B3" s="8" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="K3" s="14" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="L3" s="17" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="M3" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="N3" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="O3" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="5"/>
       <c r="B4" s="8" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L4" s="17"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="5"/>
       <c r="B5" s="8" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K5" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L5" s="17"/>
       <c r="M5" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="5"/>
       <c r="B6" s="8" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="D6" s="10" t="s">
+        <v>489</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>490</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>489</v>
+      </c>
+      <c r="G6" s="10" t="s">
         <v>485</v>
       </c>
-      <c r="E6" s="10" t="s">
-        <v>486</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>485</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>481</v>
-      </c>
       <c r="H6" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K6" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L6" s="17" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="5"/>
       <c r="B7" s="8" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="E7" s="10" t="s">
+        <v>495</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>494</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>485</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>480</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>480</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>480</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>480</v>
+      </c>
+      <c r="L7" s="17" t="s">
         <v>491</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>490</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>481</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>476</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>476</v>
-      </c>
-      <c r="J7" s="10" t="s">
-        <v>476</v>
-      </c>
-      <c r="K7" s="15" t="s">
-        <v>476</v>
-      </c>
-      <c r="L7" s="17" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="5"/>
       <c r="B8" s="8" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K8" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L8" s="17"/>
       <c r="O8" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="5"/>
       <c r="B9" s="8" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L9" s="17"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="5"/>
       <c r="B10" s="8" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L10" s="17"/>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="5"/>
       <c r="B11" s="8" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L11" s="17" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="5"/>
       <c r="B12" s="8" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L12" s="17" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="5"/>
       <c r="B13" s="8" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L13" s="17"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="5"/>
       <c r="B14" s="8" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K14" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L14" s="17"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="5"/>
       <c r="B15" s="8" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K15" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L15" s="17"/>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="5"/>
       <c r="B16" s="8" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L16" s="17"/>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="5"/>
       <c r="B17" s="8" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L17" s="17"/>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="5"/>
       <c r="B18" s="8" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C18" s="10" t="s">
+        <v>521</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>522</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>523</v>
+      </c>
+      <c r="F18" s="10" t="s">
         <v>517</v>
       </c>
-      <c r="D18" s="10" t="s">
-        <v>518</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>519</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>513</v>
-      </c>
       <c r="G18" s="10" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L18" s="17"/>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="5"/>
       <c r="B19" s="8" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L19" s="17"/>
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="5"/>
       <c r="B20" s="8" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L20" s="17"/>
     </row>
@@ -13072,65 +13068,65 @@
         <v>53</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K21" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L21" s="17"/>
     </row>
     <row r="22" spans="1:15">
       <c r="A22" s="5"/>
       <c r="B22" s="12" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K22" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L22" s="17"/>
     </row>
@@ -13138,1002 +13134,1002 @@
       <c r="A23" s="5"/>
       <c r="B23" s="13"/>
       <c r="C23" s="10" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K23" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="5"/>
       <c r="B24" s="8" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K24" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L24" s="17"/>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="5"/>
       <c r="B25" s="8" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="I25" s="10"/>
       <c r="J25" s="10"/>
       <c r="K25" s="15"/>
       <c r="L25" s="17" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
     </row>
     <row r="26" spans="1:15" ht="15" customHeight="1">
       <c r="A26" s="5"/>
       <c r="B26" s="8" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K26" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L26" s="17" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="5"/>
       <c r="B27" s="8" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K27" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L27" s="17"/>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="5"/>
       <c r="B28" s="8" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K28" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L28" s="17"/>
       <c r="O28" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="5"/>
       <c r="B29" s="8" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K29" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L29" s="17"/>
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="5"/>
       <c r="B30" s="8" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K30" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L30" s="17"/>
       <c r="N30" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
     </row>
     <row r="31" spans="1:15">
       <c r="A31" s="5"/>
       <c r="B31" s="8" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K31" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L31" s="17"/>
     </row>
     <row r="32" spans="1:15">
       <c r="A32" s="5"/>
       <c r="B32" s="8" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K32" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L32" s="17" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="5"/>
       <c r="B33" s="8" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K33" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L33" s="17" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" s="5"/>
       <c r="B34" s="8" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K34" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L34" s="17"/>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" s="5"/>
       <c r="B35" s="8" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K35" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L35" s="17" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="M35" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="5"/>
       <c r="B36" s="8" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="C36" s="10" t="s">
+        <v>586</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>587</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>588</v>
+      </c>
+      <c r="F36" s="10" t="s">
         <v>582</v>
       </c>
-      <c r="D36" s="10" t="s">
-        <v>583</v>
-      </c>
-      <c r="E36" s="10" t="s">
-        <v>584</v>
-      </c>
-      <c r="F36" s="10" t="s">
-        <v>578</v>
-      </c>
       <c r="G36" s="10" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J36" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K36" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L36" s="17"/>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" s="5"/>
       <c r="B37" s="8" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K37" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L37" s="17"/>
       <c r="N37" s="33" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" s="5"/>
       <c r="B38" s="8" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="G38" s="10" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K38" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L38" s="17"/>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" s="5"/>
       <c r="B39" s="8" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K39" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L39" s="17"/>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="5"/>
       <c r="B40" s="8" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="G40" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K40" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L40" s="17" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="30">
       <c r="A41" s="5"/>
       <c r="B41" s="8" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="I41" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J41" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K41" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L41" s="17" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="5"/>
       <c r="B42" s="8" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K42" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L42" s="17"/>
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="5"/>
       <c r="B43" s="8" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J43" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K43" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L43" s="17"/>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="5"/>
       <c r="B44" s="8" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J44" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K44" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L44" s="17"/>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="5"/>
       <c r="B45" s="8" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J45" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K45" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L45" s="17"/>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="5"/>
       <c r="B46" s="8" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="G46" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="H46" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I46" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J46" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K46" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L46" s="17"/>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="5"/>
       <c r="B47" s="8" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I47" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J47" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K47" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L47" s="17"/>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="5"/>
       <c r="B48" s="8" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="G48" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I48" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J48" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K48" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L48" s="17"/>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" s="5"/>
       <c r="B49" s="8" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I49" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J49" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K49" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L49" s="17"/>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" s="5"/>
       <c r="B50" s="8" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="G50" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="H50" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I50" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J50" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K50" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L50" s="17"/>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" s="5"/>
       <c r="B51" s="8" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I51" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J51" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K51" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L51" s="17"/>
     </row>
@@ -14143,31 +14139,31 @@
         <v>15</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="G52" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="H52" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I52" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J52" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K52" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L52" s="17"/>
     </row>
@@ -14177,446 +14173,446 @@
         <v>15</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I53" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J53" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K53" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L53" s="17"/>
     </row>
     <row r="54" spans="1:12">
       <c r="A54" s="5"/>
       <c r="B54" s="8" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="G54" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="H54" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I54" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J54" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K54" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L54" s="17"/>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" s="5"/>
       <c r="B55" s="8" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I55" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J55" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K55" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L55" s="17"/>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" s="5"/>
       <c r="B56" s="8" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F56" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="H56" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I56" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J56" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K56" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L56" s="17"/>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" s="5"/>
       <c r="B57" s="8" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F57" s="10" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="I57" s="10" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="J57" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K57" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L57" s="17"/>
     </row>
     <row r="58" spans="1:12">
       <c r="A58" s="5"/>
       <c r="B58" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>624</v>
+      </c>
+      <c r="D58" s="10" t="s">
+        <v>480</v>
+      </c>
+      <c r="E58" s="10" t="s">
+        <v>480</v>
+      </c>
+      <c r="F58" s="10" t="s">
         <v>619</v>
       </c>
-      <c r="C58" s="10" t="s">
+      <c r="G58" s="10" t="s">
         <v>620</v>
       </c>
-      <c r="D58" s="10" t="s">
-        <v>476</v>
-      </c>
-      <c r="E58" s="10" t="s">
-        <v>476</v>
-      </c>
-      <c r="F58" s="10" t="s">
-        <v>615</v>
-      </c>
-      <c r="G58" s="10" t="s">
-        <v>616</v>
-      </c>
       <c r="H58" s="10" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="I58" s="10" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="J58" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K58" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L58" s="17"/>
     </row>
     <row r="59" spans="1:12">
       <c r="A59" s="5"/>
       <c r="B59" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="C59" s="10" t="s">
+        <v>626</v>
+      </c>
+      <c r="D59" s="10" t="s">
+        <v>480</v>
+      </c>
+      <c r="E59" s="10" t="s">
+        <v>480</v>
+      </c>
+      <c r="F59" s="10" t="s">
+        <v>619</v>
+      </c>
+      <c r="G59" s="10" t="s">
+        <v>620</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>621</v>
       </c>
-      <c r="C59" s="10" t="s">
+      <c r="I59" s="10" t="s">
         <v>622</v>
       </c>
-      <c r="D59" s="10" t="s">
-        <v>476</v>
-      </c>
-      <c r="E59" s="10" t="s">
-        <v>476</v>
-      </c>
-      <c r="F59" s="10" t="s">
-        <v>615</v>
-      </c>
-      <c r="G59" s="10" t="s">
-        <v>616</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>617</v>
-      </c>
-      <c r="I59" s="10" t="s">
-        <v>618</v>
-      </c>
       <c r="J59" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K59" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L59" s="17"/>
     </row>
     <row r="60" spans="1:12">
       <c r="A60" s="5"/>
       <c r="B60" s="8" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F60" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="G60" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="H60" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J60" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K60" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L60" s="17"/>
     </row>
     <row r="61" spans="1:12">
       <c r="A61" s="5"/>
       <c r="B61" s="8" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I61" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J61" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K61" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L61" s="17"/>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" s="5"/>
       <c r="B62" s="8" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="G62" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="H62" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="I62" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J62" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K62" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L62" s="17"/>
     </row>
     <row r="63" spans="1:12">
       <c r="A63" s="5"/>
       <c r="B63" s="8" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F63" s="10" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="I63" s="10" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="J63" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K63" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L63" s="17"/>
     </row>
     <row r="64" spans="1:12">
       <c r="A64" s="5"/>
       <c r="B64" s="8" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E64" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F64" s="10" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="G64" s="10" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="H64" s="10" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="J64" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K64" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L64" s="17"/>
     </row>
     <row r="65" spans="1:15">
       <c r="A65" s="5"/>
       <c r="B65" s="8" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F65" s="10" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="I65" s="10" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="J65" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K65" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L65" s="17"/>
     </row>
     <row r="66" spans="1:15">
       <c r="A66" s="5"/>
       <c r="B66" s="12" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="C66" s="5"/>
       <c r="D66" s="5"/>
@@ -14631,7 +14627,7 @@
     <row r="67" spans="1:15">
       <c r="A67" s="5"/>
       <c r="B67" s="5" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="C67" s="5"/>
       <c r="D67" s="5"/>
@@ -14643,13 +14639,13 @@
       <c r="J67" s="5"/>
       <c r="K67" s="5"/>
       <c r="O67" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="68" spans="1:15">
       <c r="A68" s="5"/>
       <c r="B68" s="5" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="C68" s="5"/>
       <c r="D68" s="5"/>
@@ -14661,7 +14657,7 @@
       <c r="J68" s="5"/>
       <c r="K68" s="5"/>
       <c r="O68" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
     </row>
     <row r="69" spans="1:15">
@@ -14850,13 +14846,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="E1" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
@@ -14865,12 +14861,12 @@
         <v>6</v>
       </c>
       <c r="K1" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="C2" t="s">
         <v>70</v>
@@ -14881,12 +14877,12 @@
       <c r="E2" s="1"/>
       <c r="G2" s="4"/>
       <c r="K2" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="C3" t="s">
         <v>73</v>
@@ -14897,12 +14893,12 @@
       <c r="E3" s="1"/>
       <c r="G3" s="4"/>
       <c r="K3" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="C4" t="s">
         <v>70</v>
@@ -14916,15 +14912,15 @@
         <v>15</v>
       </c>
       <c r="K4" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="L4" s="21" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="C5" t="s">
         <v>73</v>
@@ -14935,12 +14931,12 @@
       <c r="E5" s="1"/>
       <c r="G5" s="4"/>
       <c r="K5" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="C6" t="s">
         <v>70</v>
@@ -14953,7 +14949,7 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="C7" t="s">
         <v>73</v>
@@ -14966,7 +14962,7 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="C8" t="s">
         <v>70</v>
@@ -14979,7 +14975,7 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="C9" t="s">
         <v>73</v>
@@ -14992,7 +14988,7 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="C10" t="s">
         <v>70</v>
@@ -15004,7 +15000,7 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="C11" t="s">
         <v>73</v>
@@ -15513,13 +15509,13 @@
         <v>23</v>
       </c>
       <c r="B39" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="C39" t="s">
         <v>25</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="E39" s="1"/>
     </row>
@@ -15528,13 +15524,13 @@
         <v>23</v>
       </c>
       <c r="B40" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="C40" t="s">
         <v>28</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="E40" s="1"/>
     </row>
@@ -15543,13 +15539,13 @@
         <v>23</v>
       </c>
       <c r="B41" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="C41" t="s">
         <v>30</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="E41" s="1"/>
     </row>
@@ -15558,13 +15554,13 @@
         <v>23</v>
       </c>
       <c r="B42" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="C42" t="s">
         <v>32</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="E42" s="1"/>
     </row>
@@ -15573,13 +15569,13 @@
         <v>23</v>
       </c>
       <c r="B43" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="C43" t="s">
         <v>25</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="E43" s="1"/>
     </row>
@@ -15588,13 +15584,13 @@
         <v>23</v>
       </c>
       <c r="B44" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="C44" t="s">
         <v>28</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="E44" s="1"/>
     </row>
@@ -15603,13 +15599,13 @@
         <v>23</v>
       </c>
       <c r="B45" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="C45" t="s">
         <v>30</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="E45" s="1"/>
     </row>
@@ -15618,25 +15614,25 @@
         <v>23</v>
       </c>
       <c r="B46" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="C46" t="s">
         <v>32</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="E46" s="1"/>
     </row>
     <row r="47" spans="1:8">
       <c r="D47" s="1" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="E47" s="1"/>
     </row>
     <row r="48" spans="1:8">
       <c r="D48" s="1" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="E48" s="1"/>
     </row>
@@ -15651,7 +15647,7 @@
         <v>70</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="E49" s="1"/>
     </row>
@@ -15666,43 +15662,43 @@
         <v>73</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="E50" s="1"/>
     </row>
     <row r="51" spans="1:5">
       <c r="D51" s="1" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="E51" s="1"/>
     </row>
     <row r="52" spans="1:5">
       <c r="D52" s="1" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="E52" s="1"/>
     </row>
     <row r="53" spans="1:5">
       <c r="D53" s="1" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="E53" s="1"/>
     </row>
     <row r="54" spans="1:5">
       <c r="D54" s="1" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="E54" s="1"/>
     </row>
     <row r="55" spans="1:5">
       <c r="D55" s="1" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="E55" s="1"/>
     </row>
     <row r="56" spans="1:5">
       <c r="D56" s="1" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="E56" s="1"/>
     </row>
@@ -15714,10 +15710,10 @@
         <v>70</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -15728,10 +15724,10 @@
         <v>73</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -15742,10 +15738,10 @@
         <v>70</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -15756,10 +15752,10 @@
         <v>73</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -15770,10 +15766,10 @@
         <v>70</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -15784,10 +15780,10 @@
         <v>73</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -15798,10 +15794,10 @@
         <v>70</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -15812,10 +15808,10 @@
         <v>73</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -15826,10 +15822,10 @@
         <v>70</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -15840,10 +15836,10 @@
         <v>73</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -15854,10 +15850,10 @@
         <v>70</v>
       </c>
       <c r="D67" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="E67" s="1" t="s">
         <v>663</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>659</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -15868,10 +15864,10 @@
         <v>73</v>
       </c>
       <c r="D68" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="E68" s="1" t="s">
         <v>663</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>659</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -15882,10 +15878,10 @@
         <v>70</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -15896,10 +15892,10 @@
         <v>73</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -15910,10 +15906,10 @@
         <v>70</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -15924,10 +15920,10 @@
         <v>73</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -15938,10 +15934,10 @@
         <v>70</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -15952,10 +15948,10 @@
         <v>73</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -15966,10 +15962,10 @@
         <v>70</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -15980,10 +15976,10 @@
         <v>73</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -15997,7 +15993,7 @@
         <v>86</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -16011,12 +16007,12 @@
         <v>86</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C79" t="s">
         <v>70</v>
@@ -16028,7 +16024,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C80" t="s">
         <v>73</v>
@@ -16040,10 +16036,10 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C81" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>50</v>
@@ -16052,717 +16048,717 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C82" t="s">
         <v>70</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="E82" s="1"/>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C83" t="s">
         <v>73</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="E83" s="1"/>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C84" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="E84" s="1"/>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C85" t="s">
         <v>70</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="E85" s="1"/>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C86" t="s">
         <v>73</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="E86" s="1"/>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C87" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="E87" s="1"/>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C88" t="s">
         <v>70</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="E88" s="1"/>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C89" t="s">
         <v>73</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="E89" s="1"/>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C90" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="E90" s="1"/>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C91" t="s">
         <v>70</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="E91" s="1"/>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C92" t="s">
         <v>73</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="E92" s="1"/>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C93" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="E93" s="1"/>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C94" t="s">
         <v>70</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="E94" s="1"/>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C95" t="s">
         <v>73</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="E95" s="1"/>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C96" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="E96" s="1"/>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C97" t="s">
         <v>70</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="E97" s="1"/>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C98" t="s">
         <v>73</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="E98" s="1"/>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C99" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="E99" s="1"/>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="C100" t="s">
         <v>70</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="E100" s="20"/>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="C101" t="s">
         <v>73</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="E101" s="20" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="C102" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="E102" s="20" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="C103" t="s">
         <v>70</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="E103" s="20"/>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="C104" t="s">
         <v>73</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="E104" s="20" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="C105" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="E105" s="20" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="C106" t="s">
         <v>70</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="E106" s="20"/>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="C107" t="s">
         <v>73</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="E107" s="20" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="C108" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="E108" s="20" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="C109" t="s">
         <v>70</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="E109" s="20"/>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="C110" t="s">
         <v>73</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="E110" s="20" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="C111" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="E111" s="20" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="C112" t="s">
         <v>70</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="E112" s="1"/>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="C113" t="s">
         <v>73</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="E113" s="20" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="C114" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="E114" s="20" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="C115" t="s">
         <v>70</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="E115" s="1"/>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="C116" t="s">
         <v>73</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="E116" s="1"/>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="C117" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="E117" s="1"/>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="C118" t="s">
         <v>11</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="E118" s="1"/>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="C119" t="s">
         <v>375</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="E119" s="1"/>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="C120" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="E120" s="1"/>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="C121" t="s">
         <v>11</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="E121" s="1"/>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="C122" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="E122" s="1"/>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="C123" t="s">
         <v>375</v>
       </c>
       <c r="D123" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="E123" s="1"/>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="C124" t="s">
         <v>11</v>
       </c>
       <c r="D124" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="E124" s="1"/>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="C125" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="D125" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="E125" s="1"/>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="C126" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="D126" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="E126" s="1"/>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="C127" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="D127" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="E127" s="1"/>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="C128" t="s">
+        <v>698</v>
+      </c>
+      <c r="D128" t="s">
         <v>694</v>
-      </c>
-      <c r="D128" t="s">
-        <v>690</v>
       </c>
       <c r="E128" s="1"/>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="C129" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="D129" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="E129" s="1"/>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C130" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="D130" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="E130" s="1"/>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C131" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="D131" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="E131" s="1"/>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C132" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="D132" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="E132" s="1"/>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C133" t="s">
         <v>11</v>
       </c>
       <c r="D133" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="E133" s="1"/>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C134" t="s">
         <v>61</v>
       </c>
       <c r="D134" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="E134" s="1"/>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C135" t="s">
         <v>375</v>
       </c>
       <c r="D135" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="E135" s="1"/>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="C136" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="D136" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="E136" s="1"/>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="C137" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="D137" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="E137" s="1"/>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="C138" t="s">
         <v>11</v>
       </c>
       <c r="D138" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="E138" s="1"/>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="C139" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="D139" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="E139" s="1"/>
     </row>
@@ -16853,7 +16849,7 @@
         <v>46</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="E159" s="3" t="s">
         <v>48</v>
@@ -16872,7 +16868,7 @@
         <v>11</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="E160" s="3" t="s">
         <v>11</v>
@@ -16903,7 +16899,7 @@
         <v>49</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="E163" s="1"/>
     </row>
@@ -16912,7 +16908,7 @@
         <v>49</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="E164" s="1"/>
     </row>
@@ -16927,7 +16923,7 @@
         <v>46</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>55</v>
@@ -16950,7 +16946,7 @@
         <v>11</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>11</v>
@@ -16973,7 +16969,7 @@
         <v>46</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>48</v>
@@ -16996,7 +16992,7 @@
         <v>11</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>11</v>
@@ -17045,7 +17041,7 @@
         <v>61</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>63</v>
@@ -17068,7 +17064,7 @@
         <v>11</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>11</v>
@@ -17091,7 +17087,7 @@
         <v>64</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>65</v>
@@ -17290,7 +17286,7 @@
         <v>86</v>
       </c>
       <c r="B186" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="C186" t="s">
         <v>70</v>
@@ -17307,7 +17303,7 @@
         <v>86</v>
       </c>
       <c r="B187" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="C187" t="s">
         <v>73</v>
@@ -17361,7 +17357,7 @@
         <v>95</v>
       </c>
       <c r="C190" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="D190" s="1" t="s">
         <v>93</v>

--- a/V2 BETA/RRF/Valkyrie Connection Table.xlsx
+++ b/V2 BETA/RRF/Valkyrie Connection Table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30105"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3837cd5b4a1a02ac/Document Library/GitHub/Project-Valkyrie/V2 BETA/RRF/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3267" documentId="8_{C788BE8B-89FF-47EE-BC54-747C3D562542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3699C84-9A73-4AE3-B60D-115B6B92C5A0}"/>
+  <xr:revisionPtr revIDLastSave="3269" documentId="8_{C788BE8B-89FF-47EE-BC54-747C3D562542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D5FA5CC-68E0-4B6D-BDAB-0C1755B6C739}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{344B6B93-88E2-4E8A-A19A-9E2625195A37}"/>
+    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="16440" firstSheet="2" activeTab="2" xr2:uid="{344B6B93-88E2-4E8A-A19A-9E2625195A37}"/>
   </bookViews>
   <sheets>
     <sheet name="DUET 3 6HC" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3249" uniqueCount="710">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3249" uniqueCount="711">
   <si>
     <t>Type</t>
   </si>
@@ -2191,13 +2191,16 @@
   <si>
     <t>rpm</t>
   </si>
+  <si>
+    <t>12V DC</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
   </numFmts>
   <fonts count="15">
     <font>
@@ -2748,7 +2751,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3462,9 +3465,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3502,7 +3505,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3608,7 +3611,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3750,7 +3753,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -10748,7 +10751,7 @@
         <v>70</v>
       </c>
       <c r="D81" s="71" t="s">
-        <v>81</v>
+        <v>710</v>
       </c>
       <c r="E81" s="39" t="s">
         <v>78</v>

--- a/V2 BETA/RRF/Valkyrie Connection Table.xlsx
+++ b/V2 BETA/RRF/Valkyrie Connection Table.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3837cd5b4a1a02ac/Document Library/GitHub/Project-Valkyrie/V2 BETA/RRF/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3269" documentId="8_{C788BE8B-89FF-47EE-BC54-747C3D562542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D5FA5CC-68E0-4B6D-BDAB-0C1755B6C739}"/>
+  <xr:revisionPtr revIDLastSave="3274" documentId="8_{C788BE8B-89FF-47EE-BC54-747C3D562542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E72A23A-6DE3-4B5A-86A0-CE609AAAF128}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="16440" firstSheet="2" activeTab="2" xr2:uid="{344B6B93-88E2-4E8A-A19A-9E2625195A37}"/>
   </bookViews>
@@ -1247,7 +1247,7 @@
     <t>https://github.com/Fly3DTeam/Buffer</t>
   </si>
   <si>
-    <t>io7_</t>
+    <t>Device</t>
   </si>
   <si>
     <t>Ident</t>
@@ -1296,6 +1296,9 @@
   </si>
   <si>
     <t>12v power , Cpap, water pump+fan+Flow meter+fan</t>
+  </si>
+  <si>
+    <t>12V DC</t>
   </si>
   <si>
     <t>?</t>
@@ -2191,16 +2194,13 @@
   <si>
     <t>rpm</t>
   </si>
-  <si>
-    <t>12V DC</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
   </numFmts>
   <fonts count="15">
     <font>
@@ -2751,7 +2751,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3465,9 +3465,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3505,7 +3505,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3611,7 +3611,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3753,7 +3753,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -10751,7 +10751,7 @@
         <v>70</v>
       </c>
       <c r="D81" s="71" t="s">
-        <v>710</v>
+        <v>418</v>
       </c>
       <c r="E81" s="39" t="s">
         <v>78</v>
@@ -10980,7 +10980,7 @@
         <v>184</v>
       </c>
       <c r="G91" s="70" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H91" s="95"/>
       <c r="I91" s="45" t="s">
@@ -11007,7 +11007,7 @@
         <v>184</v>
       </c>
       <c r="G92" s="70" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H92" s="95"/>
       <c r="I92" s="45" t="s">
@@ -11055,7 +11055,7 @@
     </row>
     <row r="96" spans="1:9">
       <c r="A96" s="75" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B96" s="35" t="s">
         <v>365</v>
@@ -11673,10 +11673,10 @@
   <sheetData>
     <row r="1" spans="1:11" ht="26.25" customHeight="1">
       <c r="A1" s="112" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F1" s="129" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="18.75">
@@ -11726,7 +11726,7 @@
         <v>141</v>
       </c>
       <c r="B5" s="114" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C5" s="114" t="s">
         <v>143</v>
@@ -11735,11 +11735,11 @@
         <v>18</v>
       </c>
       <c r="E5" s="116" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F5" s="117"/>
       <c r="G5" s="44" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -11747,7 +11747,7 @@
         <v>141</v>
       </c>
       <c r="B6" s="35" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C6" s="35" t="s">
         <v>146</v>
@@ -11756,19 +11756,19 @@
         <v>18</v>
       </c>
       <c r="E6" s="78" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F6" s="105"/>
       <c r="G6" s="44" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="87" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B7" s="35" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C7" s="35" t="s">
         <v>149</v>
@@ -11777,11 +11777,11 @@
         <v>18</v>
       </c>
       <c r="E7" s="118" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F7" s="105"/>
       <c r="G7" s="106" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -11789,7 +11789,7 @@
         <v>141</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C8" s="36" t="s">
         <v>143</v>
@@ -11798,11 +11798,11 @@
         <v>18</v>
       </c>
       <c r="E8" s="119" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F8" s="104"/>
       <c r="G8" s="45" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -11810,7 +11810,7 @@
         <v>141</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C9" s="36" t="s">
         <v>146</v>
@@ -11819,11 +11819,11 @@
         <v>18</v>
       </c>
       <c r="E9" s="119" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F9" s="104"/>
       <c r="G9" s="45" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -11831,7 +11831,7 @@
         <v>141</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C10" s="36" t="s">
         <v>143</v>
@@ -11840,22 +11840,22 @@
         <v>18</v>
       </c>
       <c r="E10" s="119" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F10" s="104"/>
       <c r="G10" s="45" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K10" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="87" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C11" s="35" t="s">
         <v>149</v>
@@ -11864,19 +11864,19 @@
         <v>18</v>
       </c>
       <c r="E11" s="118" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F11" s="105"/>
       <c r="G11" s="106" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="87" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B12" s="35" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C12" s="35" t="s">
         <v>149</v>
@@ -11885,19 +11885,19 @@
         <v>18</v>
       </c>
       <c r="E12" s="118" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F12" s="105"/>
       <c r="G12" s="106" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="87" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B13" s="71" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C13" s="35" t="s">
         <v>149</v>
@@ -11906,11 +11906,11 @@
         <v>18</v>
       </c>
       <c r="E13" s="118" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F13" s="105"/>
       <c r="G13" s="106" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -11918,7 +11918,7 @@
         <v>141</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C14" s="36" t="s">
         <v>143</v>
@@ -11927,13 +11927,13 @@
         <v>18</v>
       </c>
       <c r="E14" s="119" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F14" s="104">
         <v>40</v>
       </c>
       <c r="G14" s="45" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -11941,7 +11941,7 @@
         <v>141</v>
       </c>
       <c r="B15" s="36" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C15" s="36" t="s">
         <v>146</v>
@@ -11950,13 +11950,13 @@
         <v>18</v>
       </c>
       <c r="E15" s="119" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F15" s="104">
         <v>40</v>
       </c>
       <c r="G15" s="45" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -11964,7 +11964,7 @@
         <v>141</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C16" s="36" t="s">
         <v>149</v>
@@ -11973,13 +11973,13 @@
         <v>18</v>
       </c>
       <c r="E16" s="120" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F16" s="104">
         <v>40</v>
       </c>
       <c r="G16" s="45" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -11996,13 +11996,13 @@
         <v>18</v>
       </c>
       <c r="E17" s="78" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F17" s="105">
         <v>40</v>
       </c>
       <c r="G17" s="44" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -12019,13 +12019,13 @@
         <v>18</v>
       </c>
       <c r="E18" s="78" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F18" s="105">
         <v>40</v>
       </c>
       <c r="G18" s="44" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -12042,13 +12042,13 @@
         <v>18</v>
       </c>
       <c r="E19" s="118" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F19" s="105">
         <v>40</v>
       </c>
       <c r="G19" s="44" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -12056,7 +12056,7 @@
         <v>141</v>
       </c>
       <c r="B20" s="36" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C20" s="36" t="s">
         <v>143</v>
@@ -12065,13 +12065,13 @@
         <v>18</v>
       </c>
       <c r="E20" s="119" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F20" s="104">
         <v>40</v>
       </c>
       <c r="G20" s="45" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -12079,7 +12079,7 @@
         <v>141</v>
       </c>
       <c r="B21" s="36" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C21" s="36" t="s">
         <v>143</v>
@@ -12088,11 +12088,11 @@
         <v>18</v>
       </c>
       <c r="E21" s="119" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F21" s="104"/>
       <c r="G21" s="45" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -12100,7 +12100,7 @@
         <v>141</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C22" s="36" t="s">
         <v>146</v>
@@ -12109,11 +12109,11 @@
         <v>18</v>
       </c>
       <c r="E22" s="119" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F22" s="104"/>
       <c r="G22" s="45" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -12121,7 +12121,7 @@
         <v>141</v>
       </c>
       <c r="B23" s="36" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C23" s="36" t="s">
         <v>149</v>
@@ -12130,11 +12130,11 @@
         <v>18</v>
       </c>
       <c r="E23" s="119" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F23" s="104"/>
       <c r="G23" s="45" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -12142,7 +12142,7 @@
         <v>141</v>
       </c>
       <c r="B24" s="35" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C24" s="35" t="s">
         <v>143</v>
@@ -12151,11 +12151,11 @@
         <v>18</v>
       </c>
       <c r="E24" s="78" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F24" s="105"/>
       <c r="G24" s="44" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -12163,7 +12163,7 @@
         <v>141</v>
       </c>
       <c r="B25" s="35" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C25" s="35" t="s">
         <v>143</v>
@@ -12172,11 +12172,11 @@
         <v>18</v>
       </c>
       <c r="E25" s="78" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F25" s="105"/>
       <c r="G25" s="44" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -12184,7 +12184,7 @@
         <v>141</v>
       </c>
       <c r="B26" s="35" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C26" s="35" t="s">
         <v>146</v>
@@ -12193,11 +12193,11 @@
         <v>18</v>
       </c>
       <c r="E26" s="78" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F26" s="105"/>
       <c r="G26" s="44" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -12205,7 +12205,7 @@
         <v>141</v>
       </c>
       <c r="B27" s="35" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C27" s="35" t="s">
         <v>149</v>
@@ -12214,11 +12214,11 @@
         <v>18</v>
       </c>
       <c r="E27" s="118" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F27" s="105"/>
       <c r="G27" s="44" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -12226,7 +12226,7 @@
         <v>141</v>
       </c>
       <c r="B28" s="36" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C28" s="36" t="s">
         <v>143</v>
@@ -12235,11 +12235,11 @@
         <v>18</v>
       </c>
       <c r="E28" s="119" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F28" s="104"/>
       <c r="G28" s="45" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -12247,7 +12247,7 @@
         <v>141</v>
       </c>
       <c r="B29" s="36" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C29" s="36" t="s">
         <v>143</v>
@@ -12256,11 +12256,11 @@
         <v>18</v>
       </c>
       <c r="E29" s="119" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F29" s="104"/>
       <c r="G29" s="45" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -12268,7 +12268,7 @@
         <v>141</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C30" s="36" t="s">
         <v>146</v>
@@ -12277,11 +12277,11 @@
         <v>18</v>
       </c>
       <c r="E30" s="119" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F30" s="104"/>
       <c r="G30" s="45" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -12289,7 +12289,7 @@
         <v>141</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C31" s="36" t="s">
         <v>149</v>
@@ -12298,11 +12298,11 @@
         <v>18</v>
       </c>
       <c r="E31" s="120" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F31" s="104"/>
       <c r="G31" s="45" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -12390,7 +12390,7 @@
     <row r="1" spans="1:15">
       <c r="A1" s="5"/>
       <c r="B1" s="6" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
@@ -12406,7 +12406,7 @@
     <row r="2" spans="1:15">
       <c r="A2" s="5"/>
       <c r="B2" s="7" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -12419,649 +12419,649 @@
       <c r="K2" s="5"/>
       <c r="L2" s="16"/>
       <c r="M2" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="O2" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="5"/>
       <c r="B3" s="8" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="K3" s="14" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="L3" s="17" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N3" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="5"/>
       <c r="B4" s="8" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L4" s="17"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="5"/>
       <c r="B5" s="8" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E5" s="10" t="s">
+        <v>485</v>
+      </c>
+      <c r="F5" s="10" t="s">
         <v>484</v>
       </c>
-      <c r="F5" s="10" t="s">
-        <v>483</v>
-      </c>
       <c r="G5" s="10" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K5" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L5" s="17"/>
       <c r="M5" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="5"/>
       <c r="B6" s="8" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E6" s="10" t="s">
+        <v>491</v>
+      </c>
+      <c r="F6" s="10" t="s">
         <v>490</v>
       </c>
-      <c r="F6" s="10" t="s">
-        <v>489</v>
-      </c>
       <c r="G6" s="10" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K6" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L6" s="17" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="5"/>
       <c r="B7" s="8" t="s">
+        <v>493</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>494</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>495</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>496</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>495</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>486</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>481</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>481</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>481</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>481</v>
+      </c>
+      <c r="L7" s="17" t="s">
         <v>492</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>493</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>494</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>495</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>494</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>485</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>480</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>480</v>
-      </c>
-      <c r="J7" s="10" t="s">
-        <v>480</v>
-      </c>
-      <c r="K7" s="15" t="s">
-        <v>480</v>
-      </c>
-      <c r="L7" s="17" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="5"/>
       <c r="B8" s="8" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E8" s="10" t="s">
+        <v>500</v>
+      </c>
+      <c r="F8" s="10" t="s">
         <v>499</v>
       </c>
-      <c r="F8" s="10" t="s">
-        <v>498</v>
-      </c>
       <c r="G8" s="10" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K8" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L8" s="17"/>
       <c r="O8" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="5"/>
       <c r="B9" s="8" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E9" s="10" t="s">
+        <v>505</v>
+      </c>
+      <c r="F9" s="10" t="s">
         <v>504</v>
       </c>
-      <c r="F9" s="10" t="s">
-        <v>503</v>
-      </c>
       <c r="G9" s="10" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L9" s="17"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="5"/>
       <c r="B10" s="8" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L10" s="17"/>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="5"/>
       <c r="B11" s="8" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L11" s="17" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="5"/>
       <c r="B12" s="8" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L12" s="17" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="5"/>
       <c r="B13" s="8" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L13" s="17"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="5"/>
       <c r="B14" s="8" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K14" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L14" s="17"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="5"/>
       <c r="B15" s="8" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K15" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L15" s="17"/>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="5"/>
       <c r="B16" s="8" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E16" s="10" t="s">
+        <v>517</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>518</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>486</v>
+      </c>
+      <c r="H16" s="11" t="s">
         <v>516</v>
       </c>
-      <c r="F16" s="10" t="s">
-        <v>517</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>485</v>
-      </c>
-      <c r="H16" s="11" t="s">
-        <v>515</v>
-      </c>
       <c r="I16" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L16" s="17"/>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="5"/>
       <c r="B17" s="8" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C17" s="10" t="s">
+        <v>519</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>520</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>521</v>
+      </c>
+      <c r="F17" s="10" t="s">
         <v>518</v>
       </c>
-      <c r="D17" s="10" t="s">
-        <v>519</v>
-      </c>
-      <c r="E17" s="10" t="s">
+      <c r="G17" s="10" t="s">
+        <v>486</v>
+      </c>
+      <c r="H17" s="9" t="s">
         <v>520</v>
       </c>
-      <c r="F17" s="10" t="s">
-        <v>517</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>485</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>519</v>
-      </c>
       <c r="I17" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L17" s="17"/>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="5"/>
       <c r="B18" s="8" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E18" s="10" t="s">
+        <v>524</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>518</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>486</v>
+      </c>
+      <c r="H18" s="10" t="s">
         <v>523</v>
       </c>
-      <c r="F18" s="10" t="s">
-        <v>517</v>
-      </c>
-      <c r="G18" s="10" t="s">
-        <v>485</v>
-      </c>
-      <c r="H18" s="10" t="s">
-        <v>522</v>
-      </c>
       <c r="I18" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L18" s="17"/>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="5"/>
       <c r="B19" s="8" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E19" s="10" t="s">
+        <v>527</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>518</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>486</v>
+      </c>
+      <c r="H19" s="10" t="s">
         <v>526</v>
       </c>
-      <c r="F19" s="10" t="s">
-        <v>517</v>
-      </c>
-      <c r="G19" s="10" t="s">
-        <v>485</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>525</v>
-      </c>
       <c r="I19" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L19" s="17"/>
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="5"/>
       <c r="B20" s="8" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E20" s="10" t="s">
+        <v>530</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>518</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>486</v>
+      </c>
+      <c r="H20" s="10" t="s">
         <v>529</v>
       </c>
-      <c r="F20" s="10" t="s">
-        <v>517</v>
-      </c>
-      <c r="G20" s="10" t="s">
-        <v>485</v>
-      </c>
-      <c r="H20" s="10" t="s">
-        <v>528</v>
-      </c>
       <c r="I20" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L20" s="17"/>
     </row>
@@ -13071,65 +13071,65 @@
         <v>53</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E21" s="10" t="s">
+        <v>533</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>518</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>486</v>
+      </c>
+      <c r="H21" s="10" t="s">
         <v>532</v>
       </c>
-      <c r="F21" s="10" t="s">
-        <v>517</v>
-      </c>
-      <c r="G21" s="10" t="s">
-        <v>485</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>531</v>
-      </c>
       <c r="I21" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K21" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L21" s="17"/>
     </row>
     <row r="22" spans="1:15">
       <c r="A22" s="5"/>
       <c r="B22" s="12" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E22" s="10" t="s">
+        <v>537</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>518</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>486</v>
+      </c>
+      <c r="H22" s="10" t="s">
         <v>536</v>
       </c>
-      <c r="F22" s="10" t="s">
-        <v>517</v>
-      </c>
-      <c r="G22" s="10" t="s">
-        <v>485</v>
-      </c>
-      <c r="H22" s="10" t="s">
-        <v>535</v>
-      </c>
       <c r="I22" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K22" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L22" s="17"/>
     </row>
@@ -13137,1002 +13137,1002 @@
       <c r="A23" s="5"/>
       <c r="B23" s="13"/>
       <c r="C23" s="10" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E23" s="10" t="s">
+        <v>540</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>518</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>486</v>
+      </c>
+      <c r="H23" s="10" t="s">
         <v>539</v>
       </c>
-      <c r="F23" s="10" t="s">
-        <v>517</v>
-      </c>
-      <c r="G23" s="10" t="s">
-        <v>485</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>538</v>
-      </c>
       <c r="I23" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K23" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="5"/>
       <c r="B24" s="8" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K24" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L24" s="17"/>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="5"/>
       <c r="B25" s="8" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E25" s="10" t="s">
+        <v>545</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>546</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>486</v>
+      </c>
+      <c r="H25" s="10" t="s">
         <v>544</v>
-      </c>
-      <c r="F25" s="10" t="s">
-        <v>545</v>
-      </c>
-      <c r="G25" s="10" t="s">
-        <v>485</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>543</v>
       </c>
       <c r="I25" s="10"/>
       <c r="J25" s="10"/>
       <c r="K25" s="15"/>
       <c r="L25" s="17" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="26" spans="1:15" ht="15" customHeight="1">
       <c r="A26" s="5"/>
       <c r="B26" s="8" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D26" s="10" t="s">
+        <v>550</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>551</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>486</v>
+      </c>
+      <c r="G26" s="10" t="s">
         <v>549</v>
       </c>
-      <c r="E26" s="10" t="s">
-        <v>550</v>
-      </c>
-      <c r="F26" s="10" t="s">
-        <v>485</v>
-      </c>
-      <c r="G26" s="10" t="s">
-        <v>548</v>
-      </c>
       <c r="H26" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K26" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L26" s="17" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="5"/>
       <c r="B27" s="8" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K27" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L27" s="17"/>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="5"/>
       <c r="B28" s="8" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D28" s="10" t="s">
+        <v>560</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>561</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>486</v>
+      </c>
+      <c r="G28" s="10" t="s">
         <v>559</v>
       </c>
-      <c r="E28" s="10" t="s">
-        <v>560</v>
-      </c>
-      <c r="F28" s="10" t="s">
-        <v>485</v>
-      </c>
-      <c r="G28" s="10" t="s">
-        <v>558</v>
-      </c>
       <c r="H28" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K28" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L28" s="17"/>
       <c r="O28" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="5"/>
       <c r="B29" s="8" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D29" s="10" t="s">
+        <v>564</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>565</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>486</v>
+      </c>
+      <c r="G29" s="10" t="s">
         <v>563</v>
       </c>
-      <c r="E29" s="10" t="s">
-        <v>564</v>
-      </c>
-      <c r="F29" s="10" t="s">
-        <v>485</v>
-      </c>
-      <c r="G29" s="10" t="s">
-        <v>562</v>
-      </c>
       <c r="H29" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K29" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L29" s="17"/>
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="5"/>
       <c r="B30" s="8" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D30" s="10" t="s">
+        <v>568</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>569</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>486</v>
+      </c>
+      <c r="G30" s="10" t="s">
         <v>567</v>
       </c>
-      <c r="E30" s="10" t="s">
-        <v>568</v>
-      </c>
-      <c r="F30" s="10" t="s">
-        <v>485</v>
-      </c>
-      <c r="G30" s="10" t="s">
-        <v>566</v>
-      </c>
       <c r="H30" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K30" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L30" s="17"/>
       <c r="N30" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="31" spans="1:15">
       <c r="A31" s="5"/>
       <c r="B31" s="8" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D31" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>574</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>486</v>
+      </c>
+      <c r="G31" s="10" t="s">
         <v>572</v>
       </c>
-      <c r="E31" s="10" t="s">
-        <v>573</v>
-      </c>
-      <c r="F31" s="10" t="s">
-        <v>485</v>
-      </c>
-      <c r="G31" s="10" t="s">
-        <v>571</v>
-      </c>
       <c r="H31" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K31" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L31" s="17"/>
     </row>
     <row r="32" spans="1:15">
       <c r="A32" s="5"/>
       <c r="B32" s="8" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K32" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L32" s="17" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="5"/>
       <c r="B33" s="8" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C33" s="10" t="s">
+        <v>577</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>481</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>481</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>486</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>577</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>481</v>
+      </c>
+      <c r="I33" s="10" t="s">
+        <v>481</v>
+      </c>
+      <c r="J33" s="10" t="s">
+        <v>481</v>
+      </c>
+      <c r="K33" s="15" t="s">
+        <v>481</v>
+      </c>
+      <c r="L33" s="17" t="s">
         <v>576</v>
-      </c>
-      <c r="D33" s="10" t="s">
-        <v>480</v>
-      </c>
-      <c r="E33" s="10" t="s">
-        <v>480</v>
-      </c>
-      <c r="F33" s="10" t="s">
-        <v>485</v>
-      </c>
-      <c r="G33" s="10" t="s">
-        <v>576</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>480</v>
-      </c>
-      <c r="I33" s="10" t="s">
-        <v>480</v>
-      </c>
-      <c r="J33" s="10" t="s">
-        <v>480</v>
-      </c>
-      <c r="K33" s="15" t="s">
-        <v>480</v>
-      </c>
-      <c r="L33" s="17" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" s="5"/>
       <c r="B34" s="8" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K34" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L34" s="17"/>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" s="5"/>
       <c r="B35" s="8" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K35" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L35" s="17" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M35" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="5"/>
       <c r="B36" s="8" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J36" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K36" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L36" s="17"/>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" s="5"/>
       <c r="B37" s="8" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K37" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L37" s="17"/>
       <c r="N37" s="33" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" s="5"/>
       <c r="B38" s="8" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="G38" s="10" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K38" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L38" s="17"/>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" s="5"/>
       <c r="B39" s="8" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K39" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L39" s="17"/>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="5"/>
       <c r="B40" s="8" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G40" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K40" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L40" s="17" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="30">
       <c r="A41" s="5"/>
       <c r="B41" s="8" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="I41" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J41" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K41" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L41" s="17" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="5"/>
       <c r="B42" s="8" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K42" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L42" s="17"/>
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="5"/>
       <c r="B43" s="8" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J43" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K43" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L43" s="17"/>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="5"/>
       <c r="B44" s="8" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J44" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K44" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L44" s="17"/>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="5"/>
       <c r="B45" s="8" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J45" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K45" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L45" s="17"/>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="5"/>
       <c r="B46" s="8" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G46" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H46" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I46" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J46" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K46" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L46" s="17"/>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="5"/>
       <c r="B47" s="8" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I47" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J47" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K47" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L47" s="17"/>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="5"/>
       <c r="B48" s="8" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G48" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I48" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J48" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K48" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L48" s="17"/>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" s="5"/>
       <c r="B49" s="8" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I49" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J49" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K49" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L49" s="17"/>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" s="5"/>
       <c r="B50" s="8" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G50" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H50" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I50" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J50" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K50" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L50" s="17"/>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" s="5"/>
       <c r="B51" s="8" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I51" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J51" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K51" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L51" s="17"/>
     </row>
@@ -14142,31 +14142,31 @@
         <v>15</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G52" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H52" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I52" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J52" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K52" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L52" s="17"/>
     </row>
@@ -14176,446 +14176,446 @@
         <v>15</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I53" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J53" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K53" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L53" s="17"/>
     </row>
     <row r="54" spans="1:12">
       <c r="A54" s="5"/>
       <c r="B54" s="8" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G54" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H54" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I54" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J54" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K54" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L54" s="17"/>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" s="5"/>
       <c r="B55" s="8" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I55" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J55" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K55" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L55" s="17"/>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" s="5"/>
       <c r="B56" s="8" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F56" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H56" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I56" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J56" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K56" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L56" s="17"/>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" s="5"/>
       <c r="B57" s="8" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F57" s="10" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="I57" s="10" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="J57" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K57" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L57" s="17"/>
     </row>
     <row r="58" spans="1:12">
       <c r="A58" s="5"/>
       <c r="B58" s="8" t="s">
+        <v>624</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>625</v>
+      </c>
+      <c r="D58" s="10" t="s">
+        <v>481</v>
+      </c>
+      <c r="E58" s="10" t="s">
+        <v>481</v>
+      </c>
+      <c r="F58" s="10" t="s">
+        <v>620</v>
+      </c>
+      <c r="G58" s="10" t="s">
+        <v>621</v>
+      </c>
+      <c r="H58" s="10" t="s">
+        <v>622</v>
+      </c>
+      <c r="I58" s="10" t="s">
         <v>623</v>
       </c>
-      <c r="C58" s="10" t="s">
-        <v>624</v>
-      </c>
-      <c r="D58" s="10" t="s">
-        <v>480</v>
-      </c>
-      <c r="E58" s="10" t="s">
-        <v>480</v>
-      </c>
-      <c r="F58" s="10" t="s">
-        <v>619</v>
-      </c>
-      <c r="G58" s="10" t="s">
-        <v>620</v>
-      </c>
-      <c r="H58" s="10" t="s">
-        <v>621</v>
-      </c>
-      <c r="I58" s="10" t="s">
-        <v>622</v>
-      </c>
       <c r="J58" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K58" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L58" s="17"/>
     </row>
     <row r="59" spans="1:12">
       <c r="A59" s="5"/>
       <c r="B59" s="8" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="J59" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K59" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L59" s="17"/>
     </row>
     <row r="60" spans="1:12">
       <c r="A60" s="5"/>
       <c r="B60" s="8" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F60" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G60" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H60" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J60" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K60" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L60" s="17"/>
     </row>
     <row r="61" spans="1:12">
       <c r="A61" s="5"/>
       <c r="B61" s="8" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I61" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J61" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K61" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L61" s="17"/>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" s="5"/>
       <c r="B62" s="8" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G62" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H62" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I62" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J62" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K62" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L62" s="17"/>
     </row>
     <row r="63" spans="1:12">
       <c r="A63" s="5"/>
       <c r="B63" s="8" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F63" s="10" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="I63" s="10" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="J63" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K63" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L63" s="17"/>
     </row>
     <row r="64" spans="1:12">
       <c r="A64" s="5"/>
       <c r="B64" s="8" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E64" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F64" s="10" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="G64" s="10" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H64" s="10" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="J64" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K64" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L64" s="17"/>
     </row>
     <row r="65" spans="1:15">
       <c r="A65" s="5"/>
       <c r="B65" s="8" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F65" s="10" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="I65" s="10" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="J65" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K65" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L65" s="17"/>
     </row>
     <row r="66" spans="1:15">
       <c r="A66" s="5"/>
       <c r="B66" s="12" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C66" s="5"/>
       <c r="D66" s="5"/>
@@ -14630,7 +14630,7 @@
     <row r="67" spans="1:15">
       <c r="A67" s="5"/>
       <c r="B67" s="5" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C67" s="5"/>
       <c r="D67" s="5"/>
@@ -14642,13 +14642,13 @@
       <c r="J67" s="5"/>
       <c r="K67" s="5"/>
       <c r="O67" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="68" spans="1:15">
       <c r="A68" s="5"/>
       <c r="B68" s="5" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C68" s="5"/>
       <c r="D68" s="5"/>
@@ -14660,7 +14660,7 @@
       <c r="J68" s="5"/>
       <c r="K68" s="5"/>
       <c r="O68" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="69" spans="1:15">
@@ -14849,13 +14849,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="E1" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
@@ -14864,12 +14864,12 @@
         <v>6</v>
       </c>
       <c r="K1" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C2" t="s">
         <v>70</v>
@@ -14880,12 +14880,12 @@
       <c r="E2" s="1"/>
       <c r="G2" s="4"/>
       <c r="K2" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C3" t="s">
         <v>73</v>
@@ -14896,12 +14896,12 @@
       <c r="E3" s="1"/>
       <c r="G3" s="4"/>
       <c r="K3" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C4" t="s">
         <v>70</v>
@@ -14915,15 +14915,15 @@
         <v>15</v>
       </c>
       <c r="K4" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="L4" s="21" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C5" t="s">
         <v>73</v>
@@ -14934,12 +14934,12 @@
       <c r="E5" s="1"/>
       <c r="G5" s="4"/>
       <c r="K5" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C6" t="s">
         <v>70</v>
@@ -14952,7 +14952,7 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C7" t="s">
         <v>73</v>
@@ -14965,7 +14965,7 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C8" t="s">
         <v>70</v>
@@ -14978,7 +14978,7 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C9" t="s">
         <v>73</v>
@@ -14991,7 +14991,7 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C10" t="s">
         <v>70</v>
@@ -15003,7 +15003,7 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C11" t="s">
         <v>73</v>
@@ -15512,13 +15512,13 @@
         <v>23</v>
       </c>
       <c r="B39" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C39" t="s">
         <v>25</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E39" s="1"/>
     </row>
@@ -15527,13 +15527,13 @@
         <v>23</v>
       </c>
       <c r="B40" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C40" t="s">
         <v>28</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E40" s="1"/>
     </row>
@@ -15542,13 +15542,13 @@
         <v>23</v>
       </c>
       <c r="B41" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C41" t="s">
         <v>30</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E41" s="1"/>
     </row>
@@ -15557,13 +15557,13 @@
         <v>23</v>
       </c>
       <c r="B42" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C42" t="s">
         <v>32</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E42" s="1"/>
     </row>
@@ -15572,13 +15572,13 @@
         <v>23</v>
       </c>
       <c r="B43" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C43" t="s">
         <v>25</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="E43" s="1"/>
     </row>
@@ -15587,13 +15587,13 @@
         <v>23</v>
       </c>
       <c r="B44" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C44" t="s">
         <v>28</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="E44" s="1"/>
     </row>
@@ -15602,13 +15602,13 @@
         <v>23</v>
       </c>
       <c r="B45" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C45" t="s">
         <v>30</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="E45" s="1"/>
     </row>
@@ -15617,25 +15617,25 @@
         <v>23</v>
       </c>
       <c r="B46" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C46" t="s">
         <v>32</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="E46" s="1"/>
     </row>
     <row r="47" spans="1:8">
       <c r="D47" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="E47" s="1"/>
     </row>
     <row r="48" spans="1:8">
       <c r="D48" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="E48" s="1"/>
     </row>
@@ -15650,7 +15650,7 @@
         <v>70</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="E49" s="1"/>
     </row>
@@ -15665,43 +15665,43 @@
         <v>73</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="E50" s="1"/>
     </row>
     <row r="51" spans="1:5">
       <c r="D51" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E51" s="1"/>
     </row>
     <row r="52" spans="1:5">
       <c r="D52" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E52" s="1"/>
     </row>
     <row r="53" spans="1:5">
       <c r="D53" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E53" s="1"/>
     </row>
     <row r="54" spans="1:5">
       <c r="D54" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E54" s="1"/>
     </row>
     <row r="55" spans="1:5">
       <c r="D55" s="1" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E55" s="1"/>
     </row>
     <row r="56" spans="1:5">
       <c r="D56" s="1" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E56" s="1"/>
     </row>
@@ -15713,10 +15713,10 @@
         <v>70</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -15727,10 +15727,10 @@
         <v>73</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -15741,10 +15741,10 @@
         <v>70</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -15755,10 +15755,10 @@
         <v>73</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -15769,10 +15769,10 @@
         <v>70</v>
       </c>
       <c r="D61" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="E61" s="1" t="s">
         <v>664</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -15783,10 +15783,10 @@
         <v>73</v>
       </c>
       <c r="D62" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="E62" s="1" t="s">
         <v>664</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -15797,10 +15797,10 @@
         <v>70</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -15811,10 +15811,10 @@
         <v>73</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -15825,10 +15825,10 @@
         <v>70</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -15839,10 +15839,10 @@
         <v>73</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -15853,10 +15853,10 @@
         <v>70</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -15867,10 +15867,10 @@
         <v>73</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -15881,10 +15881,10 @@
         <v>70</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -15895,10 +15895,10 @@
         <v>73</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -15909,10 +15909,10 @@
         <v>70</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -15923,10 +15923,10 @@
         <v>73</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -15937,10 +15937,10 @@
         <v>70</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -15951,10 +15951,10 @@
         <v>73</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -15965,10 +15965,10 @@
         <v>70</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -15979,10 +15979,10 @@
         <v>73</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -15996,7 +15996,7 @@
         <v>86</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -16010,12 +16010,12 @@
         <v>86</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C79" t="s">
         <v>70</v>
@@ -16027,7 +16027,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C80" t="s">
         <v>73</v>
@@ -16039,10 +16039,10 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C81" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>50</v>
@@ -16051,717 +16051,717 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C82" t="s">
         <v>70</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E82" s="1"/>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C83" t="s">
         <v>73</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E83" s="1"/>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C84" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E84" s="1"/>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C85" t="s">
         <v>70</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="E85" s="1"/>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C86" t="s">
         <v>73</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="E86" s="1"/>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C87" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="E87" s="1"/>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C88" t="s">
         <v>70</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E88" s="1"/>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C89" t="s">
         <v>73</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E89" s="1"/>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C90" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E90" s="1"/>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C91" t="s">
         <v>70</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E91" s="1"/>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C92" t="s">
         <v>73</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E92" s="1"/>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C93" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E93" s="1"/>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C94" t="s">
         <v>70</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="E94" s="1"/>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C95" t="s">
         <v>73</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="E95" s="1"/>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C96" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="E96" s="1"/>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C97" t="s">
         <v>70</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="E97" s="1"/>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C98" t="s">
         <v>73</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="E98" s="1"/>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C99" t="s">
+        <v>681</v>
+      </c>
+      <c r="D99" s="1" t="s">
         <v>680</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>679</v>
       </c>
       <c r="E99" s="1"/>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C100" t="s">
         <v>70</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="E100" s="20"/>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C101" t="s">
         <v>73</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="E101" s="20" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" t="s">
+        <v>682</v>
+      </c>
+      <c r="C102" t="s">
         <v>681</v>
       </c>
-      <c r="C102" t="s">
-        <v>680</v>
-      </c>
       <c r="D102" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="E102" s="20" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C103" t="s">
         <v>70</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="E103" s="20"/>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C104" t="s">
         <v>73</v>
       </c>
       <c r="D104" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="E104" s="20" t="s">
         <v>684</v>
-      </c>
-      <c r="E104" s="20" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" t="s">
+        <v>682</v>
+      </c>
+      <c r="C105" t="s">
         <v>681</v>
       </c>
-      <c r="C105" t="s">
-        <v>680</v>
-      </c>
       <c r="D105" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="E105" s="20" t="s">
         <v>684</v>
-      </c>
-      <c r="E105" s="20" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C106" t="s">
         <v>70</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="E106" s="20"/>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C107" t="s">
         <v>73</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="E107" s="20" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" t="s">
+        <v>682</v>
+      </c>
+      <c r="C108" t="s">
         <v>681</v>
       </c>
-      <c r="C108" t="s">
-        <v>680</v>
-      </c>
       <c r="D108" s="1" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="E108" s="20" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C109" t="s">
         <v>70</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="E109" s="20"/>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C110" t="s">
         <v>73</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="E110" s="20" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" t="s">
+        <v>682</v>
+      </c>
+      <c r="C111" t="s">
         <v>681</v>
       </c>
-      <c r="C111" t="s">
-        <v>680</v>
-      </c>
       <c r="D111" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="E111" s="20" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C112" t="s">
         <v>70</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="E112" s="1"/>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C113" t="s">
         <v>73</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="E113" s="20" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" t="s">
+        <v>682</v>
+      </c>
+      <c r="C114" t="s">
         <v>681</v>
       </c>
-      <c r="C114" t="s">
-        <v>680</v>
-      </c>
       <c r="D114" s="1" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="E114" s="20" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C115" t="s">
         <v>70</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E115" s="1"/>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C116" t="s">
         <v>73</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E116" s="1"/>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C117" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E117" s="1"/>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C118" t="s">
         <v>11</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="E118" s="1"/>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C119" t="s">
         <v>375</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="E119" s="1"/>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C120" t="s">
+        <v>693</v>
+      </c>
+      <c r="D120" s="1" t="s">
         <v>692</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>691</v>
       </c>
       <c r="E120" s="1"/>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C121" t="s">
         <v>11</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E121" s="1"/>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C122" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E122" s="1"/>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C123" t="s">
         <v>375</v>
       </c>
       <c r="D123" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E123" s="1"/>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C124" t="s">
         <v>11</v>
       </c>
       <c r="D124" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E124" s="1"/>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C125" t="s">
+        <v>696</v>
+      </c>
+      <c r="D125" t="s">
         <v>695</v>
-      </c>
-      <c r="D125" t="s">
-        <v>694</v>
       </c>
       <c r="E125" s="1"/>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C126" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D126" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E126" s="1"/>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C127" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D127" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E127" s="1"/>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C128" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="D128" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E128" s="1"/>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C129" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="D129" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E129" s="1"/>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C130" t="s">
+        <v>702</v>
+      </c>
+      <c r="D130" t="s">
         <v>701</v>
-      </c>
-      <c r="D130" t="s">
-        <v>700</v>
       </c>
       <c r="E130" s="1"/>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C131" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="D131" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="E131" s="1"/>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C132" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D132" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="E132" s="1"/>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C133" t="s">
         <v>11</v>
       </c>
       <c r="D133" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="E133" s="1"/>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C134" t="s">
         <v>61</v>
       </c>
       <c r="D134" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="E134" s="1"/>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C135" t="s">
         <v>375</v>
       </c>
       <c r="D135" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="E135" s="1"/>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C136" t="s">
+        <v>706</v>
+      </c>
+      <c r="D136" t="s">
         <v>705</v>
-      </c>
-      <c r="D136" t="s">
-        <v>704</v>
       </c>
       <c r="E136" s="1"/>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C137" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D137" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="E137" s="1"/>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C138" t="s">
         <v>11</v>
       </c>
       <c r="D138" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="E138" s="1"/>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C139" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="D139" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="E139" s="1"/>
     </row>
@@ -16852,7 +16852,7 @@
         <v>46</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E159" s="3" t="s">
         <v>48</v>
@@ -16871,7 +16871,7 @@
         <v>11</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E160" s="3" t="s">
         <v>11</v>
@@ -16902,7 +16902,7 @@
         <v>49</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E163" s="1"/>
     </row>
@@ -16911,7 +16911,7 @@
         <v>49</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E164" s="1"/>
     </row>
@@ -16926,7 +16926,7 @@
         <v>46</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>55</v>
@@ -16949,7 +16949,7 @@
         <v>11</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>11</v>
@@ -16972,7 +16972,7 @@
         <v>46</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>48</v>
@@ -16995,7 +16995,7 @@
         <v>11</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>11</v>
@@ -17044,7 +17044,7 @@
         <v>61</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>63</v>
@@ -17067,7 +17067,7 @@
         <v>11</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>11</v>
@@ -17090,7 +17090,7 @@
         <v>64</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>65</v>
@@ -17289,7 +17289,7 @@
         <v>86</v>
       </c>
       <c r="B186" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C186" t="s">
         <v>70</v>
@@ -17306,7 +17306,7 @@
         <v>86</v>
       </c>
       <c r="B187" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C187" t="s">
         <v>73</v>
@@ -17360,7 +17360,7 @@
         <v>95</v>
       </c>
       <c r="C190" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="D190" s="1" t="s">
         <v>93</v>

--- a/V2 BETA/RRF/Valkyrie Connection Table.xlsx
+++ b/V2 BETA/RRF/Valkyrie Connection Table.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30121"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3837cd5b4a1a02ac/Document Library/GitHub/Project-Valkyrie/V2 BETA/RRF/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3274" documentId="8_{C788BE8B-89FF-47EE-BC54-747C3D562542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E72A23A-6DE3-4B5A-86A0-CE609AAAF128}"/>
+  <xr:revisionPtr revIDLastSave="3279" documentId="8_{C788BE8B-89FF-47EE-BC54-747C3D562542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC9450F1-BAE8-4D41-9E7F-1CCA440CD38B}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="16440" firstSheet="2" activeTab="2" xr2:uid="{344B6B93-88E2-4E8A-A19A-9E2625195A37}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3249" uniqueCount="711">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3252" uniqueCount="713">
   <si>
     <t>Type</t>
   </si>
@@ -1272,6 +1272,12 @@
   </si>
   <si>
     <t>Orange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fan </t>
+  </si>
+  <si>
+    <t>Chamber Heater Fan PWM</t>
   </si>
   <si>
     <t>Flint Zone Probe</t>
@@ -9929,8 +9935,12 @@
       <c r="I34" s="95"/>
     </row>
     <row r="35" spans="1:9">
-      <c r="A35" s="73"/>
-      <c r="B35" s="36"/>
+      <c r="A35" s="73" t="s">
+        <v>410</v>
+      </c>
+      <c r="B35" s="36" t="s">
+        <v>411</v>
+      </c>
       <c r="C35" s="36"/>
       <c r="D35" s="70" t="s">
         <v>200</v>
@@ -10102,7 +10112,7 @@
         <v>44</v>
       </c>
       <c r="B48" s="35" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C48" s="35" t="s">
         <v>46</v>
@@ -10121,7 +10131,7 @@
       </c>
       <c r="H48" s="90"/>
       <c r="I48" s="44" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -10129,7 +10139,7 @@
         <v>44</v>
       </c>
       <c r="B49" s="35" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C49" s="35" t="s">
         <v>9</v>
@@ -10148,7 +10158,7 @@
       </c>
       <c r="H49" s="90"/>
       <c r="I49" s="44" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -10233,7 +10243,7 @@
         <v>256</v>
       </c>
       <c r="E54" s="40" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="F54" s="36">
         <v>22</v>
@@ -10499,7 +10509,7 @@
         <v>303</v>
       </c>
       <c r="E70" s="39" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="F70" s="35">
         <v>22</v>
@@ -10552,7 +10562,7 @@
         <v>312</v>
       </c>
       <c r="E73" s="40" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="F73" s="36">
         <v>22</v>
@@ -10606,7 +10616,7 @@
         <v>318</v>
       </c>
       <c r="E75" s="40" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="F75" s="36">
         <v>22</v>
@@ -10637,7 +10647,7 @@
         <v>323</v>
       </c>
       <c r="B77" s="78" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C77" s="35" t="s">
         <v>70</v>
@@ -10664,7 +10674,7 @@
         <v>323</v>
       </c>
       <c r="B78" s="78" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C78" s="35" t="s">
         <v>73</v>
@@ -10751,7 +10761,7 @@
         <v>70</v>
       </c>
       <c r="D81" s="71" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E81" s="39" t="s">
         <v>78</v>
@@ -10980,7 +10990,7 @@
         <v>184</v>
       </c>
       <c r="G91" s="70" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="H91" s="95"/>
       <c r="I91" s="45" t="s">
@@ -11007,7 +11017,7 @@
         <v>184</v>
       </c>
       <c r="G92" s="70" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="H92" s="95"/>
       <c r="I92" s="45" t="s">
@@ -11043,7 +11053,9 @@
     <row r="95" spans="1:9">
       <c r="A95" s="75"/>
       <c r="B95" s="35"/>
-      <c r="C95" s="35"/>
+      <c r="C95" s="35" t="s">
+        <v>96</v>
+      </c>
       <c r="D95" s="71" t="s">
         <v>362</v>
       </c>
@@ -11055,7 +11067,7 @@
     </row>
     <row r="96" spans="1:9">
       <c r="A96" s="75" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B96" s="35" t="s">
         <v>365</v>
@@ -11673,10 +11685,10 @@
   <sheetData>
     <row r="1" spans="1:11" ht="26.25" customHeight="1">
       <c r="A1" s="112" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="F1" s="129" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="18.75">
@@ -11726,7 +11738,7 @@
         <v>141</v>
       </c>
       <c r="B5" s="114" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C5" s="114" t="s">
         <v>143</v>
@@ -11735,11 +11747,11 @@
         <v>18</v>
       </c>
       <c r="E5" s="116" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="F5" s="117"/>
       <c r="G5" s="44" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -11747,7 +11759,7 @@
         <v>141</v>
       </c>
       <c r="B6" s="35" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C6" s="35" t="s">
         <v>146</v>
@@ -11756,19 +11768,19 @@
         <v>18</v>
       </c>
       <c r="E6" s="78" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="F6" s="105"/>
       <c r="G6" s="44" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="87" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B7" s="35" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C7" s="35" t="s">
         <v>149</v>
@@ -11777,11 +11789,11 @@
         <v>18</v>
       </c>
       <c r="E7" s="118" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F7" s="105"/>
       <c r="G7" s="106" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -11789,7 +11801,7 @@
         <v>141</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C8" s="36" t="s">
         <v>143</v>
@@ -11798,11 +11810,11 @@
         <v>18</v>
       </c>
       <c r="E8" s="119" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="F8" s="104"/>
       <c r="G8" s="45" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -11810,7 +11822,7 @@
         <v>141</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C9" s="36" t="s">
         <v>146</v>
@@ -11819,11 +11831,11 @@
         <v>18</v>
       </c>
       <c r="E9" s="119" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="F9" s="104"/>
       <c r="G9" s="45" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -11831,7 +11843,7 @@
         <v>141</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C10" s="36" t="s">
         <v>143</v>
@@ -11840,22 +11852,22 @@
         <v>18</v>
       </c>
       <c r="E10" s="119" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="F10" s="104"/>
       <c r="G10" s="45" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="K10" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="87" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C11" s="35" t="s">
         <v>149</v>
@@ -11864,19 +11876,19 @@
         <v>18</v>
       </c>
       <c r="E11" s="118" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F11" s="105"/>
       <c r="G11" s="106" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="87" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B12" s="35" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C12" s="35" t="s">
         <v>149</v>
@@ -11885,19 +11897,19 @@
         <v>18</v>
       </c>
       <c r="E12" s="118" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F12" s="105"/>
       <c r="G12" s="106" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="87" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B13" s="71" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C13" s="35" t="s">
         <v>149</v>
@@ -11906,11 +11918,11 @@
         <v>18</v>
       </c>
       <c r="E13" s="118" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F13" s="105"/>
       <c r="G13" s="106" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -11918,7 +11930,7 @@
         <v>141</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C14" s="36" t="s">
         <v>143</v>
@@ -11927,13 +11939,13 @@
         <v>18</v>
       </c>
       <c r="E14" s="119" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="F14" s="104">
         <v>40</v>
       </c>
       <c r="G14" s="45" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -11941,7 +11953,7 @@
         <v>141</v>
       </c>
       <c r="B15" s="36" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C15" s="36" t="s">
         <v>146</v>
@@ -11950,13 +11962,13 @@
         <v>18</v>
       </c>
       <c r="E15" s="119" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="F15" s="104">
         <v>40</v>
       </c>
       <c r="G15" s="45" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -11964,7 +11976,7 @@
         <v>141</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C16" s="36" t="s">
         <v>149</v>
@@ -11973,13 +11985,13 @@
         <v>18</v>
       </c>
       <c r="E16" s="120" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F16" s="104">
         <v>40</v>
       </c>
       <c r="G16" s="45" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -11996,13 +12008,13 @@
         <v>18</v>
       </c>
       <c r="E17" s="78" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="F17" s="105">
         <v>40</v>
       </c>
       <c r="G17" s="44" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -12019,13 +12031,13 @@
         <v>18</v>
       </c>
       <c r="E18" s="78" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="F18" s="105">
         <v>40</v>
       </c>
       <c r="G18" s="44" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -12042,13 +12054,13 @@
         <v>18</v>
       </c>
       <c r="E19" s="118" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F19" s="105">
         <v>40</v>
       </c>
       <c r="G19" s="44" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -12056,7 +12068,7 @@
         <v>141</v>
       </c>
       <c r="B20" s="36" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C20" s="36" t="s">
         <v>143</v>
@@ -12065,13 +12077,13 @@
         <v>18</v>
       </c>
       <c r="E20" s="119" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="F20" s="104">
         <v>40</v>
       </c>
       <c r="G20" s="45" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -12079,7 +12091,7 @@
         <v>141</v>
       </c>
       <c r="B21" s="36" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C21" s="36" t="s">
         <v>143</v>
@@ -12088,11 +12100,11 @@
         <v>18</v>
       </c>
       <c r="E21" s="119" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="F21" s="104"/>
       <c r="G21" s="45" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -12100,7 +12112,7 @@
         <v>141</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C22" s="36" t="s">
         <v>146</v>
@@ -12109,11 +12121,11 @@
         <v>18</v>
       </c>
       <c r="E22" s="119" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="F22" s="104"/>
       <c r="G22" s="45" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -12121,7 +12133,7 @@
         <v>141</v>
       </c>
       <c r="B23" s="36" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C23" s="36" t="s">
         <v>149</v>
@@ -12130,11 +12142,11 @@
         <v>18</v>
       </c>
       <c r="E23" s="119" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="F23" s="104"/>
       <c r="G23" s="45" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -12142,7 +12154,7 @@
         <v>141</v>
       </c>
       <c r="B24" s="35" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C24" s="35" t="s">
         <v>143</v>
@@ -12151,11 +12163,11 @@
         <v>18</v>
       </c>
       <c r="E24" s="78" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="F24" s="105"/>
       <c r="G24" s="44" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -12163,7 +12175,7 @@
         <v>141</v>
       </c>
       <c r="B25" s="35" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C25" s="35" t="s">
         <v>143</v>
@@ -12172,11 +12184,11 @@
         <v>18</v>
       </c>
       <c r="E25" s="78" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="F25" s="105"/>
       <c r="G25" s="44" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -12184,7 +12196,7 @@
         <v>141</v>
       </c>
       <c r="B26" s="35" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C26" s="35" t="s">
         <v>146</v>
@@ -12193,11 +12205,11 @@
         <v>18</v>
       </c>
       <c r="E26" s="78" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="F26" s="105"/>
       <c r="G26" s="44" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -12205,7 +12217,7 @@
         <v>141</v>
       </c>
       <c r="B27" s="35" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C27" s="35" t="s">
         <v>149</v>
@@ -12214,11 +12226,11 @@
         <v>18</v>
       </c>
       <c r="E27" s="118" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F27" s="105"/>
       <c r="G27" s="44" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -12226,7 +12238,7 @@
         <v>141</v>
       </c>
       <c r="B28" s="36" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C28" s="36" t="s">
         <v>143</v>
@@ -12235,11 +12247,11 @@
         <v>18</v>
       </c>
       <c r="E28" s="119" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="F28" s="104"/>
       <c r="G28" s="45" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -12247,7 +12259,7 @@
         <v>141</v>
       </c>
       <c r="B29" s="36" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C29" s="36" t="s">
         <v>143</v>
@@ -12256,11 +12268,11 @@
         <v>18</v>
       </c>
       <c r="E29" s="119" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="F29" s="104"/>
       <c r="G29" s="45" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -12268,7 +12280,7 @@
         <v>141</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C30" s="36" t="s">
         <v>146</v>
@@ -12277,11 +12289,11 @@
         <v>18</v>
       </c>
       <c r="E30" s="119" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="F30" s="104"/>
       <c r="G30" s="45" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -12289,7 +12301,7 @@
         <v>141</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C31" s="36" t="s">
         <v>149</v>
@@ -12298,11 +12310,11 @@
         <v>18</v>
       </c>
       <c r="E31" s="120" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F31" s="104"/>
       <c r="G31" s="45" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -12390,7 +12402,7 @@
     <row r="1" spans="1:15">
       <c r="A1" s="5"/>
       <c r="B1" s="6" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
@@ -12406,7 +12418,7 @@
     <row r="2" spans="1:15">
       <c r="A2" s="5"/>
       <c r="B2" s="7" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -12419,649 +12431,649 @@
       <c r="K2" s="5"/>
       <c r="L2" s="16"/>
       <c r="M2" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="N2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="O2" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="5"/>
       <c r="B3" s="8" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="K3" s="14" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="L3" s="17" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="M3" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="N3" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="O3" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="5"/>
       <c r="B4" s="8" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L4" s="17"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="5"/>
       <c r="B5" s="8" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K5" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L5" s="17"/>
       <c r="M5" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="5"/>
       <c r="B6" s="8" t="s">
+        <v>490</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>491</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>492</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>493</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>492</v>
+      </c>
+      <c r="G6" s="10" t="s">
         <v>488</v>
       </c>
-      <c r="C6" s="10" t="s">
-        <v>489</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>490</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>491</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>490</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>486</v>
-      </c>
       <c r="H6" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K6" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L6" s="17" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="5"/>
       <c r="B7" s="8" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C7" s="10" t="s">
+        <v>496</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>497</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>498</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>497</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>488</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>483</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>483</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>483</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>483</v>
+      </c>
+      <c r="L7" s="17" t="s">
         <v>494</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>495</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>496</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>495</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>486</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>481</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>481</v>
-      </c>
-      <c r="J7" s="10" t="s">
-        <v>481</v>
-      </c>
-      <c r="K7" s="15" t="s">
-        <v>481</v>
-      </c>
-      <c r="L7" s="17" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="5"/>
       <c r="B8" s="8" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K8" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L8" s="17"/>
       <c r="O8" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="5"/>
       <c r="B9" s="8" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L9" s="17"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="5"/>
       <c r="B10" s="8" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L10" s="17"/>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="5"/>
       <c r="B11" s="8" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L11" s="17" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="5"/>
       <c r="B12" s="8" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L12" s="17" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="5"/>
       <c r="B13" s="8" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L13" s="17"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="5"/>
       <c r="B14" s="8" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K14" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L14" s="17"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="5"/>
       <c r="B15" s="8" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K15" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L15" s="17"/>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="5"/>
       <c r="B16" s="8" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="F16" s="10" t="s">
+        <v>520</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>488</v>
+      </c>
+      <c r="H16" s="11" t="s">
         <v>518</v>
       </c>
-      <c r="G16" s="10" t="s">
-        <v>486</v>
-      </c>
-      <c r="H16" s="11" t="s">
-        <v>516</v>
-      </c>
       <c r="I16" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L16" s="17"/>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="5"/>
       <c r="B17" s="8" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="D17" s="10" t="s">
+        <v>522</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>523</v>
+      </c>
+      <c r="F17" s="10" t="s">
         <v>520</v>
       </c>
-      <c r="E17" s="10" t="s">
-        <v>521</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>518</v>
-      </c>
       <c r="G17" s="10" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L17" s="17"/>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="5"/>
       <c r="B18" s="8" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L18" s="17"/>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="5"/>
       <c r="B19" s="8" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L19" s="17"/>
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="5"/>
       <c r="B20" s="8" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L20" s="17"/>
     </row>
@@ -13071,65 +13083,65 @@
         <v>53</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K21" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L21" s="17"/>
     </row>
     <row r="22" spans="1:15">
       <c r="A22" s="5"/>
       <c r="B22" s="12" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K22" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L22" s="17"/>
     </row>
@@ -13137,1002 +13149,1002 @@
       <c r="A23" s="5"/>
       <c r="B23" s="13"/>
       <c r="C23" s="10" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K23" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="5"/>
       <c r="B24" s="8" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K24" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L24" s="17"/>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="5"/>
       <c r="B25" s="8" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="F25" s="10" t="s">
+        <v>548</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>488</v>
+      </c>
+      <c r="H25" s="10" t="s">
         <v>546</v>
-      </c>
-      <c r="G25" s="10" t="s">
-        <v>486</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>544</v>
       </c>
       <c r="I25" s="10"/>
       <c r="J25" s="10"/>
       <c r="K25" s="15"/>
       <c r="L25" s="17" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="26" spans="1:15" ht="15" customHeight="1">
       <c r="A26" s="5"/>
       <c r="B26" s="8" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="E26" s="10" t="s">
+        <v>553</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>488</v>
+      </c>
+      <c r="G26" s="10" t="s">
         <v>551</v>
       </c>
-      <c r="F26" s="10" t="s">
-        <v>486</v>
-      </c>
-      <c r="G26" s="10" t="s">
-        <v>549</v>
-      </c>
       <c r="H26" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K26" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L26" s="17" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="5"/>
       <c r="B27" s="8" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K27" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L27" s="17"/>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="5"/>
       <c r="B28" s="8" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="E28" s="10" t="s">
+        <v>563</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>488</v>
+      </c>
+      <c r="G28" s="10" t="s">
         <v>561</v>
       </c>
-      <c r="F28" s="10" t="s">
-        <v>486</v>
-      </c>
-      <c r="G28" s="10" t="s">
-        <v>559</v>
-      </c>
       <c r="H28" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K28" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L28" s="17"/>
       <c r="O28" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="5"/>
       <c r="B29" s="8" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="E29" s="10" t="s">
+        <v>567</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>488</v>
+      </c>
+      <c r="G29" s="10" t="s">
         <v>565</v>
       </c>
-      <c r="F29" s="10" t="s">
-        <v>486</v>
-      </c>
-      <c r="G29" s="10" t="s">
-        <v>563</v>
-      </c>
       <c r="H29" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K29" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L29" s="17"/>
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="5"/>
       <c r="B30" s="8" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="E30" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>488</v>
+      </c>
+      <c r="G30" s="10" t="s">
         <v>569</v>
       </c>
-      <c r="F30" s="10" t="s">
-        <v>486</v>
-      </c>
-      <c r="G30" s="10" t="s">
-        <v>567</v>
-      </c>
       <c r="H30" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K30" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L30" s="17"/>
       <c r="N30" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="31" spans="1:15">
       <c r="A31" s="5"/>
       <c r="B31" s="8" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E31" s="10" t="s">
+        <v>576</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>488</v>
+      </c>
+      <c r="G31" s="10" t="s">
         <v>574</v>
       </c>
-      <c r="F31" s="10" t="s">
-        <v>486</v>
-      </c>
-      <c r="G31" s="10" t="s">
-        <v>572</v>
-      </c>
       <c r="H31" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K31" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L31" s="17"/>
     </row>
     <row r="32" spans="1:15">
       <c r="A32" s="5"/>
       <c r="B32" s="8" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K32" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L32" s="17" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="5"/>
       <c r="B33" s="8" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K33" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L33" s="17" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" s="5"/>
       <c r="B34" s="8" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K34" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L34" s="17"/>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" s="5"/>
       <c r="B35" s="8" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K35" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L35" s="17" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="M35" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="5"/>
       <c r="B36" s="8" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J36" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K36" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L36" s="17"/>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" s="5"/>
       <c r="B37" s="8" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K37" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L37" s="17"/>
       <c r="N37" s="33" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" s="5"/>
       <c r="B38" s="8" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C38" s="10" t="s">
+        <v>596</v>
+      </c>
+      <c r="D38" s="10" t="s">
         <v>594</v>
       </c>
-      <c r="D38" s="10" t="s">
-        <v>592</v>
-      </c>
       <c r="E38" s="10" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="G38" s="10" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K38" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L38" s="17"/>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" s="5"/>
       <c r="B39" s="8" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K39" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L39" s="17"/>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="5"/>
       <c r="B40" s="8" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="G40" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K40" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L40" s="17" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="30">
       <c r="A41" s="5"/>
       <c r="B41" s="8" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="I41" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J41" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K41" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L41" s="17" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="5"/>
       <c r="B42" s="8" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K42" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L42" s="17"/>
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="5"/>
       <c r="B43" s="8" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J43" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K43" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L43" s="17"/>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="5"/>
       <c r="B44" s="8" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J44" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K44" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L44" s="17"/>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="5"/>
       <c r="B45" s="8" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J45" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K45" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L45" s="17"/>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="5"/>
       <c r="B46" s="8" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="G46" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="H46" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I46" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J46" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K46" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L46" s="17"/>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="5"/>
       <c r="B47" s="8" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I47" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J47" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K47" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L47" s="17"/>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="5"/>
       <c r="B48" s="8" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="G48" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I48" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J48" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K48" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L48" s="17"/>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" s="5"/>
       <c r="B49" s="8" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I49" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J49" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K49" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L49" s="17"/>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" s="5"/>
       <c r="B50" s="8" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="G50" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="H50" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I50" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J50" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K50" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L50" s="17"/>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" s="5"/>
       <c r="B51" s="8" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I51" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J51" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K51" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L51" s="17"/>
     </row>
@@ -14142,31 +14154,31 @@
         <v>15</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="G52" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="H52" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I52" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J52" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K52" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L52" s="17"/>
     </row>
@@ -14176,446 +14188,446 @@
         <v>15</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I53" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J53" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K53" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L53" s="17"/>
     </row>
     <row r="54" spans="1:12">
       <c r="A54" s="5"/>
       <c r="B54" s="8" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="G54" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="H54" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I54" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J54" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K54" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L54" s="17"/>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" s="5"/>
       <c r="B55" s="8" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I55" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J55" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K55" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L55" s="17"/>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" s="5"/>
       <c r="B56" s="8" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F56" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="H56" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I56" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J56" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K56" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L56" s="17"/>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" s="5"/>
       <c r="B57" s="8" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F57" s="10" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="I57" s="10" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="J57" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K57" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L57" s="17"/>
     </row>
     <row r="58" spans="1:12">
       <c r="A58" s="5"/>
       <c r="B58" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>627</v>
+      </c>
+      <c r="D58" s="10" t="s">
+        <v>483</v>
+      </c>
+      <c r="E58" s="10" t="s">
+        <v>483</v>
+      </c>
+      <c r="F58" s="10" t="s">
+        <v>622</v>
+      </c>
+      <c r="G58" s="10" t="s">
+        <v>623</v>
+      </c>
+      <c r="H58" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C58" s="10" t="s">
+      <c r="I58" s="10" t="s">
         <v>625</v>
       </c>
-      <c r="D58" s="10" t="s">
-        <v>481</v>
-      </c>
-      <c r="E58" s="10" t="s">
-        <v>481</v>
-      </c>
-      <c r="F58" s="10" t="s">
-        <v>620</v>
-      </c>
-      <c r="G58" s="10" t="s">
-        <v>621</v>
-      </c>
-      <c r="H58" s="10" t="s">
-        <v>622</v>
-      </c>
-      <c r="I58" s="10" t="s">
-        <v>623</v>
-      </c>
       <c r="J58" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K58" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L58" s="17"/>
     </row>
     <row r="59" spans="1:12">
       <c r="A59" s="5"/>
       <c r="B59" s="8" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="J59" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K59" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L59" s="17"/>
     </row>
     <row r="60" spans="1:12">
       <c r="A60" s="5"/>
       <c r="B60" s="8" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F60" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="G60" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="H60" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J60" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K60" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L60" s="17"/>
     </row>
     <row r="61" spans="1:12">
       <c r="A61" s="5"/>
       <c r="B61" s="8" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I61" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J61" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K61" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L61" s="17"/>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" s="5"/>
       <c r="B62" s="8" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="G62" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="H62" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I62" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J62" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K62" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L62" s="17"/>
     </row>
     <row r="63" spans="1:12">
       <c r="A63" s="5"/>
       <c r="B63" s="8" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F63" s="10" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="I63" s="10" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="J63" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K63" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L63" s="17"/>
     </row>
     <row r="64" spans="1:12">
       <c r="A64" s="5"/>
       <c r="B64" s="8" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E64" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F64" s="10" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="G64" s="10" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="H64" s="10" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="J64" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K64" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L64" s="17"/>
     </row>
     <row r="65" spans="1:15">
       <c r="A65" s="5"/>
       <c r="B65" s="8" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F65" s="10" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="I65" s="10" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="J65" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K65" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L65" s="17"/>
     </row>
     <row r="66" spans="1:15">
       <c r="A66" s="5"/>
       <c r="B66" s="12" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C66" s="5"/>
       <c r="D66" s="5"/>
@@ -14630,7 +14642,7 @@
     <row r="67" spans="1:15">
       <c r="A67" s="5"/>
       <c r="B67" s="5" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C67" s="5"/>
       <c r="D67" s="5"/>
@@ -14642,13 +14654,13 @@
       <c r="J67" s="5"/>
       <c r="K67" s="5"/>
       <c r="O67" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="68" spans="1:15">
       <c r="A68" s="5"/>
       <c r="B68" s="5" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C68" s="5"/>
       <c r="D68" s="5"/>
@@ -14660,7 +14672,7 @@
       <c r="J68" s="5"/>
       <c r="K68" s="5"/>
       <c r="O68" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="69" spans="1:15">
@@ -14849,13 +14861,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="E1" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
@@ -14864,12 +14876,12 @@
         <v>6</v>
       </c>
       <c r="K1" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C2" t="s">
         <v>70</v>
@@ -14880,12 +14892,12 @@
       <c r="E2" s="1"/>
       <c r="G2" s="4"/>
       <c r="K2" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C3" t="s">
         <v>73</v>
@@ -14896,12 +14908,12 @@
       <c r="E3" s="1"/>
       <c r="G3" s="4"/>
       <c r="K3" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C4" t="s">
         <v>70</v>
@@ -14915,15 +14927,15 @@
         <v>15</v>
       </c>
       <c r="K4" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="L4" s="21" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C5" t="s">
         <v>73</v>
@@ -14934,12 +14946,12 @@
       <c r="E5" s="1"/>
       <c r="G5" s="4"/>
       <c r="K5" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C6" t="s">
         <v>70</v>
@@ -14952,7 +14964,7 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C7" t="s">
         <v>73</v>
@@ -14965,7 +14977,7 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C8" t="s">
         <v>70</v>
@@ -14978,7 +14990,7 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C9" t="s">
         <v>73</v>
@@ -14991,7 +15003,7 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C10" t="s">
         <v>70</v>
@@ -15003,7 +15015,7 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C11" t="s">
         <v>73</v>
@@ -15512,13 +15524,13 @@
         <v>23</v>
       </c>
       <c r="B39" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C39" t="s">
         <v>25</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="E39" s="1"/>
     </row>
@@ -15527,13 +15539,13 @@
         <v>23</v>
       </c>
       <c r="B40" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C40" t="s">
         <v>28</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="E40" s="1"/>
     </row>
@@ -15542,13 +15554,13 @@
         <v>23</v>
       </c>
       <c r="B41" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C41" t="s">
         <v>30</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="E41" s="1"/>
     </row>
@@ -15557,13 +15569,13 @@
         <v>23</v>
       </c>
       <c r="B42" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C42" t="s">
         <v>32</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="E42" s="1"/>
     </row>
@@ -15572,13 +15584,13 @@
         <v>23</v>
       </c>
       <c r="B43" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C43" t="s">
         <v>25</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="E43" s="1"/>
     </row>
@@ -15587,13 +15599,13 @@
         <v>23</v>
       </c>
       <c r="B44" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C44" t="s">
         <v>28</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="E44" s="1"/>
     </row>
@@ -15602,13 +15614,13 @@
         <v>23</v>
       </c>
       <c r="B45" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C45" t="s">
         <v>30</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="E45" s="1"/>
     </row>
@@ -15617,25 +15629,25 @@
         <v>23</v>
       </c>
       <c r="B46" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C46" t="s">
         <v>32</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="E46" s="1"/>
     </row>
     <row r="47" spans="1:8">
       <c r="D47" s="1" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="E47" s="1"/>
     </row>
     <row r="48" spans="1:8">
       <c r="D48" s="1" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="E48" s="1"/>
     </row>
@@ -15650,7 +15662,7 @@
         <v>70</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="E49" s="1"/>
     </row>
@@ -15665,43 +15677,43 @@
         <v>73</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="E50" s="1"/>
     </row>
     <row r="51" spans="1:5">
       <c r="D51" s="1" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="E51" s="1"/>
     </row>
     <row r="52" spans="1:5">
       <c r="D52" s="1" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="E52" s="1"/>
     </row>
     <row r="53" spans="1:5">
       <c r="D53" s="1" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="E53" s="1"/>
     </row>
     <row r="54" spans="1:5">
       <c r="D54" s="1" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="E54" s="1"/>
     </row>
     <row r="55" spans="1:5">
       <c r="D55" s="1" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="E55" s="1"/>
     </row>
     <row r="56" spans="1:5">
       <c r="D56" s="1" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="E56" s="1"/>
     </row>
@@ -15713,10 +15725,10 @@
         <v>70</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -15727,10 +15739,10 @@
         <v>73</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -15741,10 +15753,10 @@
         <v>70</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -15755,10 +15767,10 @@
         <v>73</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -15769,10 +15781,10 @@
         <v>70</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -15783,10 +15795,10 @@
         <v>73</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -15797,10 +15809,10 @@
         <v>70</v>
       </c>
       <c r="D63" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="E63" s="1" t="s">
         <v>666</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>664</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -15811,10 +15823,10 @@
         <v>73</v>
       </c>
       <c r="D64" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="E64" s="1" t="s">
         <v>666</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>664</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -15825,10 +15837,10 @@
         <v>70</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -15839,10 +15851,10 @@
         <v>73</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -15853,10 +15865,10 @@
         <v>70</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -15867,10 +15879,10 @@
         <v>73</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -15881,10 +15893,10 @@
         <v>70</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -15895,10 +15907,10 @@
         <v>73</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -15909,10 +15921,10 @@
         <v>70</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -15923,10 +15935,10 @@
         <v>73</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -15937,10 +15949,10 @@
         <v>70</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -15951,10 +15963,10 @@
         <v>73</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -15965,10 +15977,10 @@
         <v>70</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -15979,10 +15991,10 @@
         <v>73</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -15996,7 +16008,7 @@
         <v>86</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -16010,12 +16022,12 @@
         <v>86</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C79" t="s">
         <v>70</v>
@@ -16027,7 +16039,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C80" t="s">
         <v>73</v>
@@ -16039,10 +16051,10 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C81" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>50</v>
@@ -16051,717 +16063,717 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C82" t="s">
         <v>70</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E82" s="1"/>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C83" t="s">
         <v>73</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E83" s="1"/>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C84" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E84" s="1"/>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C85" t="s">
         <v>70</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="E85" s="1"/>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C86" t="s">
         <v>73</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="E86" s="1"/>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C87" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="E87" s="1"/>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C88" t="s">
         <v>70</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E88" s="1"/>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C89" t="s">
         <v>73</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E89" s="1"/>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C90" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E90" s="1"/>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C91" t="s">
         <v>70</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="E91" s="1"/>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C92" t="s">
         <v>73</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="E92" s="1"/>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C93" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="E93" s="1"/>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C94" t="s">
         <v>70</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="E94" s="1"/>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C95" t="s">
         <v>73</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="E95" s="1"/>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C96" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="E96" s="1"/>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C97" t="s">
         <v>70</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="E97" s="1"/>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C98" t="s">
         <v>73</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="E98" s="1"/>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C99" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="E99" s="1"/>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C100" t="s">
         <v>70</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="E100" s="20"/>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C101" t="s">
         <v>73</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="E101" s="20" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C102" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="E102" s="20" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C103" t="s">
         <v>70</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="E103" s="20"/>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C104" t="s">
         <v>73</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="E104" s="20" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C105" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="E105" s="20" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C106" t="s">
         <v>70</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="E106" s="20"/>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C107" t="s">
         <v>73</v>
       </c>
       <c r="D107" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="E107" s="20" t="s">
         <v>686</v>
-      </c>
-      <c r="E107" s="20" t="s">
-        <v>684</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C108" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="D108" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="E108" s="20" t="s">
         <v>686</v>
-      </c>
-      <c r="E108" s="20" t="s">
-        <v>684</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C109" t="s">
         <v>70</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="E109" s="20"/>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C110" t="s">
         <v>73</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="E110" s="20" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C111" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="E111" s="20" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C112" t="s">
         <v>70</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="E112" s="1"/>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C113" t="s">
         <v>73</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="E113" s="20" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C114" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="E114" s="20" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="C115" t="s">
         <v>70</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="E115" s="1"/>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="C116" t="s">
         <v>73</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="E116" s="1"/>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="C117" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="E117" s="1"/>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="C118" t="s">
         <v>11</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="E118" s="1"/>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="C119" t="s">
         <v>375</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="E119" s="1"/>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="C120" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="E120" s="1"/>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="C121" t="s">
         <v>11</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="E121" s="1"/>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="C122" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="E122" s="1"/>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="C123" t="s">
         <v>375</v>
       </c>
       <c r="D123" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="E123" s="1"/>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="C124" t="s">
         <v>11</v>
       </c>
       <c r="D124" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="E124" s="1"/>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="C125" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="D125" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="E125" s="1"/>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="C126" t="s">
+        <v>699</v>
+      </c>
+      <c r="D126" t="s">
         <v>697</v>
-      </c>
-      <c r="D126" t="s">
-        <v>695</v>
       </c>
       <c r="E126" s="1"/>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="C127" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="D127" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="E127" s="1"/>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="C128" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="D128" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="E128" s="1"/>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="C129" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="D129" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="E129" s="1"/>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="C130" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="D130" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="E130" s="1"/>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="C131" t="s">
+        <v>705</v>
+      </c>
+      <c r="D131" t="s">
         <v>703</v>
-      </c>
-      <c r="D131" t="s">
-        <v>701</v>
       </c>
       <c r="E131" s="1"/>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="C132" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="D132" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="E132" s="1"/>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="C133" t="s">
         <v>11</v>
       </c>
       <c r="D133" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="E133" s="1"/>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="C134" t="s">
         <v>61</v>
       </c>
       <c r="D134" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="E134" s="1"/>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="C135" t="s">
         <v>375</v>
       </c>
       <c r="D135" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="E135" s="1"/>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C136" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="D136" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="E136" s="1"/>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C137" t="s">
+        <v>709</v>
+      </c>
+      <c r="D137" t="s">
         <v>707</v>
-      </c>
-      <c r="D137" t="s">
-        <v>705</v>
       </c>
       <c r="E137" s="1"/>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C138" t="s">
         <v>11</v>
       </c>
       <c r="D138" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="E138" s="1"/>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C139" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="D139" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="E139" s="1"/>
     </row>
@@ -16852,7 +16864,7 @@
         <v>46</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="E159" s="3" t="s">
         <v>48</v>
@@ -16871,7 +16883,7 @@
         <v>11</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="E160" s="3" t="s">
         <v>11</v>
@@ -16902,7 +16914,7 @@
         <v>49</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E163" s="1"/>
     </row>
@@ -16911,7 +16923,7 @@
         <v>49</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E164" s="1"/>
     </row>
@@ -16926,7 +16938,7 @@
         <v>46</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>55</v>
@@ -16949,7 +16961,7 @@
         <v>11</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>11</v>
@@ -16972,7 +16984,7 @@
         <v>46</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>48</v>
@@ -16995,7 +17007,7 @@
         <v>11</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>11</v>
@@ -17044,7 +17056,7 @@
         <v>61</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>63</v>
@@ -17067,7 +17079,7 @@
         <v>11</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>11</v>
@@ -17090,7 +17102,7 @@
         <v>64</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>65</v>
@@ -17289,7 +17301,7 @@
         <v>86</v>
       </c>
       <c r="B186" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C186" t="s">
         <v>70</v>
@@ -17306,7 +17318,7 @@
         <v>86</v>
       </c>
       <c r="B187" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C187" t="s">
         <v>73</v>
@@ -17360,7 +17372,7 @@
         <v>95</v>
       </c>
       <c r="C190" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D190" s="1" t="s">
         <v>93</v>

--- a/V2 BETA/RRF/Valkyrie Connection Table.xlsx
+++ b/V2 BETA/RRF/Valkyrie Connection Table.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30126"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3837cd5b4a1a02ac/Document Library/GitHub/Project-Valkyrie/V2 BETA/RRF/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3327" documentId="8_{C788BE8B-89FF-47EE-BC54-747C3D562542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1485200-670B-4884-992D-8F8D1D0F28A7}"/>
+  <xr:revisionPtr revIDLastSave="3329" documentId="8_{C788BE8B-89FF-47EE-BC54-747C3D562542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A2EF603-B1A7-49CA-A5DF-357A29FA3475}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{344B6B93-88E2-4E8A-A19A-9E2625195A37}"/>
   </bookViews>
@@ -351,9 +351,18 @@
     <t>IO_5_in</t>
   </si>
   <si>
+    <t>Ioi5.in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">See note on adding 4K7 on the </t>
+  </si>
+  <si>
     <t>IO_5_gnd</t>
   </si>
   <si>
+    <t>V2 6HC connection drawing</t>
+  </si>
+  <si>
     <t>IO_5_out</t>
   </si>
   <si>
@@ -600,7 +609,7 @@
     <t>?</t>
   </si>
   <si>
-    <t>waterpump_connector/3</t>
+    <t>Waterpump_connector/3</t>
   </si>
   <si>
     <t>OUT 5_out</t>
@@ -609,7 +618,7 @@
     <t>out5</t>
   </si>
   <si>
-    <t>waterpump_connector/4</t>
+    <t>Waterpump_connector/4</t>
   </si>
   <si>
     <t>OUT 6_gnd</t>
@@ -1819,22 +1828,13 @@
   <si>
     <t>LC Flowmeter</t>
   </si>
-  <si>
-    <t>Ioi5.in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">See note on adding 4K7 on the </t>
-  </si>
-  <si>
-    <t>V2 6HC connection drawing</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -2285,7 +2285,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2658,10 +2658,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{9F2F2CC6-19FD-46E3-8A6D-884FD4A96CE0}" name="Table4" displayName="Table4" ref="A4:G36" totalsRowShown="0" headerRowBorderDxfId="8">
   <autoFilter ref="A4:G36" xr:uid="{9F2F2CC6-19FD-46E3-8A6D-884FD4A96CE0}"/>
@@ -2695,9 +2691,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2735,7 +2731,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2841,7 +2837,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2983,7 +2979,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4254,7 +4250,7 @@
         <v>102</v>
       </c>
       <c r="E58" s="28" t="s">
-        <v>586</v>
+        <v>103</v>
       </c>
       <c r="F58" s="25">
         <v>22</v>
@@ -4264,7 +4260,7 @@
       </c>
       <c r="H58" s="31"/>
       <c r="I58" s="82" t="s">
-        <v>587</v>
+        <v>104</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -4276,7 +4272,7 @@
       </c>
       <c r="C59" s="25"/>
       <c r="D59" s="36" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E59" s="28" t="s">
         <v>11</v>
@@ -4289,7 +4285,7 @@
       </c>
       <c r="H59" s="31"/>
       <c r="I59" s="82" t="s">
-        <v>588</v>
+        <v>106</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -4297,7 +4293,7 @@
       <c r="B60" s="25"/>
       <c r="C60" s="25"/>
       <c r="D60" s="36" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E60" s="28"/>
       <c r="F60" s="25"/>
@@ -4310,7 +4306,7 @@
       <c r="B61" s="25"/>
       <c r="C61" s="25"/>
       <c r="D61" s="36" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E61" s="28"/>
       <c r="F61" s="25"/>
@@ -4323,16 +4319,16 @@
         <v>78</v>
       </c>
       <c r="B62" s="26" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C62" s="26" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D62" s="35" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E62" s="29" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F62" s="26">
         <v>22</v>
@@ -4342,21 +4338,21 @@
       </c>
       <c r="H62" s="32"/>
       <c r="I62" s="87" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="63" spans="1:9">
       <c r="A63" s="39" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B63" s="25" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C63" s="25" t="s">
         <v>80</v>
       </c>
       <c r="D63" s="35" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E63" s="29"/>
       <c r="F63" s="26"/>
@@ -4369,13 +4365,13 @@
         <v>78</v>
       </c>
       <c r="B64" s="26" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C64" s="26" t="s">
         <v>9</v>
       </c>
       <c r="D64" s="35" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E64" s="29" t="s">
         <v>11</v>
@@ -4388,7 +4384,7 @@
       </c>
       <c r="H64" s="32"/>
       <c r="I64" s="87" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -4396,16 +4392,16 @@
         <v>78</v>
       </c>
       <c r="B65" s="26" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C65" s="26" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D65" s="35" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E65" s="29" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F65" s="26">
         <v>22</v>
@@ -4415,7 +4411,7 @@
       </c>
       <c r="H65" s="32"/>
       <c r="I65" s="87" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -4423,7 +4419,7 @@
       <c r="B66" s="26"/>
       <c r="C66" s="26"/>
       <c r="D66" s="35" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E66" s="29"/>
       <c r="F66" s="26"/>
@@ -4436,7 +4432,7 @@
       <c r="B67" s="25"/>
       <c r="C67" s="25"/>
       <c r="D67" s="36" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E67" s="28"/>
       <c r="F67" s="25"/>
@@ -4446,16 +4442,16 @@
     </row>
     <row r="68" spans="1:9">
       <c r="A68" s="39" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B68" s="25" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C68" s="25" t="s">
         <v>80</v>
       </c>
       <c r="D68" s="36" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E68" s="28"/>
       <c r="F68" s="25"/>
@@ -4468,7 +4464,7 @@
       <c r="B69" s="25"/>
       <c r="C69" s="25"/>
       <c r="D69" s="36" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E69" s="28"/>
       <c r="F69" s="25"/>
@@ -4478,19 +4474,19 @@
     </row>
     <row r="70" spans="1:9">
       <c r="A70" s="39" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B70" s="25" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C70" s="25" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D70" s="36" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E70" s="28" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F70" s="25">
         <v>22</v>
@@ -4500,7 +4496,7 @@
       </c>
       <c r="H70" s="31"/>
       <c r="I70" s="82" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -4508,7 +4504,7 @@
       <c r="B71" s="25"/>
       <c r="C71" s="25"/>
       <c r="D71" s="36" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E71" s="28"/>
       <c r="F71" s="25"/>
@@ -4521,7 +4517,7 @@
       <c r="B72" s="26"/>
       <c r="C72" s="26"/>
       <c r="D72" s="35" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E72" s="29"/>
       <c r="F72" s="26"/>
@@ -4531,19 +4527,19 @@
     </row>
     <row r="73" spans="1:9">
       <c r="A73" s="38" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B73" s="26" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C73" s="26" t="s">
         <v>80</v>
       </c>
       <c r="D73" s="35" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E73" s="29" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F73" s="26">
         <v>22</v>
@@ -4553,21 +4549,21 @@
       </c>
       <c r="H73" s="32"/>
       <c r="I73" s="81" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="74" spans="1:9">
       <c r="A74" s="38" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B74" s="26" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C74" s="26" t="s">
         <v>9</v>
       </c>
       <c r="D74" s="35" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E74" s="29" t="s">
         <v>11</v>
@@ -4580,24 +4576,24 @@
       </c>
       <c r="H74" s="32"/>
       <c r="I74" s="81" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="75" spans="1:9">
       <c r="A75" s="38" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B75" s="26" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C75" s="26" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D75" s="35" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E75" s="29" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F75" s="26">
         <v>22</v>
@@ -4607,7 +4603,7 @@
       </c>
       <c r="H75" s="32"/>
       <c r="I75" s="81" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -4615,7 +4611,7 @@
       <c r="B76" s="26"/>
       <c r="C76" s="26"/>
       <c r="D76" s="35" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E76" s="29"/>
       <c r="F76" s="26"/>
@@ -4625,16 +4621,16 @@
     </row>
     <row r="77" spans="1:9">
       <c r="A77" s="39" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B77" s="40" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C77" s="25" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D77" s="36" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E77" s="28" t="s">
         <v>15</v>
@@ -4647,24 +4643,24 @@
       </c>
       <c r="H77" s="31"/>
       <c r="I77" s="82" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="78" spans="1:9">
       <c r="A78" s="39" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B78" s="40" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C78" s="25" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D78" s="36" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E78" s="28" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F78" s="25">
         <v>14</v>
@@ -4674,24 +4670,24 @@
       </c>
       <c r="H78" s="31"/>
       <c r="I78" s="82" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="79" spans="1:9">
       <c r="A79" s="38" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B79" s="26" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C79" s="26" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D79" s="35" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E79" s="29" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="F79" s="26">
         <v>18</v>
@@ -4701,24 +4697,24 @@
       </c>
       <c r="H79" s="32"/>
       <c r="I79" s="81" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="80" spans="1:9">
       <c r="A80" s="38" t="s">
+        <v>154</v>
+      </c>
+      <c r="B80" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="C80" s="26" t="s">
         <v>151</v>
       </c>
-      <c r="B80" s="26" t="s">
-        <v>152</v>
-      </c>
-      <c r="C80" s="26" t="s">
-        <v>148</v>
-      </c>
       <c r="D80" s="35" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E80" s="29" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F80" s="26">
         <v>18</v>
@@ -4728,24 +4724,24 @@
       </c>
       <c r="H80" s="32"/>
       <c r="I80" s="81" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="81" spans="1:9">
       <c r="A81" s="39" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B81" s="25" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C81" s="25" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D81" s="36" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E81" s="28" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="F81" s="25">
         <v>18</v>
@@ -4755,24 +4751,24 @@
       </c>
       <c r="H81" s="31"/>
       <c r="I81" s="82" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="82" spans="1:9">
       <c r="A82" s="39" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B82" s="25" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C82" s="25" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D82" s="36" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E82" s="28" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F82" s="25">
         <v>18</v>
@@ -4782,24 +4778,24 @@
       </c>
       <c r="H82" s="31"/>
       <c r="I82" s="82" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="83" spans="1:9">
       <c r="A83" s="38" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C83" s="26" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D83" s="35" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E83" s="29" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="F83" s="26">
         <v>18</v>
@@ -4809,24 +4805,24 @@
       </c>
       <c r="H83" s="32"/>
       <c r="I83" s="81" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="84" spans="1:9">
       <c r="A84" s="38" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B84" s="26" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C84" s="26" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D84" s="35" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E84" s="29" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F84" s="26">
         <v>18</v>
@@ -4836,7 +4832,7 @@
       </c>
       <c r="H84" s="32"/>
       <c r="I84" s="81" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -4844,7 +4840,7 @@
       <c r="B85" s="25"/>
       <c r="C85" s="25"/>
       <c r="D85" s="36" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E85" s="28" t="s">
         <v>11</v>
@@ -4858,13 +4854,13 @@
       <c r="A86" s="39"/>
       <c r="B86" s="25"/>
       <c r="C86" s="25" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D86" s="36" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E86" s="28" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F86" s="25"/>
       <c r="G86" s="36"/>
@@ -4873,19 +4869,19 @@
     </row>
     <row r="87" spans="1:9">
       <c r="A87" s="39" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B87" s="25" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C87" s="25" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D87" s="36" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E87" s="28" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="F87" s="25">
         <v>22</v>
@@ -4898,19 +4894,19 @@
     </row>
     <row r="88" spans="1:9">
       <c r="A88" s="39" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B88" s="25" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C88" s="25" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D88" s="36" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E88" s="28" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="F88" s="25">
         <v>22</v>
@@ -4926,7 +4922,7 @@
       <c r="B89" s="26"/>
       <c r="C89" s="26"/>
       <c r="D89" s="35" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E89" s="29" t="s">
         <v>11</v>
@@ -4941,10 +4937,10 @@
       <c r="B90" s="26"/>
       <c r="C90" s="26"/>
       <c r="D90" s="35" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E90" s="29" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F90" s="26"/>
       <c r="G90" s="35"/>
@@ -4953,56 +4949,56 @@
     </row>
     <row r="91" spans="1:9">
       <c r="A91" s="38" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B91" s="26" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C91" s="26" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D91" s="35" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E91" s="29" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="F91" s="26" t="s">
         <v>32</v>
       </c>
       <c r="G91" s="35" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="H91" s="32"/>
       <c r="I91" s="81" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="92" spans="1:9">
       <c r="A92" s="38" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B92" s="26" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C92" s="26" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D92" s="35" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E92" s="29" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F92" s="26" t="s">
         <v>32</v>
       </c>
       <c r="G92" s="35" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="H92" s="32"/>
       <c r="I92" s="81" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -5010,7 +5006,7 @@
       <c r="B93" s="25"/>
       <c r="C93" s="25"/>
       <c r="D93" s="36" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E93" s="28"/>
       <c r="F93" s="25"/>
@@ -5023,7 +5019,7 @@
       <c r="B94" s="25"/>
       <c r="C94" s="25"/>
       <c r="D94" s="36" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E94" s="28"/>
       <c r="F94" s="25"/>
@@ -5035,10 +5031,10 @@
       <c r="A95" s="39"/>
       <c r="B95" s="25"/>
       <c r="C95" s="25" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D95" s="36" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="E95" s="28"/>
       <c r="F95" s="25"/>
@@ -5048,19 +5044,19 @@
     </row>
     <row r="96" spans="1:9">
       <c r="A96" s="39" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B96" s="25" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C96" s="25" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D96" s="36" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E96" s="28" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F96" s="25">
         <v>22</v>
@@ -5070,24 +5066,24 @@
       </c>
       <c r="H96" s="31"/>
       <c r="I96" s="82" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="97" spans="1:9">
       <c r="A97" s="38" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B97" s="26" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C97" s="26" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D97" s="35" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E97" s="29" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F97" s="26">
         <v>22</v>
@@ -5097,24 +5093,24 @@
       </c>
       <c r="H97" s="32"/>
       <c r="I97" s="81" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="98" spans="1:9">
       <c r="A98" s="38" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B98" s="26" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C98" s="26" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D98" s="35" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E98" s="29" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="F98" s="26">
         <v>22</v>
@@ -5124,24 +5120,24 @@
       </c>
       <c r="H98" s="32"/>
       <c r="I98" s="89" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="99" spans="1:9">
       <c r="A99" s="38" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B99" s="26" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C99" s="26" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D99" s="35" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E99" s="29" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F99" s="26">
         <v>22</v>
@@ -5151,24 +5147,24 @@
       </c>
       <c r="H99" s="32"/>
       <c r="I99" s="81" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="100" spans="1:9">
       <c r="A100" s="38" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B100" s="26" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C100" s="26" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D100" s="35" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E100" s="29" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="F100" s="26">
         <v>22</v>
@@ -5178,24 +5174,24 @@
       </c>
       <c r="H100" s="32"/>
       <c r="I100" s="89" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="101" spans="1:9">
       <c r="A101" s="39" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B101" s="25" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C101" s="25" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D101" s="36" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E101" s="28" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F101" s="25">
         <v>22</v>
@@ -5205,24 +5201,24 @@
       </c>
       <c r="H101" s="31"/>
       <c r="I101" s="82" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="102" spans="1:9">
       <c r="A102" s="39" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B102" s="25" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C102" s="25" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D102" s="36" t="s">
+        <v>214</v>
+      </c>
+      <c r="E102" s="28" t="s">
         <v>211</v>
-      </c>
-      <c r="E102" s="28" t="s">
-        <v>208</v>
       </c>
       <c r="F102" s="25">
         <v>22</v>
@@ -5232,7 +5228,7 @@
       </c>
       <c r="H102" s="31"/>
       <c r="I102" s="88" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -5240,10 +5236,10 @@
       <c r="B103" s="25"/>
       <c r="C103" s="25"/>
       <c r="D103" s="36" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="E103" s="28" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F103" s="25"/>
       <c r="G103" s="36"/>
@@ -5255,10 +5251,10 @@
       <c r="B104" s="25"/>
       <c r="C104" s="25"/>
       <c r="D104" s="36" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="E104" s="28" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F104" s="25"/>
       <c r="G104" s="36"/>
@@ -5270,10 +5266,10 @@
       <c r="B105" s="25"/>
       <c r="C105" s="25"/>
       <c r="D105" s="36" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="E105" s="28" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="F105" s="25"/>
       <c r="G105" s="36"/>
@@ -5285,7 +5281,7 @@
       <c r="B106" s="25"/>
       <c r="C106" s="25"/>
       <c r="D106" s="36" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="E106" s="28" t="s">
         <v>11</v>
@@ -5297,16 +5293,16 @@
     </row>
     <row r="107" spans="1:9">
       <c r="A107" s="38" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B107" s="26" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C107" s="26" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D107" s="35" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E107" s="29">
         <v>12</v>
@@ -5317,21 +5313,21 @@
       <c r="G107" s="35"/>
       <c r="H107" s="32"/>
       <c r="I107" s="81" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="108" spans="1:9">
       <c r="A108" s="38" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B108" s="26" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C108" s="26" t="s">
         <v>9</v>
       </c>
       <c r="D108" s="35" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E108" s="29" t="s">
         <v>11</v>
@@ -5342,24 +5338,24 @@
       <c r="G108" s="35"/>
       <c r="H108" s="32"/>
       <c r="I108" s="81" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="109" spans="1:9">
       <c r="A109" s="39" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B109" s="25" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C109" s="25" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D109" s="36" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E109" s="28" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F109" s="25">
         <v>24</v>
@@ -5369,24 +5365,24 @@
       </c>
       <c r="H109" s="31"/>
       <c r="I109" s="82" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="110" spans="1:9">
       <c r="A110" s="39" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B110" s="25" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C110" s="25" t="s">
+        <v>232</v>
+      </c>
+      <c r="D110" s="36" t="s">
         <v>229</v>
       </c>
-      <c r="D110" s="36" t="s">
-        <v>226</v>
-      </c>
       <c r="E110" s="28" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F110" s="25">
         <v>24</v>
@@ -5396,7 +5392,7 @@
       </c>
       <c r="H110" s="31"/>
       <c r="I110" s="82" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -5404,16 +5400,16 @@
         <v>100</v>
       </c>
       <c r="B111" s="26" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C111" s="26" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D111" s="35" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="E111" s="29" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F111" s="26">
         <v>24</v>
@@ -5423,7 +5419,7 @@
       </c>
       <c r="H111" s="32"/>
       <c r="I111" s="81" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -5431,16 +5427,16 @@
         <v>100</v>
       </c>
       <c r="B112" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="C112" s="26" t="s">
         <v>232</v>
       </c>
-      <c r="C112" s="26" t="s">
-        <v>229</v>
-      </c>
       <c r="D112" s="35" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="E112" s="29" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="F112" s="26">
         <v>24</v>
@@ -5450,7 +5446,7 @@
       </c>
       <c r="H112" s="32"/>
       <c r="I112" s="81" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -5458,16 +5454,16 @@
         <v>100</v>
       </c>
       <c r="B113" s="25" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C113" s="25" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D113" s="36" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E113" s="28" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F113" s="25">
         <v>24</v>
@@ -5477,7 +5473,7 @@
       </c>
       <c r="H113" s="31"/>
       <c r="I113" s="82" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -5485,16 +5481,16 @@
         <v>100</v>
       </c>
       <c r="B114" s="25" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C114" s="25" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D114" s="36" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E114" s="28" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="F114" s="25">
         <v>24</v>
@@ -5504,7 +5500,7 @@
       </c>
       <c r="H114" s="31"/>
       <c r="I114" s="82" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -5512,16 +5508,16 @@
         <v>100</v>
       </c>
       <c r="B115" s="26" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C115" s="26" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D115" s="35" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="E115" s="29" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F115" s="26">
         <v>24</v>
@@ -5533,7 +5529,7 @@
         <v>60</v>
       </c>
       <c r="I115" s="81" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -5541,16 +5537,16 @@
         <v>100</v>
       </c>
       <c r="B116" s="26" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C116" s="26" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D116" s="35" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="E116" s="29" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="F116" s="26">
         <v>24</v>
@@ -5562,24 +5558,24 @@
         <v>60</v>
       </c>
       <c r="I116" s="81" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="117" spans="1:9">
       <c r="A117" s="39" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B117" s="25" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C117" s="25" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D117" s="36" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E117" s="28" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="F117" s="25" t="s">
         <v>32</v>
@@ -5589,21 +5585,21 @@
       </c>
       <c r="H117" s="31"/>
       <c r="I117" s="82" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="118" spans="1:9">
       <c r="A118" s="39" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B118" s="25" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C118" s="25" t="s">
         <v>9</v>
       </c>
       <c r="D118" s="36" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E118" s="28" t="s">
         <v>11</v>
@@ -5616,28 +5612,28 @@
       </c>
       <c r="H118" s="31"/>
       <c r="I118" s="82" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="119" spans="1:9">
       <c r="A119" s="41" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B119" s="42" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C119" s="42"/>
       <c r="D119" s="44" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="E119" s="30" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="F119" s="27"/>
       <c r="G119" s="37"/>
       <c r="H119" s="27"/>
       <c r="I119" s="92" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
   </sheetData>
@@ -5666,636 +5662,636 @@
   <sheetData>
     <row r="1" spans="1:11" ht="26.25" customHeight="1">
       <c r="A1" s="62" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="F1" s="75" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="18.75">
       <c r="A2" s="49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="F2" s="49"/>
     </row>
     <row r="3" spans="1:11" ht="18.75">
       <c r="A3" s="50"/>
       <c r="B3" s="54" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C3" s="48"/>
       <c r="D3" s="54"/>
       <c r="E3" s="48"/>
       <c r="F3" s="47"/>
       <c r="G3" s="53" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="69" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B4" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C4" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="F4" s="70" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G4" s="51" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="63" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B5" s="64" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C5" s="64" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D5" s="65">
         <v>18</v>
       </c>
       <c r="E5" s="66" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F5" s="67"/>
       <c r="G5" s="33" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="43" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D6" s="31">
         <v>18</v>
       </c>
       <c r="E6" s="40" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="F6" s="56"/>
       <c r="G6" s="33" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="43" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="D7" s="31">
         <v>18</v>
       </c>
       <c r="E7" s="77" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F7" s="56"/>
       <c r="G7" s="57" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="52" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D8" s="32">
         <v>18</v>
       </c>
       <c r="E8" s="68" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F8" s="55"/>
       <c r="G8" s="34" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="52" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D9" s="32">
         <v>18</v>
       </c>
       <c r="E9" s="68" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="F9" s="55"/>
       <c r="G9" s="34" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="52" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D10" s="32">
         <v>18</v>
       </c>
       <c r="E10" s="68" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F10" s="55"/>
       <c r="G10" s="34" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="K10" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="43" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="D11" s="31">
         <v>18</v>
       </c>
       <c r="E11" s="77" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F11" s="56"/>
       <c r="G11" s="57" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="43" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="D12" s="31">
         <v>18</v>
       </c>
       <c r="E12" s="77" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F12" s="56"/>
       <c r="G12" s="57" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="43" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="D13" s="31">
         <v>18</v>
       </c>
       <c r="E13" s="77" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F13" s="56"/>
       <c r="G13" s="57" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="52" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D14" s="32">
         <v>18</v>
       </c>
       <c r="E14" s="68" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F14" s="55">
         <v>40</v>
       </c>
       <c r="G14" s="34" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="52" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D15" s="32">
         <v>18</v>
       </c>
       <c r="E15" s="68" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="F15" s="55">
         <v>40</v>
       </c>
       <c r="G15" s="34" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="52" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C16" s="26" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="D16" s="32">
         <v>18</v>
       </c>
       <c r="E16" s="78" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F16" s="55">
         <v>40</v>
       </c>
       <c r="G16" s="34" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="43" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D17" s="31">
         <v>18</v>
       </c>
       <c r="E17" s="40" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F17" s="56">
         <v>40</v>
       </c>
       <c r="G17" s="33" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="43" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B18" s="25" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C18" s="25" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D18" s="31">
         <v>18</v>
       </c>
       <c r="E18" s="40" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="F18" s="56">
         <v>40</v>
       </c>
       <c r="G18" s="33" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="43" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B19" s="25" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C19" s="25" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="D19" s="31">
         <v>18</v>
       </c>
       <c r="E19" s="77" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F19" s="56">
         <v>40</v>
       </c>
       <c r="G19" s="33" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="52" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B20" s="26" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C20" s="26" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D20" s="32">
         <v>18</v>
       </c>
       <c r="E20" s="68" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F20" s="55">
         <v>40</v>
       </c>
       <c r="G20" s="34" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="52" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C21" s="26" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D21" s="32">
         <v>18</v>
       </c>
       <c r="E21" s="68" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F21" s="55"/>
       <c r="G21" s="34" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="52" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C22" s="26" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D22" s="32">
         <v>18</v>
       </c>
       <c r="E22" s="68" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="F22" s="55"/>
       <c r="G22" s="34" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="52" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B23" s="26" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C23" s="26" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="D23" s="32">
         <v>18</v>
       </c>
       <c r="E23" s="68" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="F23" s="55"/>
       <c r="G23" s="34" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="43" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B24" s="25" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D24" s="31">
         <v>18</v>
       </c>
       <c r="E24" s="40" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F24" s="56"/>
       <c r="G24" s="33" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="43" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B25" s="25" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C25" s="25" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D25" s="31">
         <v>18</v>
       </c>
       <c r="E25" s="40" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F25" s="56"/>
       <c r="G25" s="33" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="43" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B26" s="25" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C26" s="25" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D26" s="31">
         <v>18</v>
       </c>
       <c r="E26" s="40" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="F26" s="56"/>
       <c r="G26" s="33" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="43" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B27" s="25" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C27" s="25" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="D27" s="31">
         <v>18</v>
       </c>
       <c r="E27" s="77" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F27" s="56"/>
       <c r="G27" s="33" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="52" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B28" s="26" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C28" s="26" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D28" s="32">
         <v>18</v>
       </c>
       <c r="E28" s="68" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F28" s="55"/>
       <c r="G28" s="34" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="52" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B29" s="26" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C29" s="26" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D29" s="32">
         <v>18</v>
       </c>
       <c r="E29" s="68" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F29" s="55"/>
       <c r="G29" s="34" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="52" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B30" s="26" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C30" s="26" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D30" s="32">
         <v>18</v>
       </c>
       <c r="E30" s="68" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="F30" s="55"/>
       <c r="G30" s="34" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="52" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B31" s="26" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C31" s="26" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="D31" s="32">
         <v>18</v>
       </c>
       <c r="E31" s="78" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F31" s="55"/>
       <c r="G31" s="34" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -6383,7 +6379,7 @@
     <row r="1" spans="1:15">
       <c r="A1" s="5"/>
       <c r="B1" s="6" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
@@ -6399,7 +6395,7 @@
     <row r="2" spans="1:15">
       <c r="A2" s="5"/>
       <c r="B2" s="7" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -6412,717 +6408,717 @@
       <c r="K2" s="5"/>
       <c r="L2" s="16"/>
       <c r="M2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="N2" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="O2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="5"/>
       <c r="B3" s="8" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="K3" s="14" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="L3" s="17" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="M3" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="N3" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="O3" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="5"/>
       <c r="B4" s="8" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L4" s="17"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="5"/>
       <c r="B5" s="8" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K5" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L5" s="17"/>
       <c r="M5" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="5"/>
       <c r="B6" s="8" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="C6" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="G6" s="10" t="s">
         <v>340</v>
       </c>
-      <c r="D6" s="10" t="s">
-        <v>341</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>342</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>341</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>337</v>
-      </c>
       <c r="H6" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K6" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L6" s="17" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="5"/>
       <c r="B7" s="8" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D7" s="10" t="s">
+        <v>349</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>349</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>335</v>
+      </c>
+      <c r="L7" s="17" t="s">
         <v>346</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>347</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>346</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>337</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>332</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>332</v>
-      </c>
-      <c r="J7" s="10" t="s">
-        <v>332</v>
-      </c>
-      <c r="K7" s="15" t="s">
-        <v>332</v>
-      </c>
-      <c r="L7" s="17" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="5"/>
       <c r="B8" s="8" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K8" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L8" s="17"/>
       <c r="O8" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="5"/>
       <c r="B9" s="8" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L9" s="17"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="5"/>
       <c r="B10" s="8" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L10" s="17"/>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="5"/>
       <c r="B11" s="8" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L11" s="17" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="5"/>
       <c r="B12" s="8" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L12" s="17" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="5"/>
       <c r="B13" s="8" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L13" s="17"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="5"/>
       <c r="B14" s="8" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K14" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L14" s="17"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="5"/>
       <c r="B15" s="8" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K15" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L15" s="17"/>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="5"/>
       <c r="B16" s="8" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L16" s="17"/>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="5"/>
       <c r="B17" s="8" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="E17" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="F17" s="10" t="s">
         <v>372</v>
       </c>
-      <c r="F17" s="10" t="s">
-        <v>369</v>
-      </c>
       <c r="G17" s="10" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L17" s="17"/>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="5"/>
       <c r="B18" s="8" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L18" s="17"/>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="5"/>
       <c r="B19" s="8" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L19" s="17"/>
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="5"/>
       <c r="B20" s="8" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L20" s="17"/>
     </row>
     <row r="21" spans="1:15">
       <c r="A21" s="5"/>
       <c r="B21" s="8" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K21" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L21" s="17"/>
     </row>
     <row r="22" spans="1:15">
       <c r="A22" s="5"/>
       <c r="B22" s="12" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K22" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L22" s="17"/>
     </row>
@@ -7130,1485 +7126,1485 @@
       <c r="A23" s="5"/>
       <c r="B23" s="13"/>
       <c r="C23" s="10" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K23" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="5"/>
       <c r="B24" s="8" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K24" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L24" s="17"/>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="5"/>
       <c r="B25" s="8" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="I25" s="10"/>
       <c r="J25" s="10"/>
       <c r="K25" s="15"/>
       <c r="L25" s="17" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="26" spans="1:15" ht="15" customHeight="1">
       <c r="A26" s="5"/>
       <c r="B26" s="8" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K26" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L26" s="17" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="5"/>
       <c r="B27" s="8" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K27" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L27" s="17"/>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="5"/>
       <c r="B28" s="8" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K28" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L28" s="17"/>
       <c r="O28" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="5"/>
       <c r="B29" s="8" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K29" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L29" s="17"/>
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="5"/>
       <c r="B30" s="8" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K30" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L30" s="17"/>
       <c r="N30" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="31" spans="1:15">
       <c r="A31" s="5"/>
       <c r="B31" s="8" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K31" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L31" s="17"/>
     </row>
     <row r="32" spans="1:15">
       <c r="A32" s="5"/>
       <c r="B32" s="8" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K32" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L32" s="17" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="5"/>
       <c r="B33" s="8" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K33" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L33" s="17" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" s="5"/>
       <c r="B34" s="8" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K34" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L34" s="17"/>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" s="5"/>
       <c r="B35" s="8" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K35" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L35" s="17" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="M35" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="5"/>
       <c r="B36" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>442</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>443</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>444</v>
+      </c>
+      <c r="F36" s="10" t="s">
         <v>438</v>
       </c>
-      <c r="C36" s="10" t="s">
-        <v>439</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>440</v>
-      </c>
-      <c r="E36" s="10" t="s">
-        <v>441</v>
-      </c>
-      <c r="F36" s="10" t="s">
-        <v>435</v>
-      </c>
       <c r="G36" s="10" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J36" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K36" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L36" s="17"/>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" s="5"/>
       <c r="B37" s="8" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K37" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L37" s="17"/>
       <c r="N37" s="23" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" s="5"/>
       <c r="B38" s="8" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="G38" s="10" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K38" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L38" s="17"/>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" s="5"/>
       <c r="B39" s="8" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K39" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L39" s="17"/>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="5"/>
       <c r="B40" s="8" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G40" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K40" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L40" s="17" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="30">
       <c r="A41" s="5"/>
       <c r="B41" s="8" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="I41" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J41" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K41" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L41" s="17" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="5"/>
       <c r="B42" s="8" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K42" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L42" s="17"/>
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="5"/>
       <c r="B43" s="8" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J43" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K43" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L43" s="17"/>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="5"/>
       <c r="B44" s="8" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J44" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K44" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L44" s="17"/>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="5"/>
       <c r="B45" s="8" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J45" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K45" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L45" s="17"/>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="5"/>
       <c r="B46" s="8" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G46" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H46" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I46" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J46" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K46" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L46" s="17"/>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="5"/>
       <c r="B47" s="8" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I47" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J47" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K47" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L47" s="17"/>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="5"/>
       <c r="B48" s="8" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G48" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I48" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J48" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K48" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L48" s="17"/>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" s="5"/>
       <c r="B49" s="8" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I49" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J49" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K49" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L49" s="17"/>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" s="5"/>
       <c r="B50" s="8" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G50" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H50" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I50" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J50" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K50" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L50" s="17"/>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" s="5"/>
       <c r="B51" s="8" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I51" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J51" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K51" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L51" s="17"/>
     </row>
     <row r="52" spans="1:12">
       <c r="A52" s="5"/>
       <c r="B52" s="5" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G52" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H52" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I52" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J52" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K52" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L52" s="17"/>
     </row>
     <row r="53" spans="1:12">
       <c r="A53" s="5"/>
       <c r="B53" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I53" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J53" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K53" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L53" s="17"/>
     </row>
     <row r="54" spans="1:12">
       <c r="A54" s="5"/>
       <c r="B54" s="8" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G54" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H54" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I54" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J54" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K54" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L54" s="17"/>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" s="5"/>
       <c r="B55" s="8" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I55" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J55" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K55" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L55" s="17"/>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" s="5"/>
       <c r="B56" s="8" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F56" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H56" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I56" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J56" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K56" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L56" s="17"/>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" s="5"/>
       <c r="B57" s="8" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F57" s="10" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="I57" s="10" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="J57" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K57" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L57" s="17"/>
     </row>
     <row r="58" spans="1:12">
       <c r="A58" s="5"/>
       <c r="B58" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>480</v>
+      </c>
+      <c r="D58" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="E58" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="F58" s="10" t="s">
+        <v>475</v>
+      </c>
+      <c r="G58" s="10" t="s">
         <v>476</v>
       </c>
-      <c r="C58" s="10" t="s">
+      <c r="H58" s="10" t="s">
         <v>477</v>
       </c>
-      <c r="D58" s="10" t="s">
-        <v>332</v>
-      </c>
-      <c r="E58" s="10" t="s">
-        <v>332</v>
-      </c>
-      <c r="F58" s="10" t="s">
-        <v>472</v>
-      </c>
-      <c r="G58" s="10" t="s">
-        <v>473</v>
-      </c>
-      <c r="H58" s="10" t="s">
-        <v>474</v>
-      </c>
       <c r="I58" s="10" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="J58" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K58" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L58" s="17"/>
     </row>
     <row r="59" spans="1:12">
       <c r="A59" s="5"/>
       <c r="B59" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="C59" s="10" t="s">
+        <v>482</v>
+      </c>
+      <c r="D59" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="E59" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="F59" s="10" t="s">
+        <v>475</v>
+      </c>
+      <c r="G59" s="10" t="s">
+        <v>476</v>
+      </c>
+      <c r="H59" s="10" t="s">
+        <v>477</v>
+      </c>
+      <c r="I59" s="10" t="s">
         <v>478</v>
       </c>
-      <c r="C59" s="10" t="s">
-        <v>479</v>
-      </c>
-      <c r="D59" s="10" t="s">
-        <v>332</v>
-      </c>
-      <c r="E59" s="10" t="s">
-        <v>332</v>
-      </c>
-      <c r="F59" s="10" t="s">
-        <v>472</v>
-      </c>
-      <c r="G59" s="10" t="s">
-        <v>473</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>474</v>
-      </c>
-      <c r="I59" s="10" t="s">
-        <v>475</v>
-      </c>
       <c r="J59" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K59" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L59" s="17"/>
     </row>
     <row r="60" spans="1:12">
       <c r="A60" s="5"/>
       <c r="B60" s="8" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F60" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G60" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H60" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J60" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K60" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L60" s="17"/>
     </row>
     <row r="61" spans="1:12">
       <c r="A61" s="5"/>
       <c r="B61" s="8" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I61" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J61" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K61" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L61" s="17"/>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" s="5"/>
       <c r="B62" s="8" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G62" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H62" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="I62" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J62" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K62" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L62" s="17"/>
     </row>
     <row r="63" spans="1:12">
       <c r="A63" s="5"/>
       <c r="B63" s="8" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F63" s="10" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="I63" s="10" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="J63" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K63" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L63" s="17"/>
     </row>
     <row r="64" spans="1:12">
       <c r="A64" s="5"/>
       <c r="B64" s="8" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E64" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F64" s="10" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="G64" s="10" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="H64" s="10" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="J64" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K64" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L64" s="17"/>
     </row>
     <row r="65" spans="1:15">
       <c r="A65" s="5"/>
       <c r="B65" s="8" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F65" s="10" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="I65" s="10" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="J65" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K65" s="15" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L65" s="17"/>
     </row>
     <row r="66" spans="1:15">
       <c r="A66" s="5"/>
       <c r="B66" s="12" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="C66" s="5"/>
       <c r="D66" s="5"/>
@@ -8623,7 +8619,7 @@
     <row r="67" spans="1:15">
       <c r="A67" s="5"/>
       <c r="B67" s="5" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="C67" s="5"/>
       <c r="D67" s="5"/>
@@ -8635,13 +8631,13 @@
       <c r="J67" s="5"/>
       <c r="K67" s="5"/>
       <c r="O67" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="68" spans="1:15">
       <c r="A68" s="5"/>
       <c r="B68" s="5" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C68" s="5"/>
       <c r="D68" s="5"/>
@@ -8653,7 +8649,7 @@
       <c r="J68" s="5"/>
       <c r="K68" s="5"/>
       <c r="O68" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="69" spans="1:15">
@@ -8836,36 +8832,36 @@
   <sheetData>
     <row r="1" spans="1:12" ht="23.25" customHeight="1">
       <c r="A1" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B1" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C1" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E1" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="F1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="K1" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="C2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D2" s="1">
         <v>10</v>
@@ -8873,15 +8869,15 @@
       <c r="E2" s="1"/>
       <c r="G2" s="4"/>
       <c r="K2" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="C3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D3" s="1">
         <v>9</v>
@@ -8889,15 +8885,15 @@
       <c r="E3" s="1"/>
       <c r="G3" s="4"/>
       <c r="K3" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="C4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D4" s="1">
         <v>8</v>
@@ -8908,18 +8904,18 @@
         <v>15</v>
       </c>
       <c r="K4" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="L4" s="21" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="C5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D5" s="1">
         <v>7</v>
@@ -8927,15 +8923,15 @@
       <c r="E5" s="1"/>
       <c r="G5" s="4"/>
       <c r="K5" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="C6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D6" s="1">
         <v>6</v>
@@ -8945,10 +8941,10 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="C7" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D7" s="1">
         <v>5</v>
@@ -8958,10 +8954,10 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="C8" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
@@ -8971,10 +8967,10 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="C9" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D9" s="1">
         <v>3</v>
@@ -8984,10 +8980,10 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C10" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D10" s="1">
         <v>2</v>
@@ -8996,10 +8992,10 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C11" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -9505,13 +9501,13 @@
         <v>27</v>
       </c>
       <c r="B39" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="C39" t="s">
         <v>29</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="E39" s="1"/>
     </row>
@@ -9520,13 +9516,13 @@
         <v>27</v>
       </c>
       <c r="B40" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="C40" t="s">
         <v>35</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="E40" s="1"/>
     </row>
@@ -9535,13 +9531,13 @@
         <v>27</v>
       </c>
       <c r="B41" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="C41" t="s">
         <v>38</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="E41" s="1"/>
     </row>
@@ -9550,13 +9546,13 @@
         <v>27</v>
       </c>
       <c r="B42" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="C42" t="s">
         <v>41</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="E42" s="1"/>
     </row>
@@ -9565,13 +9561,13 @@
         <v>27</v>
       </c>
       <c r="B43" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="C43" t="s">
         <v>29</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E43" s="1"/>
     </row>
@@ -9580,13 +9576,13 @@
         <v>27</v>
       </c>
       <c r="B44" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="C44" t="s">
         <v>35</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E44" s="1"/>
     </row>
@@ -9595,13 +9591,13 @@
         <v>27</v>
       </c>
       <c r="B45" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="C45" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E45" s="1"/>
     </row>
@@ -9610,1151 +9606,1151 @@
         <v>27</v>
       </c>
       <c r="B46" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="C46" t="s">
         <v>41</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E46" s="1"/>
     </row>
     <row r="47" spans="1:8">
       <c r="D47" s="1" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="E47" s="1"/>
     </row>
     <row r="48" spans="1:8">
       <c r="D48" s="1" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="E48" s="1"/>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B49" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C49" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="E49" s="1"/>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
+        <v>154</v>
+      </c>
+      <c r="B50" t="s">
+        <v>155</v>
+      </c>
+      <c r="C50" t="s">
         <v>151</v>
       </c>
-      <c r="B50" t="s">
-        <v>152</v>
-      </c>
-      <c r="C50" t="s">
-        <v>148</v>
-      </c>
       <c r="D50" s="1" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="E50" s="1"/>
     </row>
     <row r="51" spans="1:5">
       <c r="D51" s="1" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="E51" s="1"/>
     </row>
     <row r="52" spans="1:5">
       <c r="D52" s="1" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="E52" s="1"/>
     </row>
     <row r="53" spans="1:5">
       <c r="D53" s="1" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="E53" s="1"/>
     </row>
     <row r="54" spans="1:5">
       <c r="D54" s="1" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="E54" s="1"/>
     </row>
     <row r="55" spans="1:5">
       <c r="D55" s="1" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="E55" s="1"/>
     </row>
     <row r="56" spans="1:5">
       <c r="D56" s="1" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="E56" s="1"/>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C57" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C58" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C59" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C60" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C61" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C62" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C63" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C64" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C65" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D65" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="E65" s="1" t="s">
         <v>520</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C66" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D66" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>520</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C67" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C68" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C69" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C70" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C71" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C72" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C73" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C74" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C75" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C76" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C77" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C78" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C79" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="E79" s="1"/>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C80" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="E80" s="1"/>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C81" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="E81" s="1"/>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C82" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E82" s="1"/>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C83" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E83" s="1"/>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C84" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E84" s="1"/>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C85" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="E85" s="1"/>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C86" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="E86" s="1"/>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C87" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="E87" s="1"/>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C88" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E88" s="1"/>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C89" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E89" s="1"/>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C90" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E90" s="1"/>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C91" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="E91" s="1"/>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C92" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="E92" s="1"/>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C93" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="E93" s="1"/>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C94" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="E94" s="1"/>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C95" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="E95" s="1"/>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C96" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="E96" s="1"/>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C97" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="E97" s="1"/>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C98" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="E98" s="1"/>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C99" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="E99" s="1"/>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C100" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="E100" s="20"/>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C101" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="E101" s="20" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C102" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="E102" s="20" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C103" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="E103" s="20"/>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C104" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="E104" s="20" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C105" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="E105" s="20" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C106" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="E106" s="20"/>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C107" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="E107" s="20" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C108" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="E108" s="20" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C109" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="E109" s="20"/>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C110" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D110" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="E110" s="20" t="s">
         <v>541</v>
-      </c>
-      <c r="E110" s="20" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C111" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="D111" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="E111" s="20" t="s">
         <v>541</v>
-      </c>
-      <c r="E111" s="20" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C112" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="E112" s="1"/>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C113" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="E113" s="20" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C114" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="E114" s="20" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="C115" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="E115" s="1"/>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="C116" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="E116" s="1"/>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="C117" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="E117" s="1"/>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="C118" t="s">
         <v>11</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="E118" s="1"/>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="C119" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="E119" s="1"/>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="C120" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="E120" s="1"/>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="C121" t="s">
         <v>11</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="E121" s="1"/>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="C122" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="E122" s="1"/>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="C123" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D123" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="E123" s="1"/>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="C124" t="s">
         <v>11</v>
       </c>
       <c r="D124" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="E124" s="1"/>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="C125" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="D125" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="E125" s="1"/>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="C126" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="D126" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="E126" s="1"/>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="C127" t="s">
+        <v>555</v>
+      </c>
+      <c r="D127" t="s">
         <v>552</v>
-      </c>
-      <c r="D127" t="s">
-        <v>549</v>
       </c>
       <c r="E127" s="1"/>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="C128" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D128" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="E128" s="1"/>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="C129" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="D129" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="E129" s="1"/>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="C130" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="D130" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="E130" s="1"/>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="C131" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="D131" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="E131" s="1"/>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="C132" t="s">
+        <v>561</v>
+      </c>
+      <c r="D132" t="s">
         <v>558</v>
-      </c>
-      <c r="D132" t="s">
-        <v>555</v>
       </c>
       <c r="E132" s="1"/>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="C133" t="s">
         <v>11</v>
       </c>
       <c r="D133" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="E133" s="1"/>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="C134" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D134" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="E134" s="1"/>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="C135" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D135" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="E135" s="1"/>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C136" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="D136" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="E136" s="1"/>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C137" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="D137" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="E137" s="1"/>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C138" t="s">
         <v>11</v>
       </c>
       <c r="D138" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="E138" s="1"/>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C139" t="s">
+        <v>565</v>
+      </c>
+      <c r="D139" t="s">
         <v>562</v>
-      </c>
-      <c r="D139" t="s">
-        <v>559</v>
       </c>
       <c r="E139" s="1"/>
     </row>
@@ -10839,13 +10835,13 @@
         <v>78</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>80</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="E159" s="3" t="s">
         <v>92</v>
@@ -10858,13 +10854,13 @@
         <v>78</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="E160" s="3" t="s">
         <v>11</v>
@@ -10874,37 +10870,37 @@
     </row>
     <row r="161" spans="1:7">
       <c r="B161" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="E161" s="1"/>
     </row>
     <row r="162" spans="1:7">
       <c r="B162" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="E162" s="1"/>
     </row>
     <row r="163" spans="1:7">
       <c r="B163" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E163" s="1"/>
     </row>
     <row r="164" spans="1:7">
       <c r="B164" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E164" s="1"/>
     </row>
@@ -10913,13 +10909,13 @@
         <v>78</v>
       </c>
       <c r="B165" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C165" t="s">
         <v>80</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>82</v>
@@ -10936,13 +10932,13 @@
         <v>78</v>
       </c>
       <c r="B166" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C166" t="s">
         <v>11</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>11</v>
@@ -10959,13 +10955,13 @@
         <v>78</v>
       </c>
       <c r="B167" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="C167" t="s">
         <v>80</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>92</v>
@@ -10982,13 +10978,13 @@
         <v>78</v>
       </c>
       <c r="B168" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="C168" t="s">
         <v>11</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>11</v>
@@ -11002,10 +10998,10 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169" s="18" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="B169" s="18" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C169" s="18"/>
       <c r="D169" s="19"/>
@@ -11015,10 +11011,10 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170" s="18" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="B170" s="18" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C170" s="18"/>
       <c r="D170" s="19"/>
@@ -11031,16 +11027,16 @@
         <v>78</v>
       </c>
       <c r="B171" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="C171" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F171">
         <v>24</v>
@@ -11054,13 +11050,13 @@
         <v>78</v>
       </c>
       <c r="B172" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="C172" t="s">
         <v>11</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>11</v>
@@ -11077,16 +11073,16 @@
         <v>78</v>
       </c>
       <c r="B173" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="C173" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F173">
         <v>24</v>
@@ -11097,52 +11093,52 @@
     </row>
     <row r="174" spans="1:7">
       <c r="B174" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="E174" s="1"/>
     </row>
     <row r="175" spans="1:7">
       <c r="B175" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="E175" s="1"/>
     </row>
     <row r="176" spans="1:7">
       <c r="B176" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="E176" s="1"/>
     </row>
     <row r="177" spans="1:7">
       <c r="B177" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="E177" s="1"/>
     </row>
     <row r="178" spans="1:7">
       <c r="A178" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E178" s="3" t="s">
         <v>15</v>
@@ -11156,19 +11152,19 @@
     </row>
     <row r="179" spans="1:7">
       <c r="A179" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F179" s="2">
         <v>24</v>
@@ -11187,19 +11183,19 @@
     </row>
     <row r="182" spans="1:7">
       <c r="A182" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B182" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="C182" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="F182">
         <v>24</v>
@@ -11210,19 +11206,19 @@
     </row>
     <row r="183" spans="1:7">
       <c r="A183" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B183" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="C183" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F183">
         <v>24</v>
@@ -11233,19 +11229,19 @@
     </row>
     <row r="184" spans="1:7">
       <c r="A184" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B184" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="C184" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="F184">
         <v>24</v>
@@ -11256,19 +11252,19 @@
     </row>
     <row r="185" spans="1:7">
       <c r="A185" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B185" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="C185" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F185">
         <v>24</v>
@@ -11279,50 +11275,50 @@
     </row>
     <row r="186" spans="1:7">
       <c r="A186" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B186" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="C186" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="187" spans="1:7">
       <c r="A187" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B187" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="C187" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="188" spans="1:7">
       <c r="A188" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B188" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C188" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>11</v>
@@ -11330,67 +11326,67 @@
     </row>
     <row r="189" spans="1:7">
       <c r="A189" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B189" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C189" t="s">
         <v>11</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="190" spans="1:7">
       <c r="A190" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B190" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C190" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="191" spans="1:7">
       <c r="A191" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B191" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C191" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="192" spans="1:7">
       <c r="A192" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B192" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="C192" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>11</v>
@@ -11404,19 +11400,19 @@
     </row>
     <row r="193" spans="1:7">
       <c r="A193" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B193" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="C193" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F193">
         <v>24</v>
@@ -11427,53 +11423,53 @@
     </row>
     <row r="194" spans="1:7">
       <c r="A194" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B194" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C194" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
     </row>
     <row r="195" spans="1:7">
       <c r="A195" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B195" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C195" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="196" spans="1:7">
       <c r="A196" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B196" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="C196" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F196">
         <v>24</v>
@@ -11484,19 +11480,19 @@
     </row>
     <row r="197" spans="1:7">
       <c r="A197" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B197" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="C197" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="F197">
         <v>24</v>
@@ -11507,19 +11503,19 @@
     </row>
     <row r="198" spans="1:7">
       <c r="A198" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B198" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C198" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F198">
         <v>24</v>
@@ -11530,19 +11526,19 @@
     </row>
     <row r="199" spans="1:7">
       <c r="A199" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B199" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C199" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="F199">
         <v>24</v>
@@ -11556,16 +11552,16 @@
         <v>78</v>
       </c>
       <c r="B200" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="C200" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F200">
         <v>24</v>
@@ -11579,16 +11575,16 @@
         <v>78</v>
       </c>
       <c r="B201" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="C201" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D201" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="E201" s="1" t="s">
         <v>211</v>
-      </c>
-      <c r="E201" s="1" t="s">
-        <v>208</v>
       </c>
       <c r="F201">
         <v>24</v>
@@ -11599,16 +11595,16 @@
     </row>
     <row r="202" spans="1:7">
       <c r="B202" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C202" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F202">
         <v>24</v>
@@ -11619,16 +11615,16 @@
     </row>
     <row r="203" spans="1:7">
       <c r="B203" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C203" t="s">
+        <v>232</v>
+      </c>
+      <c r="D203" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="D203" s="1" t="s">
-        <v>226</v>
-      </c>
       <c r="E203" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F203">
         <v>24</v>
@@ -11639,19 +11635,19 @@
     </row>
     <row r="204" spans="1:7">
       <c r="A204" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B204" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C204" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F204">
         <v>24</v>
@@ -11662,19 +11658,19 @@
     </row>
     <row r="205" spans="1:7">
       <c r="A205" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B205" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C205" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="F205">
         <v>24</v>
@@ -11685,16 +11681,16 @@
     </row>
     <row r="206" spans="1:7">
       <c r="B206" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C206" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F206">
         <v>24</v>
@@ -11705,16 +11701,16 @@
     </row>
     <row r="207" spans="1:7">
       <c r="B207" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C207" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="F207">
         <v>24</v>
@@ -11725,16 +11721,16 @@
     </row>
     <row r="208" spans="1:7">
       <c r="B208" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C208" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F208">
         <v>24</v>
@@ -11745,16 +11741,16 @@
     </row>
     <row r="209" spans="2:7">
       <c r="B209" t="s">
+        <v>235</v>
+      </c>
+      <c r="C209" t="s">
         <v>232</v>
       </c>
-      <c r="C209" t="s">
-        <v>229</v>
-      </c>
       <c r="D209" s="1" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="F209">
         <v>24</v>

--- a/V2 BETA/RRF/Valkyrie Connection Table.xlsx
+++ b/V2 BETA/RRF/Valkyrie Connection Table.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3837cd5b4a1a02ac/Document Library/GitHub/Project-Valkyrie/V2 BETA/RRF/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3329" documentId="8_{C788BE8B-89FF-47EE-BC54-747C3D562542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A2EF603-B1A7-49CA-A5DF-357A29FA3475}"/>
+  <xr:revisionPtr revIDLastSave="3331" documentId="8_{C788BE8B-89FF-47EE-BC54-747C3D562542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CA571ED-146B-48C4-A898-72895D6BCDD4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{344B6B93-88E2-4E8A-A19A-9E2625195A37}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2106" uniqueCount="589">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2108" uniqueCount="590">
   <si>
     <t>Device</t>
   </si>
@@ -1828,13 +1828,16 @@
   <si>
     <t>LC Flowmeter</t>
   </si>
+  <si>
+    <t>Chamber Fan?</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -2285,7 +2288,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2691,9 +2694,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2731,7 +2734,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2837,7 +2840,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2979,7 +2982,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5028,8 +5031,12 @@
       <c r="I94" s="84"/>
     </row>
     <row r="95" spans="1:9">
-      <c r="A95" s="39"/>
-      <c r="B95" s="25"/>
+      <c r="A95" s="39" t="s">
+        <v>161</v>
+      </c>
+      <c r="B95" s="25" t="s">
+        <v>589</v>
+      </c>
       <c r="C95" s="25" t="s">
         <v>177</v>
       </c>

--- a/V2 BETA/RRF/Valkyrie Connection Table.xlsx
+++ b/V2 BETA/RRF/Valkyrie Connection Table.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30203"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3837cd5b4a1a02ac/Document Library/GitHub/Project-Valkyrie/V2 BETA/RRF/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3331" documentId="8_{C788BE8B-89FF-47EE-BC54-747C3D562542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CA571ED-146B-48C4-A898-72895D6BCDD4}"/>
+  <xr:revisionPtr revIDLastSave="3333" documentId="8_{C788BE8B-89FF-47EE-BC54-747C3D562542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7DD21833-0D63-4B9E-B0C2-54BA7F8F02CD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{344B6B93-88E2-4E8A-A19A-9E2625195A37}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2108" uniqueCount="590">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2109" uniqueCount="589">
   <si>
     <t>Device</t>
   </si>
@@ -627,7 +627,13 @@
     <t>OUT 6_vout</t>
   </si>
   <si>
+    <t>Chamber Fan</t>
+  </si>
+  <si>
     <t>OUT 6_tach</t>
+  </si>
+  <si>
+    <t>out6.tach</t>
   </si>
   <si>
     <t>CPAP Robo</t>
@@ -1325,9 +1331,6 @@
     <t>fan3</t>
   </si>
   <si>
-    <t>Chamber Fan</t>
-  </si>
-  <si>
     <t>Fan 4</t>
   </si>
   <si>
@@ -1817,9 +1820,6 @@
     <t>OUT 6</t>
   </si>
   <si>
-    <t>out6.tach</t>
-  </si>
-  <si>
     <t>Fan dbx</t>
   </si>
   <si>
@@ -1827,9 +1827,6 @@
   </si>
   <si>
     <t>LC Flowmeter</t>
-  </si>
-  <si>
-    <t>Chamber Fan?</t>
   </si>
 </sst>
 </file>
@@ -1837,7 +1834,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -2288,7 +2285,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2694,9 +2691,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2734,7 +2731,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2840,7 +2837,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2982,7 +2979,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5035,15 +5032,17 @@
         <v>161</v>
       </c>
       <c r="B95" s="25" t="s">
-        <v>589</v>
+        <v>195</v>
       </c>
       <c r="C95" s="25" t="s">
         <v>177</v>
       </c>
       <c r="D95" s="36" t="s">
-        <v>195</v>
-      </c>
-      <c r="E95" s="28"/>
+        <v>196</v>
+      </c>
+      <c r="E95" s="28" t="s">
+        <v>197</v>
+      </c>
       <c r="F95" s="25"/>
       <c r="G95" s="36"/>
       <c r="H95" s="31"/>
@@ -5051,19 +5050,19 @@
     </row>
     <row r="96" spans="1:9">
       <c r="A96" s="39" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B96" s="25" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C96" s="25" t="s">
         <v>180</v>
       </c>
       <c r="D96" s="36" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E96" s="28" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F96" s="25">
         <v>22</v>
@@ -5073,24 +5072,24 @@
       </c>
       <c r="H96" s="31"/>
       <c r="I96" s="82" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="97" spans="1:9">
       <c r="A97" s="38" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B97" s="26" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C97" s="26" t="s">
         <v>148</v>
       </c>
       <c r="D97" s="35" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E97" s="29" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F97" s="26">
         <v>22</v>
@@ -5100,24 +5099,24 @@
       </c>
       <c r="H97" s="32"/>
       <c r="I97" s="81" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="98" spans="1:9">
       <c r="A98" s="38" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B98" s="26" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C98" s="26" t="s">
         <v>151</v>
       </c>
       <c r="D98" s="35" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E98" s="29" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F98" s="26">
         <v>22</v>
@@ -5127,24 +5126,24 @@
       </c>
       <c r="H98" s="32"/>
       <c r="I98" s="89" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="99" spans="1:9">
       <c r="A99" s="38" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B99" s="26" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C99" s="26" t="s">
         <v>148</v>
       </c>
       <c r="D99" s="35" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E99" s="29" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F99" s="26">
         <v>22</v>
@@ -5154,24 +5153,24 @@
       </c>
       <c r="H99" s="32"/>
       <c r="I99" s="81" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="100" spans="1:9">
       <c r="A100" s="38" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B100" s="26" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C100" s="26" t="s">
         <v>151</v>
       </c>
       <c r="D100" s="35" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E100" s="29" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F100" s="26">
         <v>22</v>
@@ -5181,24 +5180,24 @@
       </c>
       <c r="H100" s="32"/>
       <c r="I100" s="89" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="101" spans="1:9">
       <c r="A101" s="39" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B101" s="25" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C101" s="25" t="s">
         <v>148</v>
       </c>
       <c r="D101" s="36" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E101" s="28" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F101" s="25">
         <v>22</v>
@@ -5208,24 +5207,24 @@
       </c>
       <c r="H101" s="31"/>
       <c r="I101" s="82" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="102" spans="1:9">
       <c r="A102" s="39" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B102" s="25" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C102" s="25" t="s">
         <v>151</v>
       </c>
       <c r="D102" s="36" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E102" s="28" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F102" s="25">
         <v>22</v>
@@ -5235,7 +5234,7 @@
       </c>
       <c r="H102" s="31"/>
       <c r="I102" s="88" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -5243,10 +5242,10 @@
       <c r="B103" s="25"/>
       <c r="C103" s="25"/>
       <c r="D103" s="36" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E103" s="28" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F103" s="25"/>
       <c r="G103" s="36"/>
@@ -5258,10 +5257,10 @@
       <c r="B104" s="25"/>
       <c r="C104" s="25"/>
       <c r="D104" s="36" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E104" s="28" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F104" s="25"/>
       <c r="G104" s="36"/>
@@ -5273,10 +5272,10 @@
       <c r="B105" s="25"/>
       <c r="C105" s="25"/>
       <c r="D105" s="36" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E105" s="28" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F105" s="25"/>
       <c r="G105" s="36"/>
@@ -5288,7 +5287,7 @@
       <c r="B106" s="25"/>
       <c r="C106" s="25"/>
       <c r="D106" s="36" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E106" s="28" t="s">
         <v>11</v>
@@ -5300,16 +5299,16 @@
     </row>
     <row r="107" spans="1:9">
       <c r="A107" s="38" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B107" s="26" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C107" s="26" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D107" s="35" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E107" s="29">
         <v>12</v>
@@ -5320,21 +5319,21 @@
       <c r="G107" s="35"/>
       <c r="H107" s="32"/>
       <c r="I107" s="81" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="108" spans="1:9">
       <c r="A108" s="38" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B108" s="26" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C108" s="26" t="s">
         <v>9</v>
       </c>
       <c r="D108" s="35" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E108" s="29" t="s">
         <v>11</v>
@@ -5345,24 +5344,24 @@
       <c r="G108" s="35"/>
       <c r="H108" s="32"/>
       <c r="I108" s="81" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="109" spans="1:9">
       <c r="A109" s="39" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B109" s="25" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C109" s="25" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D109" s="36" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E109" s="28" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F109" s="25">
         <v>24</v>
@@ -5372,24 +5371,24 @@
       </c>
       <c r="H109" s="31"/>
       <c r="I109" s="82" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="110" spans="1:9">
       <c r="A110" s="39" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B110" s="25" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C110" s="25" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D110" s="36" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E110" s="28" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F110" s="25">
         <v>24</v>
@@ -5399,7 +5398,7 @@
       </c>
       <c r="H110" s="31"/>
       <c r="I110" s="82" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -5407,16 +5406,16 @@
         <v>100</v>
       </c>
       <c r="B111" s="26" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C111" s="26" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D111" s="35" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E111" s="29" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F111" s="26">
         <v>24</v>
@@ -5426,7 +5425,7 @@
       </c>
       <c r="H111" s="32"/>
       <c r="I111" s="81" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -5434,16 +5433,16 @@
         <v>100</v>
       </c>
       <c r="B112" s="26" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C112" s="26" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D112" s="35" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E112" s="29" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F112" s="26">
         <v>24</v>
@@ -5453,7 +5452,7 @@
       </c>
       <c r="H112" s="32"/>
       <c r="I112" s="81" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -5461,16 +5460,16 @@
         <v>100</v>
       </c>
       <c r="B113" s="25" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C113" s="25" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D113" s="36" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E113" s="28" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F113" s="25">
         <v>24</v>
@@ -5480,7 +5479,7 @@
       </c>
       <c r="H113" s="31"/>
       <c r="I113" s="82" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -5488,16 +5487,16 @@
         <v>100</v>
       </c>
       <c r="B114" s="25" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C114" s="25" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D114" s="36" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E114" s="28" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F114" s="25">
         <v>24</v>
@@ -5507,7 +5506,7 @@
       </c>
       <c r="H114" s="31"/>
       <c r="I114" s="82" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -5515,16 +5514,16 @@
         <v>100</v>
       </c>
       <c r="B115" s="26" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C115" s="26" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D115" s="35" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E115" s="29" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F115" s="26">
         <v>24</v>
@@ -5536,7 +5535,7 @@
         <v>60</v>
       </c>
       <c r="I115" s="81" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -5544,16 +5543,16 @@
         <v>100</v>
       </c>
       <c r="B116" s="26" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C116" s="26" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D116" s="35" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E116" s="29" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F116" s="26">
         <v>24</v>
@@ -5565,7 +5564,7 @@
         <v>60</v>
       </c>
       <c r="I116" s="81" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -5573,13 +5572,13 @@
         <v>161</v>
       </c>
       <c r="B117" s="25" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C117" s="25" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D117" s="36" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E117" s="28" t="s">
         <v>157</v>
@@ -5592,7 +5591,7 @@
       </c>
       <c r="H117" s="31"/>
       <c r="I117" s="82" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -5600,13 +5599,13 @@
         <v>161</v>
       </c>
       <c r="B118" s="25" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C118" s="25" t="s">
         <v>9</v>
       </c>
       <c r="D118" s="36" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E118" s="28" t="s">
         <v>11</v>
@@ -5619,28 +5618,28 @@
       </c>
       <c r="H118" s="31"/>
       <c r="I118" s="82" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="119" spans="1:9">
       <c r="A119" s="41" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B119" s="42" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C119" s="42"/>
       <c r="D119" s="44" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E119" s="30" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F119" s="27"/>
       <c r="G119" s="37"/>
       <c r="H119" s="27"/>
       <c r="I119" s="92" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -5669,636 +5668,636 @@
   <sheetData>
     <row r="1" spans="1:11" ht="26.25" customHeight="1">
       <c r="A1" s="62" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F1" s="75" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="18.75">
       <c r="A2" s="49" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F2" s="49"/>
     </row>
     <row r="3" spans="1:11" ht="18.75">
       <c r="A3" s="50"/>
       <c r="B3" s="54" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C3" s="48"/>
       <c r="D3" s="54"/>
       <c r="E3" s="48"/>
       <c r="F3" s="47"/>
       <c r="G3" s="53" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="69" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F4" s="70" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G4" s="51" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="63" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B5" s="64" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C5" s="64" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D5" s="65">
         <v>18</v>
       </c>
       <c r="E5" s="66" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F5" s="67"/>
       <c r="G5" s="33" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="43" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D6" s="31">
         <v>18</v>
       </c>
       <c r="E6" s="40" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F6" s="56"/>
       <c r="G6" s="33" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="43" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D7" s="31">
         <v>18</v>
       </c>
       <c r="E7" s="77" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F7" s="56"/>
       <c r="G7" s="57" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="52" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D8" s="32">
         <v>18</v>
       </c>
       <c r="E8" s="68" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F8" s="55"/>
       <c r="G8" s="34" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="52" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D9" s="32">
         <v>18</v>
       </c>
       <c r="E9" s="68" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F9" s="55"/>
       <c r="G9" s="34" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="52" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D10" s="32">
         <v>18</v>
       </c>
       <c r="E10" s="68" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F10" s="55"/>
       <c r="G10" s="34" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="K10" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="43" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D11" s="31">
         <v>18</v>
       </c>
       <c r="E11" s="77" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F11" s="56"/>
       <c r="G11" s="57" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="43" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D12" s="31">
         <v>18</v>
       </c>
       <c r="E12" s="77" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F12" s="56"/>
       <c r="G12" s="57" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="43" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D13" s="31">
         <v>18</v>
       </c>
       <c r="E13" s="77" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F13" s="56"/>
       <c r="G13" s="57" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="52" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D14" s="32">
         <v>18</v>
       </c>
       <c r="E14" s="68" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F14" s="55">
         <v>40</v>
       </c>
       <c r="G14" s="34" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="52" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D15" s="32">
         <v>18</v>
       </c>
       <c r="E15" s="68" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F15" s="55">
         <v>40</v>
       </c>
       <c r="G15" s="34" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="52" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C16" s="26" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D16" s="32">
         <v>18</v>
       </c>
       <c r="E16" s="78" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F16" s="55">
         <v>40</v>
       </c>
       <c r="G16" s="34" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="43" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D17" s="31">
         <v>18</v>
       </c>
       <c r="E17" s="40" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F17" s="56">
         <v>40</v>
       </c>
       <c r="G17" s="33" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="43" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B18" s="25" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C18" s="25" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D18" s="31">
         <v>18</v>
       </c>
       <c r="E18" s="40" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F18" s="56">
         <v>40</v>
       </c>
       <c r="G18" s="33" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="43" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B19" s="25" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C19" s="25" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D19" s="31">
         <v>18</v>
       </c>
       <c r="E19" s="77" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F19" s="56">
         <v>40</v>
       </c>
       <c r="G19" s="33" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="52" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B20" s="26" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C20" s="26" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D20" s="32">
         <v>18</v>
       </c>
       <c r="E20" s="68" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F20" s="55">
         <v>40</v>
       </c>
       <c r="G20" s="34" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="52" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C21" s="26" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D21" s="32">
         <v>18</v>
       </c>
       <c r="E21" s="68" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F21" s="55"/>
       <c r="G21" s="34" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="52" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C22" s="26" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D22" s="32">
         <v>18</v>
       </c>
       <c r="E22" s="68" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F22" s="55"/>
       <c r="G22" s="34" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="52" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B23" s="26" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C23" s="26" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D23" s="32">
         <v>18</v>
       </c>
       <c r="E23" s="68" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F23" s="55"/>
       <c r="G23" s="34" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="43" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B24" s="25" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D24" s="31">
         <v>18</v>
       </c>
       <c r="E24" s="40" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F24" s="56"/>
       <c r="G24" s="33" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="43" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B25" s="25" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C25" s="25" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D25" s="31">
         <v>18</v>
       </c>
       <c r="E25" s="40" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F25" s="56"/>
       <c r="G25" s="33" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="43" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B26" s="25" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C26" s="25" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D26" s="31">
         <v>18</v>
       </c>
       <c r="E26" s="40" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F26" s="56"/>
       <c r="G26" s="33" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="43" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B27" s="25" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C27" s="25" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D27" s="31">
         <v>18</v>
       </c>
       <c r="E27" s="77" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F27" s="56"/>
       <c r="G27" s="33" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="52" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B28" s="26" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C28" s="26" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D28" s="32">
         <v>18</v>
       </c>
       <c r="E28" s="68" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F28" s="55"/>
       <c r="G28" s="34" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="52" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B29" s="26" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C29" s="26" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D29" s="32">
         <v>18</v>
       </c>
       <c r="E29" s="68" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F29" s="55"/>
       <c r="G29" s="34" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="52" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B30" s="26" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C30" s="26" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D30" s="32">
         <v>18</v>
       </c>
       <c r="E30" s="68" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F30" s="55"/>
       <c r="G30" s="34" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="52" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B31" s="26" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C31" s="26" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D31" s="32">
         <v>18</v>
       </c>
       <c r="E31" s="78" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F31" s="55"/>
       <c r="G31" s="34" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -6386,7 +6385,7 @@
     <row r="1" spans="1:15">
       <c r="A1" s="5"/>
       <c r="B1" s="6" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
@@ -6402,7 +6401,7 @@
     <row r="2" spans="1:15">
       <c r="A2" s="5"/>
       <c r="B2" s="7" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -6415,717 +6414,717 @@
       <c r="K2" s="5"/>
       <c r="L2" s="16"/>
       <c r="M2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="N2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="O2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="5"/>
       <c r="B3" s="8" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K3" s="14" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L3" s="17" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="M3" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="N3" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="O3" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="5"/>
       <c r="B4" s="8" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L4" s="17"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="5"/>
       <c r="B5" s="8" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K5" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L5" s="17"/>
       <c r="M5" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="5"/>
       <c r="B6" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>347</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="G6" s="10" t="s">
         <v>342</v>
       </c>
-      <c r="C6" s="10" t="s">
-        <v>343</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>344</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>345</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>344</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>340</v>
-      </c>
       <c r="H6" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K6" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L6" s="17" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="5"/>
       <c r="B7" s="8" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C7" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>351</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>351</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>337</v>
+      </c>
+      <c r="L7" s="17" t="s">
         <v>348</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>349</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>350</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>349</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>340</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>335</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>335</v>
-      </c>
-      <c r="J7" s="10" t="s">
-        <v>335</v>
-      </c>
-      <c r="K7" s="15" t="s">
-        <v>335</v>
-      </c>
-      <c r="L7" s="17" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="5"/>
       <c r="B8" s="8" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K8" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L8" s="17"/>
       <c r="O8" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="5"/>
       <c r="B9" s="8" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L9" s="17"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="5"/>
       <c r="B10" s="8" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L10" s="17"/>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="5"/>
       <c r="B11" s="8" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L11" s="17" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="5"/>
       <c r="B12" s="8" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L12" s="17" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="5"/>
       <c r="B13" s="8" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L13" s="17"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="5"/>
       <c r="B14" s="8" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K14" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L14" s="17"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="5"/>
       <c r="B15" s="8" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K15" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L15" s="17"/>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="5"/>
       <c r="B16" s="8" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F16" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="H16" s="11" t="s">
         <v>372</v>
       </c>
-      <c r="G16" s="10" t="s">
-        <v>340</v>
-      </c>
-      <c r="H16" s="11" t="s">
-        <v>370</v>
-      </c>
       <c r="I16" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L16" s="17"/>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="5"/>
       <c r="B17" s="8" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D17" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="F17" s="10" t="s">
         <v>374</v>
       </c>
-      <c r="E17" s="10" t="s">
-        <v>375</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>372</v>
-      </c>
       <c r="G17" s="10" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L17" s="17"/>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="5"/>
       <c r="B18" s="8" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L18" s="17"/>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="5"/>
       <c r="B19" s="8" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L19" s="17"/>
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="5"/>
       <c r="B20" s="8" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L20" s="17"/>
     </row>
     <row r="21" spans="1:15">
       <c r="A21" s="5"/>
       <c r="B21" s="8" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K21" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L21" s="17"/>
     </row>
     <row r="22" spans="1:15">
       <c r="A22" s="5"/>
       <c r="B22" s="12" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K22" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L22" s="17"/>
     </row>
@@ -7133,1485 +7132,1485 @@
       <c r="A23" s="5"/>
       <c r="B23" s="13"/>
       <c r="C23" s="10" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K23" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="5"/>
       <c r="B24" s="8" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K24" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L24" s="17"/>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="5"/>
       <c r="B25" s="8" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="F25" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="H25" s="10" t="s">
         <v>401</v>
-      </c>
-      <c r="G25" s="10" t="s">
-        <v>340</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>399</v>
       </c>
       <c r="I25" s="10"/>
       <c r="J25" s="10"/>
       <c r="K25" s="15"/>
       <c r="L25" s="17" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="26" spans="1:15" ht="15" customHeight="1">
       <c r="A26" s="5"/>
       <c r="B26" s="8" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E26" s="10" t="s">
+        <v>408</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="G26" s="10" t="s">
         <v>406</v>
       </c>
-      <c r="F26" s="10" t="s">
-        <v>340</v>
-      </c>
-      <c r="G26" s="10" t="s">
-        <v>404</v>
-      </c>
       <c r="H26" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K26" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L26" s="17" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="5"/>
       <c r="B27" s="8" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K27" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L27" s="17"/>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="5"/>
       <c r="B28" s="8" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E28" s="10" t="s">
+        <v>418</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="G28" s="10" t="s">
         <v>416</v>
       </c>
-      <c r="F28" s="10" t="s">
-        <v>340</v>
-      </c>
-      <c r="G28" s="10" t="s">
-        <v>414</v>
-      </c>
       <c r="H28" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K28" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L28" s="17"/>
       <c r="O28" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="5"/>
       <c r="B29" s="8" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E29" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="G29" s="10" t="s">
         <v>420</v>
       </c>
-      <c r="F29" s="10" t="s">
-        <v>340</v>
-      </c>
-      <c r="G29" s="10" t="s">
-        <v>418</v>
-      </c>
       <c r="H29" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K29" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L29" s="17"/>
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="5"/>
       <c r="B30" s="8" t="s">
-        <v>421</v>
+        <v>195</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D30" s="10" t="s">
+        <v>424</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="G30" s="10" t="s">
         <v>423</v>
       </c>
-      <c r="E30" s="10" t="s">
-        <v>424</v>
-      </c>
-      <c r="F30" s="10" t="s">
-        <v>340</v>
-      </c>
-      <c r="G30" s="10" t="s">
-        <v>422</v>
-      </c>
       <c r="H30" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K30" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L30" s="17"/>
       <c r="N30" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="31" spans="1:15">
       <c r="A31" s="5"/>
       <c r="B31" s="8" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D31" s="10" t="s">
+        <v>429</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>430</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="G31" s="10" t="s">
         <v>428</v>
       </c>
-      <c r="E31" s="10" t="s">
-        <v>429</v>
-      </c>
-      <c r="F31" s="10" t="s">
-        <v>340</v>
-      </c>
-      <c r="G31" s="10" t="s">
-        <v>427</v>
-      </c>
       <c r="H31" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K31" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L31" s="17"/>
     </row>
     <row r="32" spans="1:15">
       <c r="A32" s="5"/>
       <c r="B32" s="8" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K32" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L32" s="17" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="5"/>
       <c r="B33" s="8" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C33" s="10" t="s">
+        <v>433</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>433</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="I33" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="J33" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="K33" s="15" t="s">
+        <v>337</v>
+      </c>
+      <c r="L33" s="17" t="s">
         <v>432</v>
-      </c>
-      <c r="D33" s="10" t="s">
-        <v>335</v>
-      </c>
-      <c r="E33" s="10" t="s">
-        <v>335</v>
-      </c>
-      <c r="F33" s="10" t="s">
-        <v>340</v>
-      </c>
-      <c r="G33" s="10" t="s">
-        <v>432</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>335</v>
-      </c>
-      <c r="I33" s="10" t="s">
-        <v>335</v>
-      </c>
-      <c r="J33" s="10" t="s">
-        <v>335</v>
-      </c>
-      <c r="K33" s="15" t="s">
-        <v>335</v>
-      </c>
-      <c r="L33" s="17" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" s="5"/>
       <c r="B34" s="8" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K34" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L34" s="17"/>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" s="5"/>
       <c r="B35" s="8" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K35" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L35" s="17" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M35" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="5"/>
       <c r="B36" s="8" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J36" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K36" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L36" s="17"/>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" s="5"/>
       <c r="B37" s="8" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K37" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L37" s="17"/>
       <c r="N37" s="23" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" s="5"/>
       <c r="B38" s="8" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="G38" s="10" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K38" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L38" s="17"/>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" s="5"/>
       <c r="B39" s="8" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K39" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L39" s="17"/>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="5"/>
       <c r="B40" s="8" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G40" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K40" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L40" s="17" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="30">
       <c r="A41" s="5"/>
       <c r="B41" s="8" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="I41" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J41" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K41" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L41" s="17" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="5"/>
       <c r="B42" s="8" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K42" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L42" s="17"/>
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="5"/>
       <c r="B43" s="8" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J43" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K43" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L43" s="17"/>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="5"/>
       <c r="B44" s="8" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J44" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K44" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L44" s="17"/>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="5"/>
       <c r="B45" s="8" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J45" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K45" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L45" s="17"/>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="5"/>
       <c r="B46" s="8" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G46" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H46" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I46" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J46" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K46" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L46" s="17"/>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="5"/>
       <c r="B47" s="8" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I47" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J47" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K47" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L47" s="17"/>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="5"/>
       <c r="B48" s="8" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G48" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I48" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J48" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K48" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L48" s="17"/>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" s="5"/>
       <c r="B49" s="8" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I49" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J49" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K49" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L49" s="17"/>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" s="5"/>
       <c r="B50" s="8" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G50" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H50" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I50" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J50" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K50" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L50" s="17"/>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" s="5"/>
       <c r="B51" s="8" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I51" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J51" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K51" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L51" s="17"/>
     </row>
     <row r="52" spans="1:12">
       <c r="A52" s="5"/>
       <c r="B52" s="5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G52" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H52" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I52" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J52" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K52" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L52" s="17"/>
     </row>
     <row r="53" spans="1:12">
       <c r="A53" s="5"/>
       <c r="B53" s="7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I53" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J53" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K53" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L53" s="17"/>
     </row>
     <row r="54" spans="1:12">
       <c r="A54" s="5"/>
       <c r="B54" s="8" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G54" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H54" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I54" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J54" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K54" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L54" s="17"/>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" s="5"/>
       <c r="B55" s="8" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I55" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J55" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K55" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L55" s="17"/>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" s="5"/>
       <c r="B56" s="8" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F56" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H56" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I56" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J56" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K56" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L56" s="17"/>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" s="5"/>
       <c r="B57" s="8" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F57" s="10" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="I57" s="10" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="J57" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K57" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L57" s="17"/>
     </row>
     <row r="58" spans="1:12">
       <c r="A58" s="5"/>
       <c r="B58" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>481</v>
+      </c>
+      <c r="D58" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="E58" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="F58" s="10" t="s">
+        <v>476</v>
+      </c>
+      <c r="G58" s="10" t="s">
+        <v>477</v>
+      </c>
+      <c r="H58" s="10" t="s">
+        <v>478</v>
+      </c>
+      <c r="I58" s="10" t="s">
         <v>479</v>
       </c>
-      <c r="C58" s="10" t="s">
-        <v>480</v>
-      </c>
-      <c r="D58" s="10" t="s">
-        <v>335</v>
-      </c>
-      <c r="E58" s="10" t="s">
-        <v>335</v>
-      </c>
-      <c r="F58" s="10" t="s">
-        <v>475</v>
-      </c>
-      <c r="G58" s="10" t="s">
-        <v>476</v>
-      </c>
-      <c r="H58" s="10" t="s">
-        <v>477</v>
-      </c>
-      <c r="I58" s="10" t="s">
-        <v>478</v>
-      </c>
       <c r="J58" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K58" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L58" s="17"/>
     </row>
     <row r="59" spans="1:12">
       <c r="A59" s="5"/>
       <c r="B59" s="8" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="J59" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K59" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L59" s="17"/>
     </row>
     <row r="60" spans="1:12">
       <c r="A60" s="5"/>
       <c r="B60" s="8" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F60" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G60" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H60" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J60" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K60" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L60" s="17"/>
     </row>
     <row r="61" spans="1:12">
       <c r="A61" s="5"/>
       <c r="B61" s="8" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I61" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J61" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K61" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L61" s="17"/>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" s="5"/>
       <c r="B62" s="8" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G62" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H62" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I62" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J62" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K62" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L62" s="17"/>
     </row>
     <row r="63" spans="1:12">
       <c r="A63" s="5"/>
       <c r="B63" s="8" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F63" s="10" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="I63" s="10" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="J63" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K63" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L63" s="17"/>
     </row>
     <row r="64" spans="1:12">
       <c r="A64" s="5"/>
       <c r="B64" s="8" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E64" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F64" s="10" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="G64" s="10" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H64" s="10" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="J64" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K64" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L64" s="17"/>
     </row>
     <row r="65" spans="1:15">
       <c r="A65" s="5"/>
       <c r="B65" s="8" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F65" s="10" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="I65" s="10" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="J65" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K65" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L65" s="17"/>
     </row>
     <row r="66" spans="1:15">
       <c r="A66" s="5"/>
       <c r="B66" s="12" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C66" s="5"/>
       <c r="D66" s="5"/>
@@ -8626,7 +8625,7 @@
     <row r="67" spans="1:15">
       <c r="A67" s="5"/>
       <c r="B67" s="5" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C67" s="5"/>
       <c r="D67" s="5"/>
@@ -8638,13 +8637,13 @@
       <c r="J67" s="5"/>
       <c r="K67" s="5"/>
       <c r="O67" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="68" spans="1:15">
       <c r="A68" s="5"/>
       <c r="B68" s="5" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C68" s="5"/>
       <c r="D68" s="5"/>
@@ -8656,7 +8655,7 @@
       <c r="J68" s="5"/>
       <c r="K68" s="5"/>
       <c r="O68" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="69" spans="1:15">
@@ -8839,33 +8838,33 @@
   <sheetData>
     <row r="1" spans="1:12" ht="23.25" customHeight="1">
       <c r="A1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="K1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C2" t="s">
         <v>148</v>
@@ -8876,12 +8875,12 @@
       <c r="E2" s="1"/>
       <c r="G2" s="4"/>
       <c r="K2" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C3" t="s">
         <v>151</v>
@@ -8892,12 +8891,12 @@
       <c r="E3" s="1"/>
       <c r="G3" s="4"/>
       <c r="K3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C4" t="s">
         <v>148</v>
@@ -8911,15 +8910,15 @@
         <v>15</v>
       </c>
       <c r="K4" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="L4" s="21" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C5" t="s">
         <v>151</v>
@@ -8930,12 +8929,12 @@
       <c r="E5" s="1"/>
       <c r="G5" s="4"/>
       <c r="K5" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C6" t="s">
         <v>148</v>
@@ -8948,7 +8947,7 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C7" t="s">
         <v>151</v>
@@ -8961,7 +8960,7 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C8" t="s">
         <v>148</v>
@@ -8974,7 +8973,7 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C9" t="s">
         <v>151</v>
@@ -8987,7 +8986,7 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C10" t="s">
         <v>148</v>
@@ -8999,7 +8998,7 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C11" t="s">
         <v>151</v>
@@ -9508,13 +9507,13 @@
         <v>27</v>
       </c>
       <c r="B39" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C39" t="s">
         <v>29</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E39" s="1"/>
     </row>
@@ -9523,13 +9522,13 @@
         <v>27</v>
       </c>
       <c r="B40" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C40" t="s">
         <v>35</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E40" s="1"/>
     </row>
@@ -9538,13 +9537,13 @@
         <v>27</v>
       </c>
       <c r="B41" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C41" t="s">
         <v>38</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E41" s="1"/>
     </row>
@@ -9553,13 +9552,13 @@
         <v>27</v>
       </c>
       <c r="B42" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C42" t="s">
         <v>41</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E42" s="1"/>
     </row>
@@ -9568,13 +9567,13 @@
         <v>27</v>
       </c>
       <c r="B43" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C43" t="s">
         <v>29</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E43" s="1"/>
     </row>
@@ -9583,13 +9582,13 @@
         <v>27</v>
       </c>
       <c r="B44" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C44" t="s">
         <v>35</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E44" s="1"/>
     </row>
@@ -9598,13 +9597,13 @@
         <v>27</v>
       </c>
       <c r="B45" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C45" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E45" s="1"/>
     </row>
@@ -9613,25 +9612,25 @@
         <v>27</v>
       </c>
       <c r="B46" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C46" t="s">
         <v>41</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E46" s="1"/>
     </row>
     <row r="47" spans="1:8">
       <c r="D47" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E47" s="1"/>
     </row>
     <row r="48" spans="1:8">
       <c r="D48" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E48" s="1"/>
     </row>
@@ -9646,7 +9645,7 @@
         <v>148</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E49" s="1"/>
     </row>
@@ -9661,43 +9660,43 @@
         <v>151</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E50" s="1"/>
     </row>
     <row r="51" spans="1:5">
       <c r="D51" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E51" s="1"/>
     </row>
     <row r="52" spans="1:5">
       <c r="D52" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E52" s="1"/>
     </row>
     <row r="53" spans="1:5">
       <c r="D53" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E53" s="1"/>
     </row>
     <row r="54" spans="1:5">
       <c r="D54" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E54" s="1"/>
     </row>
     <row r="55" spans="1:5">
       <c r="D55" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E55" s="1"/>
     </row>
     <row r="56" spans="1:5">
       <c r="D56" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E56" s="1"/>
     </row>
@@ -9709,10 +9708,10 @@
         <v>148</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -9723,10 +9722,10 @@
         <v>151</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -9737,10 +9736,10 @@
         <v>148</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -9751,10 +9750,10 @@
         <v>151</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -9765,10 +9764,10 @@
         <v>148</v>
       </c>
       <c r="D61" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="E61" s="1" t="s">
         <v>521</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -9779,10 +9778,10 @@
         <v>151</v>
       </c>
       <c r="D62" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="E62" s="1" t="s">
         <v>521</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -9793,10 +9792,10 @@
         <v>148</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -9807,10 +9806,10 @@
         <v>151</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -9821,10 +9820,10 @@
         <v>148</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -9835,10 +9834,10 @@
         <v>151</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -9849,10 +9848,10 @@
         <v>148</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -9863,10 +9862,10 @@
         <v>151</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -9877,10 +9876,10 @@
         <v>148</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -9891,10 +9890,10 @@
         <v>151</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -9905,10 +9904,10 @@
         <v>148</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -9919,10 +9918,10 @@
         <v>151</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -9933,10 +9932,10 @@
         <v>148</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -9947,10 +9946,10 @@
         <v>151</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -9961,10 +9960,10 @@
         <v>148</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -9975,10 +9974,10 @@
         <v>151</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -9992,7 +9991,7 @@
         <v>161</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -10006,758 +10005,758 @@
         <v>161</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C79" t="s">
         <v>148</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E79" s="1"/>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C80" t="s">
         <v>151</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E80" s="1"/>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C81" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E81" s="1"/>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C82" t="s">
         <v>148</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E82" s="1"/>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C83" t="s">
         <v>151</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E83" s="1"/>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C84" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E84" s="1"/>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C85" t="s">
         <v>148</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E85" s="1"/>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C86" t="s">
         <v>151</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E86" s="1"/>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C87" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E87" s="1"/>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C88" t="s">
         <v>148</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E88" s="1"/>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C89" t="s">
         <v>151</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E89" s="1"/>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C90" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E90" s="1"/>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C91" t="s">
         <v>148</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E91" s="1"/>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C92" t="s">
         <v>151</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E92" s="1"/>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C93" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E93" s="1"/>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C94" t="s">
         <v>148</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E94" s="1"/>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C95" t="s">
         <v>151</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E95" s="1"/>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C96" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E96" s="1"/>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C97" t="s">
         <v>148</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E97" s="1"/>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C98" t="s">
         <v>151</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E98" s="1"/>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C99" t="s">
+        <v>539</v>
+      </c>
+      <c r="D99" s="1" t="s">
         <v>538</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>537</v>
       </c>
       <c r="E99" s="1"/>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C100" t="s">
         <v>148</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E100" s="20"/>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C101" t="s">
         <v>151</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E101" s="20" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" t="s">
+        <v>540</v>
+      </c>
+      <c r="C102" t="s">
         <v>539</v>
       </c>
-      <c r="C102" t="s">
-        <v>538</v>
-      </c>
       <c r="D102" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E102" s="20" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C103" t="s">
         <v>148</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E103" s="20"/>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C104" t="s">
         <v>151</v>
       </c>
       <c r="D104" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="E104" s="20" t="s">
         <v>542</v>
-      </c>
-      <c r="E104" s="20" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" t="s">
+        <v>540</v>
+      </c>
+      <c r="C105" t="s">
         <v>539</v>
       </c>
-      <c r="C105" t="s">
-        <v>538</v>
-      </c>
       <c r="D105" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="E105" s="20" t="s">
         <v>542</v>
-      </c>
-      <c r="E105" s="20" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C106" t="s">
         <v>148</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E106" s="20"/>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C107" t="s">
         <v>151</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E107" s="20" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" t="s">
+        <v>540</v>
+      </c>
+      <c r="C108" t="s">
         <v>539</v>
       </c>
-      <c r="C108" t="s">
-        <v>538</v>
-      </c>
       <c r="D108" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E108" s="20" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C109" t="s">
         <v>148</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E109" s="20"/>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C110" t="s">
         <v>151</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E110" s="20" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" t="s">
+        <v>540</v>
+      </c>
+      <c r="C111" t="s">
         <v>539</v>
       </c>
-      <c r="C111" t="s">
-        <v>538</v>
-      </c>
       <c r="D111" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E111" s="20" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C112" t="s">
         <v>148</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E112" s="1"/>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C113" t="s">
         <v>151</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E113" s="20" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" t="s">
+        <v>540</v>
+      </c>
+      <c r="C114" t="s">
         <v>539</v>
       </c>
-      <c r="C114" t="s">
-        <v>538</v>
-      </c>
       <c r="D114" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E114" s="20" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C115" t="s">
         <v>148</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E115" s="1"/>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C116" t="s">
         <v>151</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E116" s="1"/>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C117" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E117" s="1"/>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C118" t="s">
         <v>11</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E118" s="1"/>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C119" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E119" s="1"/>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C120" t="s">
+        <v>551</v>
+      </c>
+      <c r="D120" s="1" t="s">
         <v>550</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>549</v>
       </c>
       <c r="E120" s="1"/>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C121" t="s">
         <v>11</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E121" s="1"/>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C122" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E122" s="1"/>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C123" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D123" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E123" s="1"/>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C124" t="s">
         <v>11</v>
       </c>
       <c r="D124" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E124" s="1"/>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C125" t="s">
+        <v>554</v>
+      </c>
+      <c r="D125" t="s">
         <v>553</v>
-      </c>
-      <c r="D125" t="s">
-        <v>552</v>
       </c>
       <c r="E125" s="1"/>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C126" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D126" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E126" s="1"/>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C127" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D127" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E127" s="1"/>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C128" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D128" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E128" s="1"/>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C129" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D129" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E129" s="1"/>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C130" t="s">
+        <v>560</v>
+      </c>
+      <c r="D130" t="s">
         <v>559</v>
-      </c>
-      <c r="D130" t="s">
-        <v>558</v>
       </c>
       <c r="E130" s="1"/>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C131" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D131" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E131" s="1"/>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C132" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D132" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E132" s="1"/>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C133" t="s">
         <v>11</v>
       </c>
       <c r="D133" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E133" s="1"/>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C134" t="s">
         <v>110</v>
       </c>
       <c r="D134" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E134" s="1"/>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C135" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D135" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E135" s="1"/>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C136" t="s">
+        <v>564</v>
+      </c>
+      <c r="D136" t="s">
         <v>563</v>
-      </c>
-      <c r="D136" t="s">
-        <v>562</v>
       </c>
       <c r="E136" s="1"/>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C137" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D137" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E137" s="1"/>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C138" t="s">
         <v>11</v>
       </c>
       <c r="D138" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E138" s="1"/>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C139" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D139" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E139" s="1"/>
     </row>
@@ -10842,13 +10841,13 @@
         <v>78</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>80</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E159" s="3" t="s">
         <v>92</v>
@@ -10861,13 +10860,13 @@
         <v>78</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E160" s="3" t="s">
         <v>11</v>
@@ -10877,37 +10876,37 @@
     </row>
     <row r="161" spans="1:7">
       <c r="B161" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E161" s="1"/>
     </row>
     <row r="162" spans="1:7">
       <c r="B162" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E162" s="1"/>
     </row>
     <row r="163" spans="1:7">
       <c r="B163" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E163" s="1"/>
     </row>
     <row r="164" spans="1:7">
       <c r="B164" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E164" s="1"/>
     </row>
@@ -10916,13 +10915,13 @@
         <v>78</v>
       </c>
       <c r="B165" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C165" t="s">
         <v>80</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>82</v>
@@ -10939,13 +10938,13 @@
         <v>78</v>
       </c>
       <c r="B166" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C166" t="s">
         <v>11</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>11</v>
@@ -10962,13 +10961,13 @@
         <v>78</v>
       </c>
       <c r="B167" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C167" t="s">
         <v>80</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>92</v>
@@ -10985,13 +10984,13 @@
         <v>78</v>
       </c>
       <c r="B168" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C168" t="s">
         <v>11</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>11</v>
@@ -11005,10 +11004,10 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169" s="18" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B169" s="18" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C169" s="18"/>
       <c r="D169" s="19"/>
@@ -11018,10 +11017,10 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170" s="18" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B170" s="18" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C170" s="18"/>
       <c r="D170" s="19"/>
@@ -11034,13 +11033,13 @@
         <v>78</v>
       </c>
       <c r="B171" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C171" t="s">
         <v>110</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>112</v>
@@ -11057,13 +11056,13 @@
         <v>78</v>
       </c>
       <c r="B172" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C172" t="s">
         <v>11</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>11</v>
@@ -11080,13 +11079,13 @@
         <v>78</v>
       </c>
       <c r="B173" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C173" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>121</v>
@@ -11100,46 +11099,46 @@
     </row>
     <row r="174" spans="1:7">
       <c r="B174" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E174" s="1"/>
     </row>
     <row r="175" spans="1:7">
       <c r="B175" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E175" s="1"/>
     </row>
     <row r="176" spans="1:7">
       <c r="B176" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E176" s="1"/>
     </row>
     <row r="177" spans="1:7">
       <c r="B177" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E177" s="1"/>
     </row>
     <row r="178" spans="1:7">
       <c r="A178" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>148</v>
@@ -11159,10 +11158,10 @@
     </row>
     <row r="179" spans="1:7">
       <c r="A179" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>151</v>
@@ -11190,10 +11189,10 @@
     </row>
     <row r="182" spans="1:7">
       <c r="A182" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B182" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C182" t="s">
         <v>148</v>
@@ -11213,10 +11212,10 @@
     </row>
     <row r="183" spans="1:7">
       <c r="A183" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B183" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C183" t="s">
         <v>151</v>
@@ -11236,10 +11235,10 @@
     </row>
     <row r="184" spans="1:7">
       <c r="A184" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B184" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C184" t="s">
         <v>148</v>
@@ -11259,10 +11258,10 @@
     </row>
     <row r="185" spans="1:7">
       <c r="A185" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B185" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C185" t="s">
         <v>151</v>
@@ -11285,13 +11284,13 @@
         <v>161</v>
       </c>
       <c r="B186" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C186" t="s">
         <v>148</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E186" s="1" t="s">
         <v>175</v>
@@ -11302,13 +11301,13 @@
         <v>161</v>
       </c>
       <c r="B187" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C187" t="s">
         <v>151</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E187" s="1" t="s">
         <v>182</v>
@@ -11319,13 +11318,13 @@
         <v>114</v>
       </c>
       <c r="B188" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C188" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>11</v>
@@ -11336,13 +11335,13 @@
         <v>114</v>
       </c>
       <c r="B189" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C189" t="s">
         <v>11</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E189" s="1" t="s">
         <v>175</v>
@@ -11356,10 +11355,10 @@
         <v>186</v>
       </c>
       <c r="C190" t="s">
+        <v>583</v>
+      </c>
+      <c r="D190" s="1" t="s">
         <v>582</v>
-      </c>
-      <c r="D190" s="1" t="s">
-        <v>581</v>
       </c>
       <c r="E190" s="1" t="s">
         <v>179</v>
@@ -11376,7 +11375,7 @@
         <v>180</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E191" s="1" t="s">
         <v>191</v>
@@ -11384,16 +11383,16 @@
     </row>
     <row r="192" spans="1:7">
       <c r="A192" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B192" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C192" t="s">
         <v>151</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>11</v>
@@ -11407,16 +11406,16 @@
     </row>
     <row r="193" spans="1:7">
       <c r="A193" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B193" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C193" t="s">
         <v>148</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E193" s="1" t="s">
         <v>175</v>
@@ -11439,10 +11438,10 @@
         <v>177</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>585</v>
+        <v>197</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -11456,10 +11455,10 @@
         <v>180</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -11473,10 +11472,10 @@
         <v>148</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F196">
         <v>24</v>
@@ -11496,10 +11495,10 @@
         <v>151</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F197">
         <v>24</v>
@@ -11519,10 +11518,10 @@
         <v>148</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F198">
         <v>24</v>
@@ -11542,7 +11541,7 @@
         <v>151</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E199" s="1" t="s">
         <v>587</v>
@@ -11565,10 +11564,10 @@
         <v>148</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F200">
         <v>24</v>
@@ -11588,10 +11587,10 @@
         <v>151</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F201">
         <v>24</v>
@@ -11602,16 +11601,16 @@
     </row>
     <row r="202" spans="1:7">
       <c r="B202" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C202" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F202">
         <v>24</v>
@@ -11622,16 +11621,16 @@
     </row>
     <row r="203" spans="1:7">
       <c r="B203" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C203" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F203">
         <v>24</v>
@@ -11642,19 +11641,19 @@
     </row>
     <row r="204" spans="1:7">
       <c r="A204" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B204" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C204" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F204">
         <v>24</v>
@@ -11665,19 +11664,19 @@
     </row>
     <row r="205" spans="1:7">
       <c r="A205" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B205" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C205" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F205">
         <v>24</v>
@@ -11688,16 +11687,16 @@
     </row>
     <row r="206" spans="1:7">
       <c r="B206" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C206" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F206">
         <v>24</v>
@@ -11708,16 +11707,16 @@
     </row>
     <row r="207" spans="1:7">
       <c r="B207" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C207" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F207">
         <v>24</v>
@@ -11728,16 +11727,16 @@
     </row>
     <row r="208" spans="1:7">
       <c r="B208" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C208" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F208">
         <v>24</v>
@@ -11748,16 +11747,16 @@
     </row>
     <row r="209" spans="2:7">
       <c r="B209" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C209" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F209">
         <v>24</v>
